--- a/Week_6/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_6/Capstone Timesheet_Ripal Patel.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Humber\Semester 3\Capstone Project\HealthCare Plus\Week_6\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8380"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId5"/>
+    <sheet name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>Week_1</t>
   </si>
@@ -166,63 +174,66 @@
     <t>Week_6</t>
   </si>
   <si>
-    <t>Figma User Testing (for 2 Users)</t>
+    <t>Figma User Testing (2 Users)</t>
+  </si>
+  <si>
+    <t>Figma User Testing (3 Users)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd-mmm"/>
-    <numFmt numFmtId="165" formatCode="d-mmm"/>
+    <numFmt numFmtId="164" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="165" formatCode="d\-mmm"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -232,7 +243,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -289,8 +300,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
-    <border/>
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -304,189 +321,189 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="57">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="7" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,7 +511,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -684,23 +701,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AA953"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="62.25"/>
-    <col customWidth="1" min="3" max="3" width="12.25"/>
-    <col customWidth="1" min="4" max="4" width="12.13"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="62.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,13 +757,13 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="5">
-        <v>46037.0</v>
+        <v>46037</v>
       </c>
       <c r="D2" s="6">
         <v>1.3</v>
@@ -772,13 +792,13 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="5">
-        <v>46037.0</v>
+        <v>46037</v>
       </c>
       <c r="D3" s="6">
         <v>0.15</v>
@@ -807,16 +827,16 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5">
-        <v>46037.0</v>
+        <v>46037</v>
       </c>
       <c r="D4" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -842,16 +862,16 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="5">
-        <v>46037.0</v>
+        <v>46037</v>
       </c>
       <c r="D5" s="4">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -877,13 +897,13 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="5">
-        <v>46038.0</v>
+        <v>46038</v>
       </c>
       <c r="D6" s="4">
         <v>4.75</v>
@@ -912,13 +932,13 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>46038.0</v>
+        <v>46038</v>
       </c>
       <c r="D7" s="4">
         <v>3.5</v>
@@ -947,13 +967,13 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="5">
-        <v>46038.0</v>
+        <v>46038</v>
       </c>
       <c r="D8" s="4">
         <v>5.75</v>
@@ -982,16 +1002,16 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>46039.0</v>
+        <v>46039</v>
       </c>
       <c r="D9" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1017,13 +1037,13 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="5">
-        <v>46039.0</v>
+        <v>46039</v>
       </c>
       <c r="D10" s="4">
         <v>5.5</v>
@@ -1052,13 +1072,13 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="5">
-        <v>46041.0</v>
+        <v>46041</v>
       </c>
       <c r="D11" s="4">
         <v>4.75</v>
@@ -1087,13 +1107,13 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="5">
-        <v>46043.0</v>
+        <v>46043</v>
       </c>
       <c r="D12" s="4">
         <v>4.75</v>
@@ -1122,7 +1142,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
@@ -1151,14 +1171,14 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="7">
-        <f>sum(D2:D12)</f>
+        <f>SUM(D2:D12)</f>
         <v>38.6</v>
       </c>
       <c r="E14" s="2"/>
@@ -1185,7 +1205,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1214,7 +1234,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1243,7 +1263,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="9" t="s">
         <v>16</v>
       </c>
@@ -1280,13 +1300,13 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="12">
-        <v>46044.0</v>
+        <v>46044</v>
       </c>
       <c r="D18" s="13">
         <v>1.5</v>
@@ -1315,16 +1335,16 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="12">
-        <v>46044.0</v>
+        <v>46044</v>
       </c>
       <c r="D19" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1350,16 +1370,16 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="12">
-        <v>46044.0</v>
+        <v>46044</v>
       </c>
       <c r="D20" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1385,16 +1405,16 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="12">
-        <v>46045.0</v>
+        <v>46045</v>
       </c>
       <c r="D21" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1420,16 +1440,16 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="12">
-        <v>46045.0</v>
+        <v>46045</v>
       </c>
       <c r="D22" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1455,13 +1475,13 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="12">
-        <v>46046.0</v>
+        <v>46046</v>
       </c>
       <c r="D23" s="13">
         <v>1.5</v>
@@ -1490,13 +1510,13 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="12">
-        <v>46046.0</v>
+        <v>46046</v>
       </c>
       <c r="D24" s="13">
         <v>2.5</v>
@@ -1525,16 +1545,16 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="12">
-        <v>46046.0</v>
+        <v>46046</v>
       </c>
       <c r="D25" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1560,13 +1580,13 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
       <c r="B26" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="12">
-        <v>46047.0</v>
+        <v>46047</v>
       </c>
       <c r="D26" s="13">
         <v>1.75</v>
@@ -1595,16 +1615,16 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="12">
-        <v>46047.0</v>
+        <v>46047</v>
       </c>
       <c r="D27" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1630,13 +1650,13 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="12">
-        <v>46047.0</v>
+        <v>46047</v>
       </c>
       <c r="D28" s="13">
         <v>2.75</v>
@@ -1665,16 +1685,16 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="16">
-        <v>46048.0</v>
+        <v>46048</v>
       </c>
       <c r="D29" s="17">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1700,16 +1720,16 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A30" s="14"/>
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="16">
-        <v>46048.0</v>
+        <v>46048</v>
       </c>
       <c r="D30" s="17">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -1735,16 +1755,16 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A31" s="14"/>
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C31" s="16">
-        <v>46048.0</v>
+        <v>46048</v>
       </c>
       <c r="D31" s="17">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1770,13 +1790,13 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A32" s="14"/>
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="16">
-        <v>46049.0</v>
+        <v>46049</v>
       </c>
       <c r="D32" s="17">
         <v>2.5</v>
@@ -1805,13 +1825,13 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A33" s="14"/>
       <c r="B33" s="18" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="19">
-        <v>46049.0</v>
+        <v>46049</v>
       </c>
       <c r="D33" s="20">
         <v>3.75</v>
@@ -1840,14 +1860,14 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="22"/>
       <c r="D34" s="21">
-        <f>sum(D18:D33)</f>
+        <f>SUM(D18:D33)</f>
         <v>33.4</v>
       </c>
       <c r="E34" s="2"/>
@@ -1874,7 +1894,7 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1903,7 +1923,7 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1932,7 +1952,7 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A37" s="23" t="s">
         <v>33</v>
       </c>
@@ -1969,13 +1989,13 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A38" s="24"/>
       <c r="B38" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C38" s="26">
-        <v>46052.0</v>
+        <v>46052</v>
       </c>
       <c r="D38" s="27">
         <v>1.5</v>
@@ -2004,13 +2024,13 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A39" s="24"/>
       <c r="B39" s="25" t="s">
         <v>35</v>
       </c>
       <c r="C39" s="26">
-        <v>46052.0</v>
+        <v>46052</v>
       </c>
       <c r="D39" s="27">
         <v>1.75</v>
@@ -2039,13 +2059,13 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A40" s="24"/>
       <c r="B40" s="25" t="s">
         <v>36</v>
       </c>
       <c r="C40" s="26">
-        <v>46052.0</v>
+        <v>46052</v>
       </c>
       <c r="D40" s="27">
         <v>2.15</v>
@@ -2074,13 +2094,13 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A41" s="24"/>
       <c r="B41" s="25" t="s">
         <v>37</v>
       </c>
       <c r="C41" s="26">
-        <v>46054.0</v>
+        <v>46054</v>
       </c>
       <c r="D41" s="27">
         <v>2.75</v>
@@ -2109,13 +2129,13 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A42" s="24"/>
       <c r="B42" s="25" t="s">
         <v>38</v>
       </c>
       <c r="C42" s="26">
-        <v>46055.0</v>
+        <v>46055</v>
       </c>
       <c r="D42" s="27">
         <v>3.75</v>
@@ -2144,7 +2164,7 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2173,14 +2193,14 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A44" s="28"/>
       <c r="B44" s="29" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="24">
-        <f>sum(D38:D42)</f>
+        <f>SUM(D38:D42)</f>
         <v>11.9</v>
       </c>
       <c r="E44" s="3"/>
@@ -2207,7 +2227,7 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2236,7 +2256,7 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2265,7 +2285,7 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A47" s="31" t="s">
         <v>39</v>
       </c>
@@ -2302,13 +2322,13 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A48" s="32"/>
       <c r="B48" s="33" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="34">
-        <v>46059.0</v>
+        <v>46059</v>
       </c>
       <c r="D48" s="35">
         <v>3.75</v>
@@ -2337,13 +2357,13 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A49" s="32"/>
       <c r="B49" s="33" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="34">
-        <v>46061.0</v>
+        <v>46061</v>
       </c>
       <c r="D49" s="35">
         <v>3.25</v>
@@ -2372,13 +2392,13 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A50" s="32"/>
       <c r="B50" s="33" t="s">
         <v>42</v>
       </c>
       <c r="C50" s="34">
-        <v>46061.0</v>
+        <v>46061</v>
       </c>
       <c r="D50" s="35">
         <v>4.5</v>
@@ -2407,13 +2427,13 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A51" s="32"/>
       <c r="B51" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="34">
-        <v>46062.0</v>
+        <v>46062</v>
       </c>
       <c r="D51" s="35">
         <v>3.75</v>
@@ -2442,13 +2462,13 @@
       <c r="Z51" s="3"/>
       <c r="AA51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A52" s="32"/>
       <c r="B52" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C52" s="34">
-        <v>46063.0</v>
+        <v>46063</v>
       </c>
       <c r="D52" s="35">
         <v>3.5</v>
@@ -2477,7 +2497,7 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2506,14 +2526,14 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A54" s="36"/>
       <c r="B54" s="37" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="38"/>
       <c r="D54" s="39">
-        <f>sum(D48:D52)</f>
+        <f>SUM(D48:D52)</f>
         <v>18.75</v>
       </c>
       <c r="E54" s="3"/>
@@ -2540,7 +2560,7 @@
       <c r="Z54" s="3"/>
       <c r="AA54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2569,7 +2589,7 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2598,7 +2618,7 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A57" s="40" t="s">
         <v>45</v>
       </c>
@@ -2635,13 +2655,13 @@
       <c r="Z57" s="3"/>
       <c r="AA57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A58" s="41"/>
       <c r="B58" s="42" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="43">
-        <v>46066.0</v>
+        <v>46066</v>
       </c>
       <c r="D58" s="44">
         <v>2.15</v>
@@ -2670,13 +2690,13 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A59" s="41"/>
       <c r="B59" s="42" t="s">
         <v>47</v>
       </c>
       <c r="C59" s="43">
-        <v>46066.0</v>
+        <v>46066</v>
       </c>
       <c r="D59" s="44">
         <v>3.75</v>
@@ -2705,13 +2725,13 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A60" s="41"/>
       <c r="B60" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="43">
-        <v>46069.0</v>
+        <v>46069</v>
       </c>
       <c r="D60" s="44">
         <v>3.5</v>
@@ -2740,13 +2760,13 @@
       <c r="Z60" s="3"/>
       <c r="AA60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A61" s="41"/>
       <c r="B61" s="42" t="s">
         <v>49</v>
       </c>
       <c r="C61" s="43">
-        <v>46069.0</v>
+        <v>46069</v>
       </c>
       <c r="D61" s="44">
         <v>2.5</v>
@@ -2775,7 +2795,7 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2804,14 +2824,14 @@
       <c r="Z62" s="3"/>
       <c r="AA62" s="3"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A63" s="45"/>
       <c r="B63" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="47"/>
       <c r="D63" s="41">
-        <f>sum(D58:D61)</f>
+        <f>SUM(D58:D61)</f>
         <v>11.9</v>
       </c>
       <c r="E63" s="3"/>
@@ -2838,7 +2858,7 @@
       <c r="Z63" s="3"/>
       <c r="AA63" s="3"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2867,7 +2887,7 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2896,17 +2916,17 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3"/>
     </row>
-    <row r="66">
-      <c r="A66" s="48" t="s">
+    <row r="66" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="B66" s="48" t="s">
+      <c r="B66" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="48" t="s">
+      <c r="C66" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="48" t="s">
+      <c r="D66" s="52" t="s">
         <v>3</v>
       </c>
       <c r="E66" s="3"/>
@@ -2933,15 +2953,15 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3"/>
     </row>
-    <row r="67">
-      <c r="A67" s="49"/>
-      <c r="B67" s="50" t="s">
+    <row r="67" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="53"/>
+      <c r="B67" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="C67" s="51">
-        <v>46073.0</v>
+      <c r="C67" s="55">
+        <v>46073</v>
       </c>
-      <c r="D67" s="52">
+      <c r="D67" s="56">
         <v>1.75</v>
       </c>
       <c r="E67" s="3"/>
@@ -2968,11 +2988,17 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
     </row>
-    <row r="68">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
+    <row r="68" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="53"/>
+      <c r="B68" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" s="55">
+        <v>46074</v>
+      </c>
+      <c r="D68" s="56">
+        <v>2</v>
+      </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -2997,16 +3023,11 @@
       <c r="Z68" s="3"/>
       <c r="AA68" s="3"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A69" s="53"/>
-      <c r="B69" s="54" t="s">
-        <v>15</v>
-      </c>
+      <c r="B69" s="54"/>
       <c r="C69" s="55"/>
-      <c r="D69" s="49">
-        <f>sum(D67)</f>
-        <v>1.75</v>
-      </c>
+      <c r="D69" s="56"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -3031,11 +3052,11 @@
       <c r="Z69" s="3"/>
       <c r="AA69" s="3"/>
     </row>
-    <row r="70">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
+    <row r="70" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="53"/>
+      <c r="B70" s="54"/>
+      <c r="C70" s="55"/>
+      <c r="D70" s="56"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
@@ -3060,7 +3081,7 @@
       <c r="Z70" s="3"/>
       <c r="AA70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -3089,11 +3110,16 @@
       <c r="Z71" s="3"/>
       <c r="AA71" s="3"/>
     </row>
-    <row r="72">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
+    <row r="72" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="49"/>
+      <c r="B72" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="51"/>
+      <c r="D72" s="48">
+        <f>SUM(D67:D68)</f>
+        <v>3.75</v>
+      </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -3118,7 +3144,7 @@
       <c r="Z72" s="3"/>
       <c r="AA72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -3147,7 +3173,7 @@
       <c r="Z73" s="3"/>
       <c r="AA73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3176,7 +3202,7 @@
       <c r="Z74" s="3"/>
       <c r="AA74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3205,7 +3231,7 @@
       <c r="Z75" s="3"/>
       <c r="AA75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -3234,7 +3260,7 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -3263,7 +3289,7 @@
       <c r="Z77" s="3"/>
       <c r="AA77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -3292,7 +3318,7 @@
       <c r="Z78" s="3"/>
       <c r="AA78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -3321,7 +3347,7 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -3350,7 +3376,7 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -3379,7 +3405,7 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -3408,7 +3434,7 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -3437,7 +3463,7 @@
       <c r="Z83" s="3"/>
       <c r="AA83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -3466,7 +3492,7 @@
       <c r="Z84" s="3"/>
       <c r="AA84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -3495,7 +3521,7 @@
       <c r="Z85" s="3"/>
       <c r="AA85" s="3"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -3524,7 +3550,7 @@
       <c r="Z86" s="3"/>
       <c r="AA86" s="3"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -3553,7 +3579,7 @@
       <c r="Z87" s="3"/>
       <c r="AA87" s="3"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -3582,7 +3608,7 @@
       <c r="Z88" s="3"/>
       <c r="AA88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3611,7 +3637,7 @@
       <c r="Z89" s="3"/>
       <c r="AA89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3640,7 +3666,7 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -3669,7 +3695,7 @@
       <c r="Z91" s="3"/>
       <c r="AA91" s="3"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -3698,7 +3724,7 @@
       <c r="Z92" s="3"/>
       <c r="AA92" s="3"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -3727,7 +3753,7 @@
       <c r="Z93" s="3"/>
       <c r="AA93" s="3"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -3756,7 +3782,7 @@
       <c r="Z94" s="3"/>
       <c r="AA94" s="3"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -3785,7 +3811,7 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -3814,7 +3840,7 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -3843,7 +3869,7 @@
       <c r="Z97" s="3"/>
       <c r="AA97" s="3"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -3872,7 +3898,7 @@
       <c r="Z98" s="3"/>
       <c r="AA98" s="3"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -3901,7 +3927,7 @@
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -3930,7 +3956,7 @@
       <c r="Z100" s="3"/>
       <c r="AA100" s="3"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -3959,7 +3985,7 @@
       <c r="Z101" s="3"/>
       <c r="AA101" s="3"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -3988,7 +4014,7 @@
       <c r="Z102" s="3"/>
       <c r="AA102" s="3"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4017,7 +4043,7 @@
       <c r="Z103" s="3"/>
       <c r="AA103" s="3"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4046,7 +4072,7 @@
       <c r="Z104" s="3"/>
       <c r="AA104" s="3"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4075,7 +4101,7 @@
       <c r="Z105" s="3"/>
       <c r="AA105" s="3"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4104,7 +4130,7 @@
       <c r="Z106" s="3"/>
       <c r="AA106" s="3"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4133,7 +4159,7 @@
       <c r="Z107" s="3"/>
       <c r="AA107" s="3"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4162,7 +4188,7 @@
       <c r="Z108" s="3"/>
       <c r="AA108" s="3"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4191,7 +4217,7 @@
       <c r="Z109" s="3"/>
       <c r="AA109" s="3"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4220,7 +4246,7 @@
       <c r="Z110" s="3"/>
       <c r="AA110" s="3"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4249,7 +4275,7 @@
       <c r="Z111" s="3"/>
       <c r="AA111" s="3"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4278,7 +4304,7 @@
       <c r="Z112" s="3"/>
       <c r="AA112" s="3"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4307,7 +4333,7 @@
       <c r="Z113" s="3"/>
       <c r="AA113" s="3"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4336,7 +4362,7 @@
       <c r="Z114" s="3"/>
       <c r="AA114" s="3"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4365,7 +4391,7 @@
       <c r="Z115" s="3"/>
       <c r="AA115" s="3"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4394,7 +4420,7 @@
       <c r="Z116" s="3"/>
       <c r="AA116" s="3"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4423,7 +4449,7 @@
       <c r="Z117" s="3"/>
       <c r="AA117" s="3"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4452,7 +4478,7 @@
       <c r="Z118" s="3"/>
       <c r="AA118" s="3"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4481,7 +4507,7 @@
       <c r="Z119" s="3"/>
       <c r="AA119" s="3"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -4510,7 +4536,7 @@
       <c r="Z120" s="3"/>
       <c r="AA120" s="3"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4539,7 +4565,7 @@
       <c r="Z121" s="3"/>
       <c r="AA121" s="3"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4568,7 +4594,7 @@
       <c r="Z122" s="3"/>
       <c r="AA122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4597,7 +4623,7 @@
       <c r="Z123" s="3"/>
       <c r="AA123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4626,7 +4652,7 @@
       <c r="Z124" s="3"/>
       <c r="AA124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4655,7 +4681,7 @@
       <c r="Z125" s="3"/>
       <c r="AA125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4684,7 +4710,7 @@
       <c r="Z126" s="3"/>
       <c r="AA126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -4713,7 +4739,7 @@
       <c r="Z127" s="3"/>
       <c r="AA127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -4742,7 +4768,7 @@
       <c r="Z128" s="3"/>
       <c r="AA128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -4771,7 +4797,7 @@
       <c r="Z129" s="3"/>
       <c r="AA129" s="3"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -4800,7 +4826,7 @@
       <c r="Z130" s="3"/>
       <c r="AA130" s="3"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -4829,7 +4855,7 @@
       <c r="Z131" s="3"/>
       <c r="AA131" s="3"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -4858,7 +4884,7 @@
       <c r="Z132" s="3"/>
       <c r="AA132" s="3"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -4887,7 +4913,7 @@
       <c r="Z133" s="3"/>
       <c r="AA133" s="3"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -4916,7 +4942,7 @@
       <c r="Z134" s="3"/>
       <c r="AA134" s="3"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -4945,7 +4971,7 @@
       <c r="Z135" s="3"/>
       <c r="AA135" s="3"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -4974,7 +5000,7 @@
       <c r="Z136" s="3"/>
       <c r="AA136" s="3"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -5003,7 +5029,7 @@
       <c r="Z137" s="3"/>
       <c r="AA137" s="3"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -5032,7 +5058,7 @@
       <c r="Z138" s="3"/>
       <c r="AA138" s="3"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -5061,7 +5087,7 @@
       <c r="Z139" s="3"/>
       <c r="AA139" s="3"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -5090,7 +5116,7 @@
       <c r="Z140" s="3"/>
       <c r="AA140" s="3"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -5119,7 +5145,7 @@
       <c r="Z141" s="3"/>
       <c r="AA141" s="3"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -5148,7 +5174,7 @@
       <c r="Z142" s="3"/>
       <c r="AA142" s="3"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -5177,7 +5203,7 @@
       <c r="Z143" s="3"/>
       <c r="AA143" s="3"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -5206,7 +5232,7 @@
       <c r="Z144" s="3"/>
       <c r="AA144" s="3"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -5235,7 +5261,7 @@
       <c r="Z145" s="3"/>
       <c r="AA145" s="3"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -5264,7 +5290,7 @@
       <c r="Z146" s="3"/>
       <c r="AA146" s="3"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -5293,7 +5319,7 @@
       <c r="Z147" s="3"/>
       <c r="AA147" s="3"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -5322,7 +5348,7 @@
       <c r="Z148" s="3"/>
       <c r="AA148" s="3"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -5351,7 +5377,7 @@
       <c r="Z149" s="3"/>
       <c r="AA149" s="3"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -5380,7 +5406,7 @@
       <c r="Z150" s="3"/>
       <c r="AA150" s="3"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -5409,7 +5435,7 @@
       <c r="Z151" s="3"/>
       <c r="AA151" s="3"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -5438,7 +5464,7 @@
       <c r="Z152" s="3"/>
       <c r="AA152" s="3"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -5467,7 +5493,7 @@
       <c r="Z153" s="3"/>
       <c r="AA153" s="3"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -5496,7 +5522,7 @@
       <c r="Z154" s="3"/>
       <c r="AA154" s="3"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -5525,7 +5551,7 @@
       <c r="Z155" s="3"/>
       <c r="AA155" s="3"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -5554,7 +5580,7 @@
       <c r="Z156" s="3"/>
       <c r="AA156" s="3"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -5583,7 +5609,7 @@
       <c r="Z157" s="3"/>
       <c r="AA157" s="3"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -5612,7 +5638,7 @@
       <c r="Z158" s="3"/>
       <c r="AA158" s="3"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -5641,7 +5667,7 @@
       <c r="Z159" s="3"/>
       <c r="AA159" s="3"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -5670,7 +5696,7 @@
       <c r="Z160" s="3"/>
       <c r="AA160" s="3"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -5699,7 +5725,7 @@
       <c r="Z161" s="3"/>
       <c r="AA161" s="3"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -5728,7 +5754,7 @@
       <c r="Z162" s="3"/>
       <c r="AA162" s="3"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -5757,7 +5783,7 @@
       <c r="Z163" s="3"/>
       <c r="AA163" s="3"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -5786,7 +5812,7 @@
       <c r="Z164" s="3"/>
       <c r="AA164" s="3"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -5815,7 +5841,7 @@
       <c r="Z165" s="3"/>
       <c r="AA165" s="3"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -5844,7 +5870,7 @@
       <c r="Z166" s="3"/>
       <c r="AA166" s="3"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -5873,7 +5899,7 @@
       <c r="Z167" s="3"/>
       <c r="AA167" s="3"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -5902,7 +5928,7 @@
       <c r="Z168" s="3"/>
       <c r="AA168" s="3"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -5931,7 +5957,7 @@
       <c r="Z169" s="3"/>
       <c r="AA169" s="3"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -5960,7 +5986,7 @@
       <c r="Z170" s="3"/>
       <c r="AA170" s="3"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -5989,7 +6015,7 @@
       <c r="Z171" s="3"/>
       <c r="AA171" s="3"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -6018,7 +6044,7 @@
       <c r="Z172" s="3"/>
       <c r="AA172" s="3"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -6047,7 +6073,7 @@
       <c r="Z173" s="3"/>
       <c r="AA173" s="3"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -6076,7 +6102,7 @@
       <c r="Z174" s="3"/>
       <c r="AA174" s="3"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -6105,7 +6131,7 @@
       <c r="Z175" s="3"/>
       <c r="AA175" s="3"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -6134,7 +6160,7 @@
       <c r="Z176" s="3"/>
       <c r="AA176" s="3"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -6163,7 +6189,7 @@
       <c r="Z177" s="3"/>
       <c r="AA177" s="3"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -6192,7 +6218,7 @@
       <c r="Z178" s="3"/>
       <c r="AA178" s="3"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -6221,7 +6247,7 @@
       <c r="Z179" s="3"/>
       <c r="AA179" s="3"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -6250,7 +6276,7 @@
       <c r="Z180" s="3"/>
       <c r="AA180" s="3"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -6279,7 +6305,7 @@
       <c r="Z181" s="3"/>
       <c r="AA181" s="3"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -6308,7 +6334,7 @@
       <c r="Z182" s="3"/>
       <c r="AA182" s="3"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -6337,7 +6363,7 @@
       <c r="Z183" s="3"/>
       <c r="AA183" s="3"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -6366,7 +6392,7 @@
       <c r="Z184" s="3"/>
       <c r="AA184" s="3"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -6395,7 +6421,7 @@
       <c r="Z185" s="3"/>
       <c r="AA185" s="3"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -6424,7 +6450,7 @@
       <c r="Z186" s="3"/>
       <c r="AA186" s="3"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -6453,7 +6479,7 @@
       <c r="Z187" s="3"/>
       <c r="AA187" s="3"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -6482,7 +6508,7 @@
       <c r="Z188" s="3"/>
       <c r="AA188" s="3"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -6511,7 +6537,7 @@
       <c r="Z189" s="3"/>
       <c r="AA189" s="3"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -6540,7 +6566,7 @@
       <c r="Z190" s="3"/>
       <c r="AA190" s="3"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -6569,7 +6595,7 @@
       <c r="Z191" s="3"/>
       <c r="AA191" s="3"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -6598,7 +6624,7 @@
       <c r="Z192" s="3"/>
       <c r="AA192" s="3"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -6627,7 +6653,7 @@
       <c r="Z193" s="3"/>
       <c r="AA193" s="3"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -6656,7 +6682,7 @@
       <c r="Z194" s="3"/>
       <c r="AA194" s="3"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -6685,7 +6711,7 @@
       <c r="Z195" s="3"/>
       <c r="AA195" s="3"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -6714,7 +6740,7 @@
       <c r="Z196" s="3"/>
       <c r="AA196" s="3"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -6743,7 +6769,7 @@
       <c r="Z197" s="3"/>
       <c r="AA197" s="3"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -6772,7 +6798,7 @@
       <c r="Z198" s="3"/>
       <c r="AA198" s="3"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -6801,7 +6827,7 @@
       <c r="Z199" s="3"/>
       <c r="AA199" s="3"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -6830,7 +6856,7 @@
       <c r="Z200" s="3"/>
       <c r="AA200" s="3"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -6859,7 +6885,7 @@
       <c r="Z201" s="3"/>
       <c r="AA201" s="3"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -6888,7 +6914,7 @@
       <c r="Z202" s="3"/>
       <c r="AA202" s="3"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -6917,7 +6943,7 @@
       <c r="Z203" s="3"/>
       <c r="AA203" s="3"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -6946,7 +6972,7 @@
       <c r="Z204" s="3"/>
       <c r="AA204" s="3"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -6975,7 +7001,7 @@
       <c r="Z205" s="3"/>
       <c r="AA205" s="3"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -7004,7 +7030,7 @@
       <c r="Z206" s="3"/>
       <c r="AA206" s="3"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -7033,7 +7059,7 @@
       <c r="Z207" s="3"/>
       <c r="AA207" s="3"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -7062,7 +7088,7 @@
       <c r="Z208" s="3"/>
       <c r="AA208" s="3"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -7091,7 +7117,7 @@
       <c r="Z209" s="3"/>
       <c r="AA209" s="3"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -7120,7 +7146,7 @@
       <c r="Z210" s="3"/>
       <c r="AA210" s="3"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -7149,7 +7175,7 @@
       <c r="Z211" s="3"/>
       <c r="AA211" s="3"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -7178,7 +7204,7 @@
       <c r="Z212" s="3"/>
       <c r="AA212" s="3"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -7207,7 +7233,7 @@
       <c r="Z213" s="3"/>
       <c r="AA213" s="3"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -7236,7 +7262,7 @@
       <c r="Z214" s="3"/>
       <c r="AA214" s="3"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -7265,7 +7291,7 @@
       <c r="Z215" s="3"/>
       <c r="AA215" s="3"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -7294,7 +7320,7 @@
       <c r="Z216" s="3"/>
       <c r="AA216" s="3"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -7323,7 +7349,7 @@
       <c r="Z217" s="3"/>
       <c r="AA217" s="3"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -7352,7 +7378,7 @@
       <c r="Z218" s="3"/>
       <c r="AA218" s="3"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -7381,7 +7407,7 @@
       <c r="Z219" s="3"/>
       <c r="AA219" s="3"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -7410,7 +7436,7 @@
       <c r="Z220" s="3"/>
       <c r="AA220" s="3"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -7439,7 +7465,7 @@
       <c r="Z221" s="3"/>
       <c r="AA221" s="3"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -7468,7 +7494,7 @@
       <c r="Z222" s="3"/>
       <c r="AA222" s="3"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -7497,7 +7523,7 @@
       <c r="Z223" s="3"/>
       <c r="AA223" s="3"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -7526,7 +7552,7 @@
       <c r="Z224" s="3"/>
       <c r="AA224" s="3"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -7555,7 +7581,7 @@
       <c r="Z225" s="3"/>
       <c r="AA225" s="3"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -7584,7 +7610,7 @@
       <c r="Z226" s="3"/>
       <c r="AA226" s="3"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -7613,7 +7639,7 @@
       <c r="Z227" s="3"/>
       <c r="AA227" s="3"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -7642,7 +7668,7 @@
       <c r="Z228" s="3"/>
       <c r="AA228" s="3"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -7671,7 +7697,7 @@
       <c r="Z229" s="3"/>
       <c r="AA229" s="3"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -7700,7 +7726,7 @@
       <c r="Z230" s="3"/>
       <c r="AA230" s="3"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -7729,7 +7755,7 @@
       <c r="Z231" s="3"/>
       <c r="AA231" s="3"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -7758,7 +7784,7 @@
       <c r="Z232" s="3"/>
       <c r="AA232" s="3"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -7787,7 +7813,7 @@
       <c r="Z233" s="3"/>
       <c r="AA233" s="3"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -7816,7 +7842,7 @@
       <c r="Z234" s="3"/>
       <c r="AA234" s="3"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -7845,7 +7871,7 @@
       <c r="Z235" s="3"/>
       <c r="AA235" s="3"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -7874,7 +7900,7 @@
       <c r="Z236" s="3"/>
       <c r="AA236" s="3"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -7903,7 +7929,7 @@
       <c r="Z237" s="3"/>
       <c r="AA237" s="3"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -7932,7 +7958,7 @@
       <c r="Z238" s="3"/>
       <c r="AA238" s="3"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -7961,7 +7987,7 @@
       <c r="Z239" s="3"/>
       <c r="AA239" s="3"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -7990,7 +8016,7 @@
       <c r="Z240" s="3"/>
       <c r="AA240" s="3"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -8019,7 +8045,7 @@
       <c r="Z241" s="3"/>
       <c r="AA241" s="3"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -8048,7 +8074,7 @@
       <c r="Z242" s="3"/>
       <c r="AA242" s="3"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -8077,7 +8103,7 @@
       <c r="Z243" s="3"/>
       <c r="AA243" s="3"/>
     </row>
-    <row r="244">
+    <row r="244" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -8106,7 +8132,7 @@
       <c r="Z244" s="3"/>
       <c r="AA244" s="3"/>
     </row>
-    <row r="245">
+    <row r="245" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -8135,7 +8161,7 @@
       <c r="Z245" s="3"/>
       <c r="AA245" s="3"/>
     </row>
-    <row r="246">
+    <row r="246" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -8164,7 +8190,7 @@
       <c r="Z246" s="3"/>
       <c r="AA246" s="3"/>
     </row>
-    <row r="247">
+    <row r="247" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -8193,7 +8219,7 @@
       <c r="Z247" s="3"/>
       <c r="AA247" s="3"/>
     </row>
-    <row r="248">
+    <row r="248" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -8222,7 +8248,7 @@
       <c r="Z248" s="3"/>
       <c r="AA248" s="3"/>
     </row>
-    <row r="249">
+    <row r="249" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -8251,7 +8277,7 @@
       <c r="Z249" s="3"/>
       <c r="AA249" s="3"/>
     </row>
-    <row r="250">
+    <row r="250" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -8280,7 +8306,7 @@
       <c r="Z250" s="3"/>
       <c r="AA250" s="3"/>
     </row>
-    <row r="251">
+    <row r="251" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -8309,7 +8335,7 @@
       <c r="Z251" s="3"/>
       <c r="AA251" s="3"/>
     </row>
-    <row r="252">
+    <row r="252" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -8338,7 +8364,7 @@
       <c r="Z252" s="3"/>
       <c r="AA252" s="3"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -8367,7 +8393,7 @@
       <c r="Z253" s="3"/>
       <c r="AA253" s="3"/>
     </row>
-    <row r="254">
+    <row r="254" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -8396,7 +8422,7 @@
       <c r="Z254" s="3"/>
       <c r="AA254" s="3"/>
     </row>
-    <row r="255">
+    <row r="255" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -8425,7 +8451,7 @@
       <c r="Z255" s="3"/>
       <c r="AA255" s="3"/>
     </row>
-    <row r="256">
+    <row r="256" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -8454,7 +8480,7 @@
       <c r="Z256" s="3"/>
       <c r="AA256" s="3"/>
     </row>
-    <row r="257">
+    <row r="257" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -8483,7 +8509,7 @@
       <c r="Z257" s="3"/>
       <c r="AA257" s="3"/>
     </row>
-    <row r="258">
+    <row r="258" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -8512,7 +8538,7 @@
       <c r="Z258" s="3"/>
       <c r="AA258" s="3"/>
     </row>
-    <row r="259">
+    <row r="259" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -8541,7 +8567,7 @@
       <c r="Z259" s="3"/>
       <c r="AA259" s="3"/>
     </row>
-    <row r="260">
+    <row r="260" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -8570,7 +8596,7 @@
       <c r="Z260" s="3"/>
       <c r="AA260" s="3"/>
     </row>
-    <row r="261">
+    <row r="261" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -8599,7 +8625,7 @@
       <c r="Z261" s="3"/>
       <c r="AA261" s="3"/>
     </row>
-    <row r="262">
+    <row r="262" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -8628,7 +8654,7 @@
       <c r="Z262" s="3"/>
       <c r="AA262" s="3"/>
     </row>
-    <row r="263">
+    <row r="263" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -8657,7 +8683,7 @@
       <c r="Z263" s="3"/>
       <c r="AA263" s="3"/>
     </row>
-    <row r="264">
+    <row r="264" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -8686,7 +8712,7 @@
       <c r="Z264" s="3"/>
       <c r="AA264" s="3"/>
     </row>
-    <row r="265">
+    <row r="265" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -8715,7 +8741,7 @@
       <c r="Z265" s="3"/>
       <c r="AA265" s="3"/>
     </row>
-    <row r="266">
+    <row r="266" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -8744,7 +8770,7 @@
       <c r="Z266" s="3"/>
       <c r="AA266" s="3"/>
     </row>
-    <row r="267">
+    <row r="267" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -8773,7 +8799,7 @@
       <c r="Z267" s="3"/>
       <c r="AA267" s="3"/>
     </row>
-    <row r="268">
+    <row r="268" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -8802,7 +8828,7 @@
       <c r="Z268" s="3"/>
       <c r="AA268" s="3"/>
     </row>
-    <row r="269">
+    <row r="269" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -8831,7 +8857,7 @@
       <c r="Z269" s="3"/>
       <c r="AA269" s="3"/>
     </row>
-    <row r="270">
+    <row r="270" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -8860,7 +8886,7 @@
       <c r="Z270" s="3"/>
       <c r="AA270" s="3"/>
     </row>
-    <row r="271">
+    <row r="271" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -8889,7 +8915,7 @@
       <c r="Z271" s="3"/>
       <c r="AA271" s="3"/>
     </row>
-    <row r="272">
+    <row r="272" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -8918,7 +8944,7 @@
       <c r="Z272" s="3"/>
       <c r="AA272" s="3"/>
     </row>
-    <row r="273">
+    <row r="273" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -8947,7 +8973,7 @@
       <c r="Z273" s="3"/>
       <c r="AA273" s="3"/>
     </row>
-    <row r="274">
+    <row r="274" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -8976,7 +9002,7 @@
       <c r="Z274" s="3"/>
       <c r="AA274" s="3"/>
     </row>
-    <row r="275">
+    <row r="275" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -9005,7 +9031,7 @@
       <c r="Z275" s="3"/>
       <c r="AA275" s="3"/>
     </row>
-    <row r="276">
+    <row r="276" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -9034,7 +9060,7 @@
       <c r="Z276" s="3"/>
       <c r="AA276" s="3"/>
     </row>
-    <row r="277">
+    <row r="277" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -9063,7 +9089,7 @@
       <c r="Z277" s="3"/>
       <c r="AA277" s="3"/>
     </row>
-    <row r="278">
+    <row r="278" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -9092,7 +9118,7 @@
       <c r="Z278" s="3"/>
       <c r="AA278" s="3"/>
     </row>
-    <row r="279">
+    <row r="279" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -9121,7 +9147,7 @@
       <c r="Z279" s="3"/>
       <c r="AA279" s="3"/>
     </row>
-    <row r="280">
+    <row r="280" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -9150,7 +9176,7 @@
       <c r="Z280" s="3"/>
       <c r="AA280" s="3"/>
     </row>
-    <row r="281">
+    <row r="281" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -9179,7 +9205,7 @@
       <c r="Z281" s="3"/>
       <c r="AA281" s="3"/>
     </row>
-    <row r="282">
+    <row r="282" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -9208,7 +9234,7 @@
       <c r="Z282" s="3"/>
       <c r="AA282" s="3"/>
     </row>
-    <row r="283">
+    <row r="283" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -9237,7 +9263,7 @@
       <c r="Z283" s="3"/>
       <c r="AA283" s="3"/>
     </row>
-    <row r="284">
+    <row r="284" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -9266,7 +9292,7 @@
       <c r="Z284" s="3"/>
       <c r="AA284" s="3"/>
     </row>
-    <row r="285">
+    <row r="285" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -9295,7 +9321,7 @@
       <c r="Z285" s="3"/>
       <c r="AA285" s="3"/>
     </row>
-    <row r="286">
+    <row r="286" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -9324,7 +9350,7 @@
       <c r="Z286" s="3"/>
       <c r="AA286" s="3"/>
     </row>
-    <row r="287">
+    <row r="287" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -9353,7 +9379,7 @@
       <c r="Z287" s="3"/>
       <c r="AA287" s="3"/>
     </row>
-    <row r="288">
+    <row r="288" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -9382,7 +9408,7 @@
       <c r="Z288" s="3"/>
       <c r="AA288" s="3"/>
     </row>
-    <row r="289">
+    <row r="289" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -9411,7 +9437,7 @@
       <c r="Z289" s="3"/>
       <c r="AA289" s="3"/>
     </row>
-    <row r="290">
+    <row r="290" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -9440,7 +9466,7 @@
       <c r="Z290" s="3"/>
       <c r="AA290" s="3"/>
     </row>
-    <row r="291">
+    <row r="291" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -9469,7 +9495,7 @@
       <c r="Z291" s="3"/>
       <c r="AA291" s="3"/>
     </row>
-    <row r="292">
+    <row r="292" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -9498,7 +9524,7 @@
       <c r="Z292" s="3"/>
       <c r="AA292" s="3"/>
     </row>
-    <row r="293">
+    <row r="293" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -9527,7 +9553,7 @@
       <c r="Z293" s="3"/>
       <c r="AA293" s="3"/>
     </row>
-    <row r="294">
+    <row r="294" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -9556,7 +9582,7 @@
       <c r="Z294" s="3"/>
       <c r="AA294" s="3"/>
     </row>
-    <row r="295">
+    <row r="295" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -9585,7 +9611,7 @@
       <c r="Z295" s="3"/>
       <c r="AA295" s="3"/>
     </row>
-    <row r="296">
+    <row r="296" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -9614,7 +9640,7 @@
       <c r="Z296" s="3"/>
       <c r="AA296" s="3"/>
     </row>
-    <row r="297">
+    <row r="297" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -9643,7 +9669,7 @@
       <c r="Z297" s="3"/>
       <c r="AA297" s="3"/>
     </row>
-    <row r="298">
+    <row r="298" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -9672,7 +9698,7 @@
       <c r="Z298" s="3"/>
       <c r="AA298" s="3"/>
     </row>
-    <row r="299">
+    <row r="299" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -9701,7 +9727,7 @@
       <c r="Z299" s="3"/>
       <c r="AA299" s="3"/>
     </row>
-    <row r="300">
+    <row r="300" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -9730,7 +9756,7 @@
       <c r="Z300" s="3"/>
       <c r="AA300" s="3"/>
     </row>
-    <row r="301">
+    <row r="301" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -9759,7 +9785,7 @@
       <c r="Z301" s="3"/>
       <c r="AA301" s="3"/>
     </row>
-    <row r="302">
+    <row r="302" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -9788,7 +9814,7 @@
       <c r="Z302" s="3"/>
       <c r="AA302" s="3"/>
     </row>
-    <row r="303">
+    <row r="303" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -9817,7 +9843,7 @@
       <c r="Z303" s="3"/>
       <c r="AA303" s="3"/>
     </row>
-    <row r="304">
+    <row r="304" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -9846,7 +9872,7 @@
       <c r="Z304" s="3"/>
       <c r="AA304" s="3"/>
     </row>
-    <row r="305">
+    <row r="305" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -9875,7 +9901,7 @@
       <c r="Z305" s="3"/>
       <c r="AA305" s="3"/>
     </row>
-    <row r="306">
+    <row r="306" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -9904,7 +9930,7 @@
       <c r="Z306" s="3"/>
       <c r="AA306" s="3"/>
     </row>
-    <row r="307">
+    <row r="307" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -9933,7 +9959,7 @@
       <c r="Z307" s="3"/>
       <c r="AA307" s="3"/>
     </row>
-    <row r="308">
+    <row r="308" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -9962,7 +9988,7 @@
       <c r="Z308" s="3"/>
       <c r="AA308" s="3"/>
     </row>
-    <row r="309">
+    <row r="309" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -9991,7 +10017,7 @@
       <c r="Z309" s="3"/>
       <c r="AA309" s="3"/>
     </row>
-    <row r="310">
+    <row r="310" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -10020,7 +10046,7 @@
       <c r="Z310" s="3"/>
       <c r="AA310" s="3"/>
     </row>
-    <row r="311">
+    <row r="311" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -10049,7 +10075,7 @@
       <c r="Z311" s="3"/>
       <c r="AA311" s="3"/>
     </row>
-    <row r="312">
+    <row r="312" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -10078,7 +10104,7 @@
       <c r="Z312" s="3"/>
       <c r="AA312" s="3"/>
     </row>
-    <row r="313">
+    <row r="313" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -10107,7 +10133,7 @@
       <c r="Z313" s="3"/>
       <c r="AA313" s="3"/>
     </row>
-    <row r="314">
+    <row r="314" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -10136,7 +10162,7 @@
       <c r="Z314" s="3"/>
       <c r="AA314" s="3"/>
     </row>
-    <row r="315">
+    <row r="315" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -10165,7 +10191,7 @@
       <c r="Z315" s="3"/>
       <c r="AA315" s="3"/>
     </row>
-    <row r="316">
+    <row r="316" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -10194,7 +10220,7 @@
       <c r="Z316" s="3"/>
       <c r="AA316" s="3"/>
     </row>
-    <row r="317">
+    <row r="317" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -10223,7 +10249,7 @@
       <c r="Z317" s="3"/>
       <c r="AA317" s="3"/>
     </row>
-    <row r="318">
+    <row r="318" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -10252,7 +10278,7 @@
       <c r="Z318" s="3"/>
       <c r="AA318" s="3"/>
     </row>
-    <row r="319">
+    <row r="319" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -10281,7 +10307,7 @@
       <c r="Z319" s="3"/>
       <c r="AA319" s="3"/>
     </row>
-    <row r="320">
+    <row r="320" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -10310,7 +10336,7 @@
       <c r="Z320" s="3"/>
       <c r="AA320" s="3"/>
     </row>
-    <row r="321">
+    <row r="321" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -10339,7 +10365,7 @@
       <c r="Z321" s="3"/>
       <c r="AA321" s="3"/>
     </row>
-    <row r="322">
+    <row r="322" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -10368,7 +10394,7 @@
       <c r="Z322" s="3"/>
       <c r="AA322" s="3"/>
     </row>
-    <row r="323">
+    <row r="323" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -10397,7 +10423,7 @@
       <c r="Z323" s="3"/>
       <c r="AA323" s="3"/>
     </row>
-    <row r="324">
+    <row r="324" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -10426,7 +10452,7 @@
       <c r="Z324" s="3"/>
       <c r="AA324" s="3"/>
     </row>
-    <row r="325">
+    <row r="325" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -10455,7 +10481,7 @@
       <c r="Z325" s="3"/>
       <c r="AA325" s="3"/>
     </row>
-    <row r="326">
+    <row r="326" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -10484,7 +10510,7 @@
       <c r="Z326" s="3"/>
       <c r="AA326" s="3"/>
     </row>
-    <row r="327">
+    <row r="327" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -10513,7 +10539,7 @@
       <c r="Z327" s="3"/>
       <c r="AA327" s="3"/>
     </row>
-    <row r="328">
+    <row r="328" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -10542,7 +10568,7 @@
       <c r="Z328" s="3"/>
       <c r="AA328" s="3"/>
     </row>
-    <row r="329">
+    <row r="329" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -10571,7 +10597,7 @@
       <c r="Z329" s="3"/>
       <c r="AA329" s="3"/>
     </row>
-    <row r="330">
+    <row r="330" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -10600,7 +10626,7 @@
       <c r="Z330" s="3"/>
       <c r="AA330" s="3"/>
     </row>
-    <row r="331">
+    <row r="331" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -10629,7 +10655,7 @@
       <c r="Z331" s="3"/>
       <c r="AA331" s="3"/>
     </row>
-    <row r="332">
+    <row r="332" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -10658,7 +10684,7 @@
       <c r="Z332" s="3"/>
       <c r="AA332" s="3"/>
     </row>
-    <row r="333">
+    <row r="333" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -10687,7 +10713,7 @@
       <c r="Z333" s="3"/>
       <c r="AA333" s="3"/>
     </row>
-    <row r="334">
+    <row r="334" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -10716,7 +10742,7 @@
       <c r="Z334" s="3"/>
       <c r="AA334" s="3"/>
     </row>
-    <row r="335">
+    <row r="335" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -10745,7 +10771,7 @@
       <c r="Z335" s="3"/>
       <c r="AA335" s="3"/>
     </row>
-    <row r="336">
+    <row r="336" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -10774,7 +10800,7 @@
       <c r="Z336" s="3"/>
       <c r="AA336" s="3"/>
     </row>
-    <row r="337">
+    <row r="337" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -10803,7 +10829,7 @@
       <c r="Z337" s="3"/>
       <c r="AA337" s="3"/>
     </row>
-    <row r="338">
+    <row r="338" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -10832,7 +10858,7 @@
       <c r="Z338" s="3"/>
       <c r="AA338" s="3"/>
     </row>
-    <row r="339">
+    <row r="339" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -10861,7 +10887,7 @@
       <c r="Z339" s="3"/>
       <c r="AA339" s="3"/>
     </row>
-    <row r="340">
+    <row r="340" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -10890,7 +10916,7 @@
       <c r="Z340" s="3"/>
       <c r="AA340" s="3"/>
     </row>
-    <row r="341">
+    <row r="341" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -10919,7 +10945,7 @@
       <c r="Z341" s="3"/>
       <c r="AA341" s="3"/>
     </row>
-    <row r="342">
+    <row r="342" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -10948,7 +10974,7 @@
       <c r="Z342" s="3"/>
       <c r="AA342" s="3"/>
     </row>
-    <row r="343">
+    <row r="343" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -10977,7 +11003,7 @@
       <c r="Z343" s="3"/>
       <c r="AA343" s="3"/>
     </row>
-    <row r="344">
+    <row r="344" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -11006,7 +11032,7 @@
       <c r="Z344" s="3"/>
       <c r="AA344" s="3"/>
     </row>
-    <row r="345">
+    <row r="345" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -11035,7 +11061,7 @@
       <c r="Z345" s="3"/>
       <c r="AA345" s="3"/>
     </row>
-    <row r="346">
+    <row r="346" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -11064,7 +11090,7 @@
       <c r="Z346" s="3"/>
       <c r="AA346" s="3"/>
     </row>
-    <row r="347">
+    <row r="347" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -11093,7 +11119,7 @@
       <c r="Z347" s="3"/>
       <c r="AA347" s="3"/>
     </row>
-    <row r="348">
+    <row r="348" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -11122,7 +11148,7 @@
       <c r="Z348" s="3"/>
       <c r="AA348" s="3"/>
     </row>
-    <row r="349">
+    <row r="349" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -11151,7 +11177,7 @@
       <c r="Z349" s="3"/>
       <c r="AA349" s="3"/>
     </row>
-    <row r="350">
+    <row r="350" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -11180,7 +11206,7 @@
       <c r="Z350" s="3"/>
       <c r="AA350" s="3"/>
     </row>
-    <row r="351">
+    <row r="351" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -11209,7 +11235,7 @@
       <c r="Z351" s="3"/>
       <c r="AA351" s="3"/>
     </row>
-    <row r="352">
+    <row r="352" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -11238,7 +11264,7 @@
       <c r="Z352" s="3"/>
       <c r="AA352" s="3"/>
     </row>
-    <row r="353">
+    <row r="353" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -11267,7 +11293,7 @@
       <c r="Z353" s="3"/>
       <c r="AA353" s="3"/>
     </row>
-    <row r="354">
+    <row r="354" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -11296,7 +11322,7 @@
       <c r="Z354" s="3"/>
       <c r="AA354" s="3"/>
     </row>
-    <row r="355">
+    <row r="355" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -11325,7 +11351,7 @@
       <c r="Z355" s="3"/>
       <c r="AA355" s="3"/>
     </row>
-    <row r="356">
+    <row r="356" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -11354,7 +11380,7 @@
       <c r="Z356" s="3"/>
       <c r="AA356" s="3"/>
     </row>
-    <row r="357">
+    <row r="357" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -11383,7 +11409,7 @@
       <c r="Z357" s="3"/>
       <c r="AA357" s="3"/>
     </row>
-    <row r="358">
+    <row r="358" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -11412,7 +11438,7 @@
       <c r="Z358" s="3"/>
       <c r="AA358" s="3"/>
     </row>
-    <row r="359">
+    <row r="359" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -11441,7 +11467,7 @@
       <c r="Z359" s="3"/>
       <c r="AA359" s="3"/>
     </row>
-    <row r="360">
+    <row r="360" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -11470,7 +11496,7 @@
       <c r="Z360" s="3"/>
       <c r="AA360" s="3"/>
     </row>
-    <row r="361">
+    <row r="361" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -11499,7 +11525,7 @@
       <c r="Z361" s="3"/>
       <c r="AA361" s="3"/>
     </row>
-    <row r="362">
+    <row r="362" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -11528,7 +11554,7 @@
       <c r="Z362" s="3"/>
       <c r="AA362" s="3"/>
     </row>
-    <row r="363">
+    <row r="363" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -11557,7 +11583,7 @@
       <c r="Z363" s="3"/>
       <c r="AA363" s="3"/>
     </row>
-    <row r="364">
+    <row r="364" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -11586,7 +11612,7 @@
       <c r="Z364" s="3"/>
       <c r="AA364" s="3"/>
     </row>
-    <row r="365">
+    <row r="365" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -11615,7 +11641,7 @@
       <c r="Z365" s="3"/>
       <c r="AA365" s="3"/>
     </row>
-    <row r="366">
+    <row r="366" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -11644,7 +11670,7 @@
       <c r="Z366" s="3"/>
       <c r="AA366" s="3"/>
     </row>
-    <row r="367">
+    <row r="367" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -11673,7 +11699,7 @@
       <c r="Z367" s="3"/>
       <c r="AA367" s="3"/>
     </row>
-    <row r="368">
+    <row r="368" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -11702,7 +11728,7 @@
       <c r="Z368" s="3"/>
       <c r="AA368" s="3"/>
     </row>
-    <row r="369">
+    <row r="369" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -11731,7 +11757,7 @@
       <c r="Z369" s="3"/>
       <c r="AA369" s="3"/>
     </row>
-    <row r="370">
+    <row r="370" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -11760,7 +11786,7 @@
       <c r="Z370" s="3"/>
       <c r="AA370" s="3"/>
     </row>
-    <row r="371">
+    <row r="371" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -11789,7 +11815,7 @@
       <c r="Z371" s="3"/>
       <c r="AA371" s="3"/>
     </row>
-    <row r="372">
+    <row r="372" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -11818,7 +11844,7 @@
       <c r="Z372" s="3"/>
       <c r="AA372" s="3"/>
     </row>
-    <row r="373">
+    <row r="373" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -11847,7 +11873,7 @@
       <c r="Z373" s="3"/>
       <c r="AA373" s="3"/>
     </row>
-    <row r="374">
+    <row r="374" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -11876,7 +11902,7 @@
       <c r="Z374" s="3"/>
       <c r="AA374" s="3"/>
     </row>
-    <row r="375">
+    <row r="375" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -11905,7 +11931,7 @@
       <c r="Z375" s="3"/>
       <c r="AA375" s="3"/>
     </row>
-    <row r="376">
+    <row r="376" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -11934,7 +11960,7 @@
       <c r="Z376" s="3"/>
       <c r="AA376" s="3"/>
     </row>
-    <row r="377">
+    <row r="377" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -11963,7 +11989,7 @@
       <c r="Z377" s="3"/>
       <c r="AA377" s="3"/>
     </row>
-    <row r="378">
+    <row r="378" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -11992,7 +12018,7 @@
       <c r="Z378" s="3"/>
       <c r="AA378" s="3"/>
     </row>
-    <row r="379">
+    <row r="379" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -12021,7 +12047,7 @@
       <c r="Z379" s="3"/>
       <c r="AA379" s="3"/>
     </row>
-    <row r="380">
+    <row r="380" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -12050,7 +12076,7 @@
       <c r="Z380" s="3"/>
       <c r="AA380" s="3"/>
     </row>
-    <row r="381">
+    <row r="381" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -12079,7 +12105,7 @@
       <c r="Z381" s="3"/>
       <c r="AA381" s="3"/>
     </row>
-    <row r="382">
+    <row r="382" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -12108,7 +12134,7 @@
       <c r="Z382" s="3"/>
       <c r="AA382" s="3"/>
     </row>
-    <row r="383">
+    <row r="383" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -12137,7 +12163,7 @@
       <c r="Z383" s="3"/>
       <c r="AA383" s="3"/>
     </row>
-    <row r="384">
+    <row r="384" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -12166,7 +12192,7 @@
       <c r="Z384" s="3"/>
       <c r="AA384" s="3"/>
     </row>
-    <row r="385">
+    <row r="385" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -12195,7 +12221,7 @@
       <c r="Z385" s="3"/>
       <c r="AA385" s="3"/>
     </row>
-    <row r="386">
+    <row r="386" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -12224,7 +12250,7 @@
       <c r="Z386" s="3"/>
       <c r="AA386" s="3"/>
     </row>
-    <row r="387">
+    <row r="387" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -12253,7 +12279,7 @@
       <c r="Z387" s="3"/>
       <c r="AA387" s="3"/>
     </row>
-    <row r="388">
+    <row r="388" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -12282,7 +12308,7 @@
       <c r="Z388" s="3"/>
       <c r="AA388" s="3"/>
     </row>
-    <row r="389">
+    <row r="389" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -12311,7 +12337,7 @@
       <c r="Z389" s="3"/>
       <c r="AA389" s="3"/>
     </row>
-    <row r="390">
+    <row r="390" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -12340,7 +12366,7 @@
       <c r="Z390" s="3"/>
       <c r="AA390" s="3"/>
     </row>
-    <row r="391">
+    <row r="391" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -12369,7 +12395,7 @@
       <c r="Z391" s="3"/>
       <c r="AA391" s="3"/>
     </row>
-    <row r="392">
+    <row r="392" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -12398,7 +12424,7 @@
       <c r="Z392" s="3"/>
       <c r="AA392" s="3"/>
     </row>
-    <row r="393">
+    <row r="393" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -12427,7 +12453,7 @@
       <c r="Z393" s="3"/>
       <c r="AA393" s="3"/>
     </row>
-    <row r="394">
+    <row r="394" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -12456,7 +12482,7 @@
       <c r="Z394" s="3"/>
       <c r="AA394" s="3"/>
     </row>
-    <row r="395">
+    <row r="395" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -12485,7 +12511,7 @@
       <c r="Z395" s="3"/>
       <c r="AA395" s="3"/>
     </row>
-    <row r="396">
+    <row r="396" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -12514,7 +12540,7 @@
       <c r="Z396" s="3"/>
       <c r="AA396" s="3"/>
     </row>
-    <row r="397">
+    <row r="397" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -12543,7 +12569,7 @@
       <c r="Z397" s="3"/>
       <c r="AA397" s="3"/>
     </row>
-    <row r="398">
+    <row r="398" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -12572,7 +12598,7 @@
       <c r="Z398" s="3"/>
       <c r="AA398" s="3"/>
     </row>
-    <row r="399">
+    <row r="399" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -12601,7 +12627,7 @@
       <c r="Z399" s="3"/>
       <c r="AA399" s="3"/>
     </row>
-    <row r="400">
+    <row r="400" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -12630,7 +12656,7 @@
       <c r="Z400" s="3"/>
       <c r="AA400" s="3"/>
     </row>
-    <row r="401">
+    <row r="401" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -12659,7 +12685,7 @@
       <c r="Z401" s="3"/>
       <c r="AA401" s="3"/>
     </row>
-    <row r="402">
+    <row r="402" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -12688,7 +12714,7 @@
       <c r="Z402" s="3"/>
       <c r="AA402" s="3"/>
     </row>
-    <row r="403">
+    <row r="403" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -12717,7 +12743,7 @@
       <c r="Z403" s="3"/>
       <c r="AA403" s="3"/>
     </row>
-    <row r="404">
+    <row r="404" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -12746,7 +12772,7 @@
       <c r="Z404" s="3"/>
       <c r="AA404" s="3"/>
     </row>
-    <row r="405">
+    <row r="405" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -12775,7 +12801,7 @@
       <c r="Z405" s="3"/>
       <c r="AA405" s="3"/>
     </row>
-    <row r="406">
+    <row r="406" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -12804,7 +12830,7 @@
       <c r="Z406" s="3"/>
       <c r="AA406" s="3"/>
     </row>
-    <row r="407">
+    <row r="407" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -12833,7 +12859,7 @@
       <c r="Z407" s="3"/>
       <c r="AA407" s="3"/>
     </row>
-    <row r="408">
+    <row r="408" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -12862,7 +12888,7 @@
       <c r="Z408" s="3"/>
       <c r="AA408" s="3"/>
     </row>
-    <row r="409">
+    <row r="409" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -12891,7 +12917,7 @@
       <c r="Z409" s="3"/>
       <c r="AA409" s="3"/>
     </row>
-    <row r="410">
+    <row r="410" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -12920,7 +12946,7 @@
       <c r="Z410" s="3"/>
       <c r="AA410" s="3"/>
     </row>
-    <row r="411">
+    <row r="411" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -12949,7 +12975,7 @@
       <c r="Z411" s="3"/>
       <c r="AA411" s="3"/>
     </row>
-    <row r="412">
+    <row r="412" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -12978,7 +13004,7 @@
       <c r="Z412" s="3"/>
       <c r="AA412" s="3"/>
     </row>
-    <row r="413">
+    <row r="413" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -13007,7 +13033,7 @@
       <c r="Z413" s="3"/>
       <c r="AA413" s="3"/>
     </row>
-    <row r="414">
+    <row r="414" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -13036,7 +13062,7 @@
       <c r="Z414" s="3"/>
       <c r="AA414" s="3"/>
     </row>
-    <row r="415">
+    <row r="415" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -13065,7 +13091,7 @@
       <c r="Z415" s="3"/>
       <c r="AA415" s="3"/>
     </row>
-    <row r="416">
+    <row r="416" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -13094,7 +13120,7 @@
       <c r="Z416" s="3"/>
       <c r="AA416" s="3"/>
     </row>
-    <row r="417">
+    <row r="417" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -13123,7 +13149,7 @@
       <c r="Z417" s="3"/>
       <c r="AA417" s="3"/>
     </row>
-    <row r="418">
+    <row r="418" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -13152,7 +13178,7 @@
       <c r="Z418" s="3"/>
       <c r="AA418" s="3"/>
     </row>
-    <row r="419">
+    <row r="419" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -13181,7 +13207,7 @@
       <c r="Z419" s="3"/>
       <c r="AA419" s="3"/>
     </row>
-    <row r="420">
+    <row r="420" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -13210,7 +13236,7 @@
       <c r="Z420" s="3"/>
       <c r="AA420" s="3"/>
     </row>
-    <row r="421">
+    <row r="421" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -13239,7 +13265,7 @@
       <c r="Z421" s="3"/>
       <c r="AA421" s="3"/>
     </row>
-    <row r="422">
+    <row r="422" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -13268,7 +13294,7 @@
       <c r="Z422" s="3"/>
       <c r="AA422" s="3"/>
     </row>
-    <row r="423">
+    <row r="423" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -13297,7 +13323,7 @@
       <c r="Z423" s="3"/>
       <c r="AA423" s="3"/>
     </row>
-    <row r="424">
+    <row r="424" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -13326,7 +13352,7 @@
       <c r="Z424" s="3"/>
       <c r="AA424" s="3"/>
     </row>
-    <row r="425">
+    <row r="425" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -13355,7 +13381,7 @@
       <c r="Z425" s="3"/>
       <c r="AA425" s="3"/>
     </row>
-    <row r="426">
+    <row r="426" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -13384,7 +13410,7 @@
       <c r="Z426" s="3"/>
       <c r="AA426" s="3"/>
     </row>
-    <row r="427">
+    <row r="427" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -13413,7 +13439,7 @@
       <c r="Z427" s="3"/>
       <c r="AA427" s="3"/>
     </row>
-    <row r="428">
+    <row r="428" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -13442,7 +13468,7 @@
       <c r="Z428" s="3"/>
       <c r="AA428" s="3"/>
     </row>
-    <row r="429">
+    <row r="429" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -13471,7 +13497,7 @@
       <c r="Z429" s="3"/>
       <c r="AA429" s="3"/>
     </row>
-    <row r="430">
+    <row r="430" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -13500,7 +13526,7 @@
       <c r="Z430" s="3"/>
       <c r="AA430" s="3"/>
     </row>
-    <row r="431">
+    <row r="431" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -13529,7 +13555,7 @@
       <c r="Z431" s="3"/>
       <c r="AA431" s="3"/>
     </row>
-    <row r="432">
+    <row r="432" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -13558,7 +13584,7 @@
       <c r="Z432" s="3"/>
       <c r="AA432" s="3"/>
     </row>
-    <row r="433">
+    <row r="433" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -13587,7 +13613,7 @@
       <c r="Z433" s="3"/>
       <c r="AA433" s="3"/>
     </row>
-    <row r="434">
+    <row r="434" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -13616,7 +13642,7 @@
       <c r="Z434" s="3"/>
       <c r="AA434" s="3"/>
     </row>
-    <row r="435">
+    <row r="435" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -13645,7 +13671,7 @@
       <c r="Z435" s="3"/>
       <c r="AA435" s="3"/>
     </row>
-    <row r="436">
+    <row r="436" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -13674,7 +13700,7 @@
       <c r="Z436" s="3"/>
       <c r="AA436" s="3"/>
     </row>
-    <row r="437">
+    <row r="437" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -13703,7 +13729,7 @@
       <c r="Z437" s="3"/>
       <c r="AA437" s="3"/>
     </row>
-    <row r="438">
+    <row r="438" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -13732,7 +13758,7 @@
       <c r="Z438" s="3"/>
       <c r="AA438" s="3"/>
     </row>
-    <row r="439">
+    <row r="439" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -13761,7 +13787,7 @@
       <c r="Z439" s="3"/>
       <c r="AA439" s="3"/>
     </row>
-    <row r="440">
+    <row r="440" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -13790,7 +13816,7 @@
       <c r="Z440" s="3"/>
       <c r="AA440" s="3"/>
     </row>
-    <row r="441">
+    <row r="441" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -13819,7 +13845,7 @@
       <c r="Z441" s="3"/>
       <c r="AA441" s="3"/>
     </row>
-    <row r="442">
+    <row r="442" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -13848,7 +13874,7 @@
       <c r="Z442" s="3"/>
       <c r="AA442" s="3"/>
     </row>
-    <row r="443">
+    <row r="443" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -13877,7 +13903,7 @@
       <c r="Z443" s="3"/>
       <c r="AA443" s="3"/>
     </row>
-    <row r="444">
+    <row r="444" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -13906,7 +13932,7 @@
       <c r="Z444" s="3"/>
       <c r="AA444" s="3"/>
     </row>
-    <row r="445">
+    <row r="445" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -13935,7 +13961,7 @@
       <c r="Z445" s="3"/>
       <c r="AA445" s="3"/>
     </row>
-    <row r="446">
+    <row r="446" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -13964,7 +13990,7 @@
       <c r="Z446" s="3"/>
       <c r="AA446" s="3"/>
     </row>
-    <row r="447">
+    <row r="447" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -13993,7 +14019,7 @@
       <c r="Z447" s="3"/>
       <c r="AA447" s="3"/>
     </row>
-    <row r="448">
+    <row r="448" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -14022,7 +14048,7 @@
       <c r="Z448" s="3"/>
       <c r="AA448" s="3"/>
     </row>
-    <row r="449">
+    <row r="449" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -14051,7 +14077,7 @@
       <c r="Z449" s="3"/>
       <c r="AA449" s="3"/>
     </row>
-    <row r="450">
+    <row r="450" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -14080,7 +14106,7 @@
       <c r="Z450" s="3"/>
       <c r="AA450" s="3"/>
     </row>
-    <row r="451">
+    <row r="451" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -14109,7 +14135,7 @@
       <c r="Z451" s="3"/>
       <c r="AA451" s="3"/>
     </row>
-    <row r="452">
+    <row r="452" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -14138,7 +14164,7 @@
       <c r="Z452" s="3"/>
       <c r="AA452" s="3"/>
     </row>
-    <row r="453">
+    <row r="453" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -14167,7 +14193,7 @@
       <c r="Z453" s="3"/>
       <c r="AA453" s="3"/>
     </row>
-    <row r="454">
+    <row r="454" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -14196,7 +14222,7 @@
       <c r="Z454" s="3"/>
       <c r="AA454" s="3"/>
     </row>
-    <row r="455">
+    <row r="455" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -14225,7 +14251,7 @@
       <c r="Z455" s="3"/>
       <c r="AA455" s="3"/>
     </row>
-    <row r="456">
+    <row r="456" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -14254,7 +14280,7 @@
       <c r="Z456" s="3"/>
       <c r="AA456" s="3"/>
     </row>
-    <row r="457">
+    <row r="457" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -14283,7 +14309,7 @@
       <c r="Z457" s="3"/>
       <c r="AA457" s="3"/>
     </row>
-    <row r="458">
+    <row r="458" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -14312,7 +14338,7 @@
       <c r="Z458" s="3"/>
       <c r="AA458" s="3"/>
     </row>
-    <row r="459">
+    <row r="459" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -14341,7 +14367,7 @@
       <c r="Z459" s="3"/>
       <c r="AA459" s="3"/>
     </row>
-    <row r="460">
+    <row r="460" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -14370,7 +14396,7 @@
       <c r="Z460" s="3"/>
       <c r="AA460" s="3"/>
     </row>
-    <row r="461">
+    <row r="461" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -14399,7 +14425,7 @@
       <c r="Z461" s="3"/>
       <c r="AA461" s="3"/>
     </row>
-    <row r="462">
+    <row r="462" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -14428,7 +14454,7 @@
       <c r="Z462" s="3"/>
       <c r="AA462" s="3"/>
     </row>
-    <row r="463">
+    <row r="463" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -14457,7 +14483,7 @@
       <c r="Z463" s="3"/>
       <c r="AA463" s="3"/>
     </row>
-    <row r="464">
+    <row r="464" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -14486,7 +14512,7 @@
       <c r="Z464" s="3"/>
       <c r="AA464" s="3"/>
     </row>
-    <row r="465">
+    <row r="465" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -14515,7 +14541,7 @@
       <c r="Z465" s="3"/>
       <c r="AA465" s="3"/>
     </row>
-    <row r="466">
+    <row r="466" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -14544,7 +14570,7 @@
       <c r="Z466" s="3"/>
       <c r="AA466" s="3"/>
     </row>
-    <row r="467">
+    <row r="467" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -14573,7 +14599,7 @@
       <c r="Z467" s="3"/>
       <c r="AA467" s="3"/>
     </row>
-    <row r="468">
+    <row r="468" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -14602,7 +14628,7 @@
       <c r="Z468" s="3"/>
       <c r="AA468" s="3"/>
     </row>
-    <row r="469">
+    <row r="469" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -14631,7 +14657,7 @@
       <c r="Z469" s="3"/>
       <c r="AA469" s="3"/>
     </row>
-    <row r="470">
+    <row r="470" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -14660,7 +14686,7 @@
       <c r="Z470" s="3"/>
       <c r="AA470" s="3"/>
     </row>
-    <row r="471">
+    <row r="471" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -14689,7 +14715,7 @@
       <c r="Z471" s="3"/>
       <c r="AA471" s="3"/>
     </row>
-    <row r="472">
+    <row r="472" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -14718,7 +14744,7 @@
       <c r="Z472" s="3"/>
       <c r="AA472" s="3"/>
     </row>
-    <row r="473">
+    <row r="473" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -14747,7 +14773,7 @@
       <c r="Z473" s="3"/>
       <c r="AA473" s="3"/>
     </row>
-    <row r="474">
+    <row r="474" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -14776,7 +14802,7 @@
       <c r="Z474" s="3"/>
       <c r="AA474" s="3"/>
     </row>
-    <row r="475">
+    <row r="475" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -14805,7 +14831,7 @@
       <c r="Z475" s="3"/>
       <c r="AA475" s="3"/>
     </row>
-    <row r="476">
+    <row r="476" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -14834,7 +14860,7 @@
       <c r="Z476" s="3"/>
       <c r="AA476" s="3"/>
     </row>
-    <row r="477">
+    <row r="477" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -14863,7 +14889,7 @@
       <c r="Z477" s="3"/>
       <c r="AA477" s="3"/>
     </row>
-    <row r="478">
+    <row r="478" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -14892,7 +14918,7 @@
       <c r="Z478" s="3"/>
       <c r="AA478" s="3"/>
     </row>
-    <row r="479">
+    <row r="479" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -14921,7 +14947,7 @@
       <c r="Z479" s="3"/>
       <c r="AA479" s="3"/>
     </row>
-    <row r="480">
+    <row r="480" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -14950,7 +14976,7 @@
       <c r="Z480" s="3"/>
       <c r="AA480" s="3"/>
     </row>
-    <row r="481">
+    <row r="481" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -14979,7 +15005,7 @@
       <c r="Z481" s="3"/>
       <c r="AA481" s="3"/>
     </row>
-    <row r="482">
+    <row r="482" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -15008,7 +15034,7 @@
       <c r="Z482" s="3"/>
       <c r="AA482" s="3"/>
     </row>
-    <row r="483">
+    <row r="483" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -15037,7 +15063,7 @@
       <c r="Z483" s="3"/>
       <c r="AA483" s="3"/>
     </row>
-    <row r="484">
+    <row r="484" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -15066,7 +15092,7 @@
       <c r="Z484" s="3"/>
       <c r="AA484" s="3"/>
     </row>
-    <row r="485">
+    <row r="485" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -15095,7 +15121,7 @@
       <c r="Z485" s="3"/>
       <c r="AA485" s="3"/>
     </row>
-    <row r="486">
+    <row r="486" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -15124,7 +15150,7 @@
       <c r="Z486" s="3"/>
       <c r="AA486" s="3"/>
     </row>
-    <row r="487">
+    <row r="487" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -15153,7 +15179,7 @@
       <c r="Z487" s="3"/>
       <c r="AA487" s="3"/>
     </row>
-    <row r="488">
+    <row r="488" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -15182,7 +15208,7 @@
       <c r="Z488" s="3"/>
       <c r="AA488" s="3"/>
     </row>
-    <row r="489">
+    <row r="489" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -15211,7 +15237,7 @@
       <c r="Z489" s="3"/>
       <c r="AA489" s="3"/>
     </row>
-    <row r="490">
+    <row r="490" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -15240,7 +15266,7 @@
       <c r="Z490" s="3"/>
       <c r="AA490" s="3"/>
     </row>
-    <row r="491">
+    <row r="491" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -15269,7 +15295,7 @@
       <c r="Z491" s="3"/>
       <c r="AA491" s="3"/>
     </row>
-    <row r="492">
+    <row r="492" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -15298,7 +15324,7 @@
       <c r="Z492" s="3"/>
       <c r="AA492" s="3"/>
     </row>
-    <row r="493">
+    <row r="493" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -15327,7 +15353,7 @@
       <c r="Z493" s="3"/>
       <c r="AA493" s="3"/>
     </row>
-    <row r="494">
+    <row r="494" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -15356,7 +15382,7 @@
       <c r="Z494" s="3"/>
       <c r="AA494" s="3"/>
     </row>
-    <row r="495">
+    <row r="495" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -15385,7 +15411,7 @@
       <c r="Z495" s="3"/>
       <c r="AA495" s="3"/>
     </row>
-    <row r="496">
+    <row r="496" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -15414,7 +15440,7 @@
       <c r="Z496" s="3"/>
       <c r="AA496" s="3"/>
     </row>
-    <row r="497">
+    <row r="497" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -15443,7 +15469,7 @@
       <c r="Z497" s="3"/>
       <c r="AA497" s="3"/>
     </row>
-    <row r="498">
+    <row r="498" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -15472,7 +15498,7 @@
       <c r="Z498" s="3"/>
       <c r="AA498" s="3"/>
     </row>
-    <row r="499">
+    <row r="499" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -15501,7 +15527,7 @@
       <c r="Z499" s="3"/>
       <c r="AA499" s="3"/>
     </row>
-    <row r="500">
+    <row r="500" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -15530,7 +15556,7 @@
       <c r="Z500" s="3"/>
       <c r="AA500" s="3"/>
     </row>
-    <row r="501">
+    <row r="501" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -15559,7 +15585,7 @@
       <c r="Z501" s="3"/>
       <c r="AA501" s="3"/>
     </row>
-    <row r="502">
+    <row r="502" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -15588,7 +15614,7 @@
       <c r="Z502" s="3"/>
       <c r="AA502" s="3"/>
     </row>
-    <row r="503">
+    <row r="503" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -15617,7 +15643,7 @@
       <c r="Z503" s="3"/>
       <c r="AA503" s="3"/>
     </row>
-    <row r="504">
+    <row r="504" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -15646,7 +15672,7 @@
       <c r="Z504" s="3"/>
       <c r="AA504" s="3"/>
     </row>
-    <row r="505">
+    <row r="505" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -15675,7 +15701,7 @@
       <c r="Z505" s="3"/>
       <c r="AA505" s="3"/>
     </row>
-    <row r="506">
+    <row r="506" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -15704,7 +15730,7 @@
       <c r="Z506" s="3"/>
       <c r="AA506" s="3"/>
     </row>
-    <row r="507">
+    <row r="507" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -15733,7 +15759,7 @@
       <c r="Z507" s="3"/>
       <c r="AA507" s="3"/>
     </row>
-    <row r="508">
+    <row r="508" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -15762,7 +15788,7 @@
       <c r="Z508" s="3"/>
       <c r="AA508" s="3"/>
     </row>
-    <row r="509">
+    <row r="509" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -15791,7 +15817,7 @@
       <c r="Z509" s="3"/>
       <c r="AA509" s="3"/>
     </row>
-    <row r="510">
+    <row r="510" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -15820,7 +15846,7 @@
       <c r="Z510" s="3"/>
       <c r="AA510" s="3"/>
     </row>
-    <row r="511">
+    <row r="511" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -15849,7 +15875,7 @@
       <c r="Z511" s="3"/>
       <c r="AA511" s="3"/>
     </row>
-    <row r="512">
+    <row r="512" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -15878,7 +15904,7 @@
       <c r="Z512" s="3"/>
       <c r="AA512" s="3"/>
     </row>
-    <row r="513">
+    <row r="513" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -15907,7 +15933,7 @@
       <c r="Z513" s="3"/>
       <c r="AA513" s="3"/>
     </row>
-    <row r="514">
+    <row r="514" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -15936,7 +15962,7 @@
       <c r="Z514" s="3"/>
       <c r="AA514" s="3"/>
     </row>
-    <row r="515">
+    <row r="515" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -15965,7 +15991,7 @@
       <c r="Z515" s="3"/>
       <c r="AA515" s="3"/>
     </row>
-    <row r="516">
+    <row r="516" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -15994,7 +16020,7 @@
       <c r="Z516" s="3"/>
       <c r="AA516" s="3"/>
     </row>
-    <row r="517">
+    <row r="517" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -16023,7 +16049,7 @@
       <c r="Z517" s="3"/>
       <c r="AA517" s="3"/>
     </row>
-    <row r="518">
+    <row r="518" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -16052,7 +16078,7 @@
       <c r="Z518" s="3"/>
       <c r="AA518" s="3"/>
     </row>
-    <row r="519">
+    <row r="519" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -16081,7 +16107,7 @@
       <c r="Z519" s="3"/>
       <c r="AA519" s="3"/>
     </row>
-    <row r="520">
+    <row r="520" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -16110,7 +16136,7 @@
       <c r="Z520" s="3"/>
       <c r="AA520" s="3"/>
     </row>
-    <row r="521">
+    <row r="521" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -16139,7 +16165,7 @@
       <c r="Z521" s="3"/>
       <c r="AA521" s="3"/>
     </row>
-    <row r="522">
+    <row r="522" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -16168,7 +16194,7 @@
       <c r="Z522" s="3"/>
       <c r="AA522" s="3"/>
     </row>
-    <row r="523">
+    <row r="523" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -16197,7 +16223,7 @@
       <c r="Z523" s="3"/>
       <c r="AA523" s="3"/>
     </row>
-    <row r="524">
+    <row r="524" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -16226,7 +16252,7 @@
       <c r="Z524" s="3"/>
       <c r="AA524" s="3"/>
     </row>
-    <row r="525">
+    <row r="525" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -16255,7 +16281,7 @@
       <c r="Z525" s="3"/>
       <c r="AA525" s="3"/>
     </row>
-    <row r="526">
+    <row r="526" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -16284,7 +16310,7 @@
       <c r="Z526" s="3"/>
       <c r="AA526" s="3"/>
     </row>
-    <row r="527">
+    <row r="527" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -16313,7 +16339,7 @@
       <c r="Z527" s="3"/>
       <c r="AA527" s="3"/>
     </row>
-    <row r="528">
+    <row r="528" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -16342,7 +16368,7 @@
       <c r="Z528" s="3"/>
       <c r="AA528" s="3"/>
     </row>
-    <row r="529">
+    <row r="529" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -16371,7 +16397,7 @@
       <c r="Z529" s="3"/>
       <c r="AA529" s="3"/>
     </row>
-    <row r="530">
+    <row r="530" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -16400,7 +16426,7 @@
       <c r="Z530" s="3"/>
       <c r="AA530" s="3"/>
     </row>
-    <row r="531">
+    <row r="531" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -16429,7 +16455,7 @@
       <c r="Z531" s="3"/>
       <c r="AA531" s="3"/>
     </row>
-    <row r="532">
+    <row r="532" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -16458,7 +16484,7 @@
       <c r="Z532" s="3"/>
       <c r="AA532" s="3"/>
     </row>
-    <row r="533">
+    <row r="533" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -16487,7 +16513,7 @@
       <c r="Z533" s="3"/>
       <c r="AA533" s="3"/>
     </row>
-    <row r="534">
+    <row r="534" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -16516,7 +16542,7 @@
       <c r="Z534" s="3"/>
       <c r="AA534" s="3"/>
     </row>
-    <row r="535">
+    <row r="535" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -16545,7 +16571,7 @@
       <c r="Z535" s="3"/>
       <c r="AA535" s="3"/>
     </row>
-    <row r="536">
+    <row r="536" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -16574,7 +16600,7 @@
       <c r="Z536" s="3"/>
       <c r="AA536" s="3"/>
     </row>
-    <row r="537">
+    <row r="537" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -16603,7 +16629,7 @@
       <c r="Z537" s="3"/>
       <c r="AA537" s="3"/>
     </row>
-    <row r="538">
+    <row r="538" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -16632,7 +16658,7 @@
       <c r="Z538" s="3"/>
       <c r="AA538" s="3"/>
     </row>
-    <row r="539">
+    <row r="539" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -16661,7 +16687,7 @@
       <c r="Z539" s="3"/>
       <c r="AA539" s="3"/>
     </row>
-    <row r="540">
+    <row r="540" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -16690,7 +16716,7 @@
       <c r="Z540" s="3"/>
       <c r="AA540" s="3"/>
     </row>
-    <row r="541">
+    <row r="541" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -16719,7 +16745,7 @@
       <c r="Z541" s="3"/>
       <c r="AA541" s="3"/>
     </row>
-    <row r="542">
+    <row r="542" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -16748,7 +16774,7 @@
       <c r="Z542" s="3"/>
       <c r="AA542" s="3"/>
     </row>
-    <row r="543">
+    <row r="543" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -16777,7 +16803,7 @@
       <c r="Z543" s="3"/>
       <c r="AA543" s="3"/>
     </row>
-    <row r="544">
+    <row r="544" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -16806,7 +16832,7 @@
       <c r="Z544" s="3"/>
       <c r="AA544" s="3"/>
     </row>
-    <row r="545">
+    <row r="545" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -16835,7 +16861,7 @@
       <c r="Z545" s="3"/>
       <c r="AA545" s="3"/>
     </row>
-    <row r="546">
+    <row r="546" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -16864,7 +16890,7 @@
       <c r="Z546" s="3"/>
       <c r="AA546" s="3"/>
     </row>
-    <row r="547">
+    <row r="547" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -16893,7 +16919,7 @@
       <c r="Z547" s="3"/>
       <c r="AA547" s="3"/>
     </row>
-    <row r="548">
+    <row r="548" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -16922,7 +16948,7 @@
       <c r="Z548" s="3"/>
       <c r="AA548" s="3"/>
     </row>
-    <row r="549">
+    <row r="549" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -16951,7 +16977,7 @@
       <c r="Z549" s="3"/>
       <c r="AA549" s="3"/>
     </row>
-    <row r="550">
+    <row r="550" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -16980,7 +17006,7 @@
       <c r="Z550" s="3"/>
       <c r="AA550" s="3"/>
     </row>
-    <row r="551">
+    <row r="551" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -17009,7 +17035,7 @@
       <c r="Z551" s="3"/>
       <c r="AA551" s="3"/>
     </row>
-    <row r="552">
+    <row r="552" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -17038,7 +17064,7 @@
       <c r="Z552" s="3"/>
       <c r="AA552" s="3"/>
     </row>
-    <row r="553">
+    <row r="553" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -17067,7 +17093,7 @@
       <c r="Z553" s="3"/>
       <c r="AA553" s="3"/>
     </row>
-    <row r="554">
+    <row r="554" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -17096,7 +17122,7 @@
       <c r="Z554" s="3"/>
       <c r="AA554" s="3"/>
     </row>
-    <row r="555">
+    <row r="555" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -17125,7 +17151,7 @@
       <c r="Z555" s="3"/>
       <c r="AA555" s="3"/>
     </row>
-    <row r="556">
+    <row r="556" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -17154,7 +17180,7 @@
       <c r="Z556" s="3"/>
       <c r="AA556" s="3"/>
     </row>
-    <row r="557">
+    <row r="557" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -17183,7 +17209,7 @@
       <c r="Z557" s="3"/>
       <c r="AA557" s="3"/>
     </row>
-    <row r="558">
+    <row r="558" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -17212,7 +17238,7 @@
       <c r="Z558" s="3"/>
       <c r="AA558" s="3"/>
     </row>
-    <row r="559">
+    <row r="559" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -17241,7 +17267,7 @@
       <c r="Z559" s="3"/>
       <c r="AA559" s="3"/>
     </row>
-    <row r="560">
+    <row r="560" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -17270,7 +17296,7 @@
       <c r="Z560" s="3"/>
       <c r="AA560" s="3"/>
     </row>
-    <row r="561">
+    <row r="561" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -17299,7 +17325,7 @@
       <c r="Z561" s="3"/>
       <c r="AA561" s="3"/>
     </row>
-    <row r="562">
+    <row r="562" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -17328,7 +17354,7 @@
       <c r="Z562" s="3"/>
       <c r="AA562" s="3"/>
     </row>
-    <row r="563">
+    <row r="563" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -17357,7 +17383,7 @@
       <c r="Z563" s="3"/>
       <c r="AA563" s="3"/>
     </row>
-    <row r="564">
+    <row r="564" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -17386,7 +17412,7 @@
       <c r="Z564" s="3"/>
       <c r="AA564" s="3"/>
     </row>
-    <row r="565">
+    <row r="565" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -17415,7 +17441,7 @@
       <c r="Z565" s="3"/>
       <c r="AA565" s="3"/>
     </row>
-    <row r="566">
+    <row r="566" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -17444,7 +17470,7 @@
       <c r="Z566" s="3"/>
       <c r="AA566" s="3"/>
     </row>
-    <row r="567">
+    <row r="567" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -17473,7 +17499,7 @@
       <c r="Z567" s="3"/>
       <c r="AA567" s="3"/>
     </row>
-    <row r="568">
+    <row r="568" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -17502,7 +17528,7 @@
       <c r="Z568" s="3"/>
       <c r="AA568" s="3"/>
     </row>
-    <row r="569">
+    <row r="569" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -17531,7 +17557,7 @@
       <c r="Z569" s="3"/>
       <c r="AA569" s="3"/>
     </row>
-    <row r="570">
+    <row r="570" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -17560,7 +17586,7 @@
       <c r="Z570" s="3"/>
       <c r="AA570" s="3"/>
     </row>
-    <row r="571">
+    <row r="571" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -17589,7 +17615,7 @@
       <c r="Z571" s="3"/>
       <c r="AA571" s="3"/>
     </row>
-    <row r="572">
+    <row r="572" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -17618,7 +17644,7 @@
       <c r="Z572" s="3"/>
       <c r="AA572" s="3"/>
     </row>
-    <row r="573">
+    <row r="573" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -17647,7 +17673,7 @@
       <c r="Z573" s="3"/>
       <c r="AA573" s="3"/>
     </row>
-    <row r="574">
+    <row r="574" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -17676,7 +17702,7 @@
       <c r="Z574" s="3"/>
       <c r="AA574" s="3"/>
     </row>
-    <row r="575">
+    <row r="575" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -17705,7 +17731,7 @@
       <c r="Z575" s="3"/>
       <c r="AA575" s="3"/>
     </row>
-    <row r="576">
+    <row r="576" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -17734,7 +17760,7 @@
       <c r="Z576" s="3"/>
       <c r="AA576" s="3"/>
     </row>
-    <row r="577">
+    <row r="577" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -17763,7 +17789,7 @@
       <c r="Z577" s="3"/>
       <c r="AA577" s="3"/>
     </row>
-    <row r="578">
+    <row r="578" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -17792,7 +17818,7 @@
       <c r="Z578" s="3"/>
       <c r="AA578" s="3"/>
     </row>
-    <row r="579">
+    <row r="579" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -17821,7 +17847,7 @@
       <c r="Z579" s="3"/>
       <c r="AA579" s="3"/>
     </row>
-    <row r="580">
+    <row r="580" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -17850,7 +17876,7 @@
       <c r="Z580" s="3"/>
       <c r="AA580" s="3"/>
     </row>
-    <row r="581">
+    <row r="581" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -17879,7 +17905,7 @@
       <c r="Z581" s="3"/>
       <c r="AA581" s="3"/>
     </row>
-    <row r="582">
+    <row r="582" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -17908,7 +17934,7 @@
       <c r="Z582" s="3"/>
       <c r="AA582" s="3"/>
     </row>
-    <row r="583">
+    <row r="583" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -17937,7 +17963,7 @@
       <c r="Z583" s="3"/>
       <c r="AA583" s="3"/>
     </row>
-    <row r="584">
+    <row r="584" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -17966,7 +17992,7 @@
       <c r="Z584" s="3"/>
       <c r="AA584" s="3"/>
     </row>
-    <row r="585">
+    <row r="585" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -17995,7 +18021,7 @@
       <c r="Z585" s="3"/>
       <c r="AA585" s="3"/>
     </row>
-    <row r="586">
+    <row r="586" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -18024,7 +18050,7 @@
       <c r="Z586" s="3"/>
       <c r="AA586" s="3"/>
     </row>
-    <row r="587">
+    <row r="587" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -18053,7 +18079,7 @@
       <c r="Z587" s="3"/>
       <c r="AA587" s="3"/>
     </row>
-    <row r="588">
+    <row r="588" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -18082,7 +18108,7 @@
       <c r="Z588" s="3"/>
       <c r="AA588" s="3"/>
     </row>
-    <row r="589">
+    <row r="589" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -18111,7 +18137,7 @@
       <c r="Z589" s="3"/>
       <c r="AA589" s="3"/>
     </row>
-    <row r="590">
+    <row r="590" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -18140,7 +18166,7 @@
       <c r="Z590" s="3"/>
       <c r="AA590" s="3"/>
     </row>
-    <row r="591">
+    <row r="591" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -18169,7 +18195,7 @@
       <c r="Z591" s="3"/>
       <c r="AA591" s="3"/>
     </row>
-    <row r="592">
+    <row r="592" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -18198,7 +18224,7 @@
       <c r="Z592" s="3"/>
       <c r="AA592" s="3"/>
     </row>
-    <row r="593">
+    <row r="593" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -18227,7 +18253,7 @@
       <c r="Z593" s="3"/>
       <c r="AA593" s="3"/>
     </row>
-    <row r="594">
+    <row r="594" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -18256,7 +18282,7 @@
       <c r="Z594" s="3"/>
       <c r="AA594" s="3"/>
     </row>
-    <row r="595">
+    <row r="595" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -18285,7 +18311,7 @@
       <c r="Z595" s="3"/>
       <c r="AA595" s="3"/>
     </row>
-    <row r="596">
+    <row r="596" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -18314,7 +18340,7 @@
       <c r="Z596" s="3"/>
       <c r="AA596" s="3"/>
     </row>
-    <row r="597">
+    <row r="597" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -18343,7 +18369,7 @@
       <c r="Z597" s="3"/>
       <c r="AA597" s="3"/>
     </row>
-    <row r="598">
+    <row r="598" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -18372,7 +18398,7 @@
       <c r="Z598" s="3"/>
       <c r="AA598" s="3"/>
     </row>
-    <row r="599">
+    <row r="599" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -18401,7 +18427,7 @@
       <c r="Z599" s="3"/>
       <c r="AA599" s="3"/>
     </row>
-    <row r="600">
+    <row r="600" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -18430,7 +18456,7 @@
       <c r="Z600" s="3"/>
       <c r="AA600" s="3"/>
     </row>
-    <row r="601">
+    <row r="601" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -18459,7 +18485,7 @@
       <c r="Z601" s="3"/>
       <c r="AA601" s="3"/>
     </row>
-    <row r="602">
+    <row r="602" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -18488,7 +18514,7 @@
       <c r="Z602" s="3"/>
       <c r="AA602" s="3"/>
     </row>
-    <row r="603">
+    <row r="603" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -18517,7 +18543,7 @@
       <c r="Z603" s="3"/>
       <c r="AA603" s="3"/>
     </row>
-    <row r="604">
+    <row r="604" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -18546,7 +18572,7 @@
       <c r="Z604" s="3"/>
       <c r="AA604" s="3"/>
     </row>
-    <row r="605">
+    <row r="605" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -18575,7 +18601,7 @@
       <c r="Z605" s="3"/>
       <c r="AA605" s="3"/>
     </row>
-    <row r="606">
+    <row r="606" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -18604,7 +18630,7 @@
       <c r="Z606" s="3"/>
       <c r="AA606" s="3"/>
     </row>
-    <row r="607">
+    <row r="607" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -18633,7 +18659,7 @@
       <c r="Z607" s="3"/>
       <c r="AA607" s="3"/>
     </row>
-    <row r="608">
+    <row r="608" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -18662,7 +18688,7 @@
       <c r="Z608" s="3"/>
       <c r="AA608" s="3"/>
     </row>
-    <row r="609">
+    <row r="609" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -18691,7 +18717,7 @@
       <c r="Z609" s="3"/>
       <c r="AA609" s="3"/>
     </row>
-    <row r="610">
+    <row r="610" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -18720,7 +18746,7 @@
       <c r="Z610" s="3"/>
       <c r="AA610" s="3"/>
     </row>
-    <row r="611">
+    <row r="611" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -18749,7 +18775,7 @@
       <c r="Z611" s="3"/>
       <c r="AA611" s="3"/>
     </row>
-    <row r="612">
+    <row r="612" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -18778,7 +18804,7 @@
       <c r="Z612" s="3"/>
       <c r="AA612" s="3"/>
     </row>
-    <row r="613">
+    <row r="613" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -18807,7 +18833,7 @@
       <c r="Z613" s="3"/>
       <c r="AA613" s="3"/>
     </row>
-    <row r="614">
+    <row r="614" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -18836,7 +18862,7 @@
       <c r="Z614" s="3"/>
       <c r="AA614" s="3"/>
     </row>
-    <row r="615">
+    <row r="615" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -18865,7 +18891,7 @@
       <c r="Z615" s="3"/>
       <c r="AA615" s="3"/>
     </row>
-    <row r="616">
+    <row r="616" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -18894,7 +18920,7 @@
       <c r="Z616" s="3"/>
       <c r="AA616" s="3"/>
     </row>
-    <row r="617">
+    <row r="617" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -18923,7 +18949,7 @@
       <c r="Z617" s="3"/>
       <c r="AA617" s="3"/>
     </row>
-    <row r="618">
+    <row r="618" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -18952,7 +18978,7 @@
       <c r="Z618" s="3"/>
       <c r="AA618" s="3"/>
     </row>
-    <row r="619">
+    <row r="619" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -18981,7 +19007,7 @@
       <c r="Z619" s="3"/>
       <c r="AA619" s="3"/>
     </row>
-    <row r="620">
+    <row r="620" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -19010,7 +19036,7 @@
       <c r="Z620" s="3"/>
       <c r="AA620" s="3"/>
     </row>
-    <row r="621">
+    <row r="621" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -19039,7 +19065,7 @@
       <c r="Z621" s="3"/>
       <c r="AA621" s="3"/>
     </row>
-    <row r="622">
+    <row r="622" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -19068,7 +19094,7 @@
       <c r="Z622" s="3"/>
       <c r="AA622" s="3"/>
     </row>
-    <row r="623">
+    <row r="623" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -19097,7 +19123,7 @@
       <c r="Z623" s="3"/>
       <c r="AA623" s="3"/>
     </row>
-    <row r="624">
+    <row r="624" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -19126,7 +19152,7 @@
       <c r="Z624" s="3"/>
       <c r="AA624" s="3"/>
     </row>
-    <row r="625">
+    <row r="625" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -19155,7 +19181,7 @@
       <c r="Z625" s="3"/>
       <c r="AA625" s="3"/>
     </row>
-    <row r="626">
+    <row r="626" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -19184,7 +19210,7 @@
       <c r="Z626" s="3"/>
       <c r="AA626" s="3"/>
     </row>
-    <row r="627">
+    <row r="627" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -19213,7 +19239,7 @@
       <c r="Z627" s="3"/>
       <c r="AA627" s="3"/>
     </row>
-    <row r="628">
+    <row r="628" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -19242,7 +19268,7 @@
       <c r="Z628" s="3"/>
       <c r="AA628" s="3"/>
     </row>
-    <row r="629">
+    <row r="629" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -19271,7 +19297,7 @@
       <c r="Z629" s="3"/>
       <c r="AA629" s="3"/>
     </row>
-    <row r="630">
+    <row r="630" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -19300,7 +19326,7 @@
       <c r="Z630" s="3"/>
       <c r="AA630" s="3"/>
     </row>
-    <row r="631">
+    <row r="631" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -19329,7 +19355,7 @@
       <c r="Z631" s="3"/>
       <c r="AA631" s="3"/>
     </row>
-    <row r="632">
+    <row r="632" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -19358,7 +19384,7 @@
       <c r="Z632" s="3"/>
       <c r="AA632" s="3"/>
     </row>
-    <row r="633">
+    <row r="633" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -19387,7 +19413,7 @@
       <c r="Z633" s="3"/>
       <c r="AA633" s="3"/>
     </row>
-    <row r="634">
+    <row r="634" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -19416,7 +19442,7 @@
       <c r="Z634" s="3"/>
       <c r="AA634" s="3"/>
     </row>
-    <row r="635">
+    <row r="635" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -19445,7 +19471,7 @@
       <c r="Z635" s="3"/>
       <c r="AA635" s="3"/>
     </row>
-    <row r="636">
+    <row r="636" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -19474,7 +19500,7 @@
       <c r="Z636" s="3"/>
       <c r="AA636" s="3"/>
     </row>
-    <row r="637">
+    <row r="637" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -19503,7 +19529,7 @@
       <c r="Z637" s="3"/>
       <c r="AA637" s="3"/>
     </row>
-    <row r="638">
+    <row r="638" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -19532,7 +19558,7 @@
       <c r="Z638" s="3"/>
       <c r="AA638" s="3"/>
     </row>
-    <row r="639">
+    <row r="639" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -19561,7 +19587,7 @@
       <c r="Z639" s="3"/>
       <c r="AA639" s="3"/>
     </row>
-    <row r="640">
+    <row r="640" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -19590,7 +19616,7 @@
       <c r="Z640" s="3"/>
       <c r="AA640" s="3"/>
     </row>
-    <row r="641">
+    <row r="641" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -19619,7 +19645,7 @@
       <c r="Z641" s="3"/>
       <c r="AA641" s="3"/>
     </row>
-    <row r="642">
+    <row r="642" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -19648,7 +19674,7 @@
       <c r="Z642" s="3"/>
       <c r="AA642" s="3"/>
     </row>
-    <row r="643">
+    <row r="643" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -19677,7 +19703,7 @@
       <c r="Z643" s="3"/>
       <c r="AA643" s="3"/>
     </row>
-    <row r="644">
+    <row r="644" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -19706,7 +19732,7 @@
       <c r="Z644" s="3"/>
       <c r="AA644" s="3"/>
     </row>
-    <row r="645">
+    <row r="645" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -19735,7 +19761,7 @@
       <c r="Z645" s="3"/>
       <c r="AA645" s="3"/>
     </row>
-    <row r="646">
+    <row r="646" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -19764,7 +19790,7 @@
       <c r="Z646" s="3"/>
       <c r="AA646" s="3"/>
     </row>
-    <row r="647">
+    <row r="647" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -19793,7 +19819,7 @@
       <c r="Z647" s="3"/>
       <c r="AA647" s="3"/>
     </row>
-    <row r="648">
+    <row r="648" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -19822,7 +19848,7 @@
       <c r="Z648" s="3"/>
       <c r="AA648" s="3"/>
     </row>
-    <row r="649">
+    <row r="649" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -19851,7 +19877,7 @@
       <c r="Z649" s="3"/>
       <c r="AA649" s="3"/>
     </row>
-    <row r="650">
+    <row r="650" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -19880,7 +19906,7 @@
       <c r="Z650" s="3"/>
       <c r="AA650" s="3"/>
     </row>
-    <row r="651">
+    <row r="651" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -19909,7 +19935,7 @@
       <c r="Z651" s="3"/>
       <c r="AA651" s="3"/>
     </row>
-    <row r="652">
+    <row r="652" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -19938,7 +19964,7 @@
       <c r="Z652" s="3"/>
       <c r="AA652" s="3"/>
     </row>
-    <row r="653">
+    <row r="653" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -19967,7 +19993,7 @@
       <c r="Z653" s="3"/>
       <c r="AA653" s="3"/>
     </row>
-    <row r="654">
+    <row r="654" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -19996,7 +20022,7 @@
       <c r="Z654" s="3"/>
       <c r="AA654" s="3"/>
     </row>
-    <row r="655">
+    <row r="655" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -20025,7 +20051,7 @@
       <c r="Z655" s="3"/>
       <c r="AA655" s="3"/>
     </row>
-    <row r="656">
+    <row r="656" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -20054,7 +20080,7 @@
       <c r="Z656" s="3"/>
       <c r="AA656" s="3"/>
     </row>
-    <row r="657">
+    <row r="657" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -20083,7 +20109,7 @@
       <c r="Z657" s="3"/>
       <c r="AA657" s="3"/>
     </row>
-    <row r="658">
+    <row r="658" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -20112,7 +20138,7 @@
       <c r="Z658" s="3"/>
       <c r="AA658" s="3"/>
     </row>
-    <row r="659">
+    <row r="659" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -20141,7 +20167,7 @@
       <c r="Z659" s="3"/>
       <c r="AA659" s="3"/>
     </row>
-    <row r="660">
+    <row r="660" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -20170,7 +20196,7 @@
       <c r="Z660" s="3"/>
       <c r="AA660" s="3"/>
     </row>
-    <row r="661">
+    <row r="661" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -20199,7 +20225,7 @@
       <c r="Z661" s="3"/>
       <c r="AA661" s="3"/>
     </row>
-    <row r="662">
+    <row r="662" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -20228,7 +20254,7 @@
       <c r="Z662" s="3"/>
       <c r="AA662" s="3"/>
     </row>
-    <row r="663">
+    <row r="663" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -20257,7 +20283,7 @@
       <c r="Z663" s="3"/>
       <c r="AA663" s="3"/>
     </row>
-    <row r="664">
+    <row r="664" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -20286,7 +20312,7 @@
       <c r="Z664" s="3"/>
       <c r="AA664" s="3"/>
     </row>
-    <row r="665">
+    <row r="665" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -20315,7 +20341,7 @@
       <c r="Z665" s="3"/>
       <c r="AA665" s="3"/>
     </row>
-    <row r="666">
+    <row r="666" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -20344,7 +20370,7 @@
       <c r="Z666" s="3"/>
       <c r="AA666" s="3"/>
     </row>
-    <row r="667">
+    <row r="667" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -20373,7 +20399,7 @@
       <c r="Z667" s="3"/>
       <c r="AA667" s="3"/>
     </row>
-    <row r="668">
+    <row r="668" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -20402,7 +20428,7 @@
       <c r="Z668" s="3"/>
       <c r="AA668" s="3"/>
     </row>
-    <row r="669">
+    <row r="669" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -20431,7 +20457,7 @@
       <c r="Z669" s="3"/>
       <c r="AA669" s="3"/>
     </row>
-    <row r="670">
+    <row r="670" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -20460,7 +20486,7 @@
       <c r="Z670" s="3"/>
       <c r="AA670" s="3"/>
     </row>
-    <row r="671">
+    <row r="671" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -20489,7 +20515,7 @@
       <c r="Z671" s="3"/>
       <c r="AA671" s="3"/>
     </row>
-    <row r="672">
+    <row r="672" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -20518,7 +20544,7 @@
       <c r="Z672" s="3"/>
       <c r="AA672" s="3"/>
     </row>
-    <row r="673">
+    <row r="673" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -20547,7 +20573,7 @@
       <c r="Z673" s="3"/>
       <c r="AA673" s="3"/>
     </row>
-    <row r="674">
+    <row r="674" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -20576,7 +20602,7 @@
       <c r="Z674" s="3"/>
       <c r="AA674" s="3"/>
     </row>
-    <row r="675">
+    <row r="675" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -20605,7 +20631,7 @@
       <c r="Z675" s="3"/>
       <c r="AA675" s="3"/>
     </row>
-    <row r="676">
+    <row r="676" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -20634,7 +20660,7 @@
       <c r="Z676" s="3"/>
       <c r="AA676" s="3"/>
     </row>
-    <row r="677">
+    <row r="677" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -20663,7 +20689,7 @@
       <c r="Z677" s="3"/>
       <c r="AA677" s="3"/>
     </row>
-    <row r="678">
+    <row r="678" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -20692,7 +20718,7 @@
       <c r="Z678" s="3"/>
       <c r="AA678" s="3"/>
     </row>
-    <row r="679">
+    <row r="679" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -20721,7 +20747,7 @@
       <c r="Z679" s="3"/>
       <c r="AA679" s="3"/>
     </row>
-    <row r="680">
+    <row r="680" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -20750,7 +20776,7 @@
       <c r="Z680" s="3"/>
       <c r="AA680" s="3"/>
     </row>
-    <row r="681">
+    <row r="681" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -20779,7 +20805,7 @@
       <c r="Z681" s="3"/>
       <c r="AA681" s="3"/>
     </row>
-    <row r="682">
+    <row r="682" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -20808,7 +20834,7 @@
       <c r="Z682" s="3"/>
       <c r="AA682" s="3"/>
     </row>
-    <row r="683">
+    <row r="683" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -20837,7 +20863,7 @@
       <c r="Z683" s="3"/>
       <c r="AA683" s="3"/>
     </row>
-    <row r="684">
+    <row r="684" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -20866,7 +20892,7 @@
       <c r="Z684" s="3"/>
       <c r="AA684" s="3"/>
     </row>
-    <row r="685">
+    <row r="685" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -20895,7 +20921,7 @@
       <c r="Z685" s="3"/>
       <c r="AA685" s="3"/>
     </row>
-    <row r="686">
+    <row r="686" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -20924,7 +20950,7 @@
       <c r="Z686" s="3"/>
       <c r="AA686" s="3"/>
     </row>
-    <row r="687">
+    <row r="687" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -20953,7 +20979,7 @@
       <c r="Z687" s="3"/>
       <c r="AA687" s="3"/>
     </row>
-    <row r="688">
+    <row r="688" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -20982,7 +21008,7 @@
       <c r="Z688" s="3"/>
       <c r="AA688" s="3"/>
     </row>
-    <row r="689">
+    <row r="689" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -21011,7 +21037,7 @@
       <c r="Z689" s="3"/>
       <c r="AA689" s="3"/>
     </row>
-    <row r="690">
+    <row r="690" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -21040,7 +21066,7 @@
       <c r="Z690" s="3"/>
       <c r="AA690" s="3"/>
     </row>
-    <row r="691">
+    <row r="691" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -21069,7 +21095,7 @@
       <c r="Z691" s="3"/>
       <c r="AA691" s="3"/>
     </row>
-    <row r="692">
+    <row r="692" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -21098,7 +21124,7 @@
       <c r="Z692" s="3"/>
       <c r="AA692" s="3"/>
     </row>
-    <row r="693">
+    <row r="693" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -21127,7 +21153,7 @@
       <c r="Z693" s="3"/>
       <c r="AA693" s="3"/>
     </row>
-    <row r="694">
+    <row r="694" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -21156,7 +21182,7 @@
       <c r="Z694" s="3"/>
       <c r="AA694" s="3"/>
     </row>
-    <row r="695">
+    <row r="695" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -21185,7 +21211,7 @@
       <c r="Z695" s="3"/>
       <c r="AA695" s="3"/>
     </row>
-    <row r="696">
+    <row r="696" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -21214,7 +21240,7 @@
       <c r="Z696" s="3"/>
       <c r="AA696" s="3"/>
     </row>
-    <row r="697">
+    <row r="697" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -21243,7 +21269,7 @@
       <c r="Z697" s="3"/>
       <c r="AA697" s="3"/>
     </row>
-    <row r="698">
+    <row r="698" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -21272,7 +21298,7 @@
       <c r="Z698" s="3"/>
       <c r="AA698" s="3"/>
     </row>
-    <row r="699">
+    <row r="699" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -21301,7 +21327,7 @@
       <c r="Z699" s="3"/>
       <c r="AA699" s="3"/>
     </row>
-    <row r="700">
+    <row r="700" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -21330,7 +21356,7 @@
       <c r="Z700" s="3"/>
       <c r="AA700" s="3"/>
     </row>
-    <row r="701">
+    <row r="701" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -21359,7 +21385,7 @@
       <c r="Z701" s="3"/>
       <c r="AA701" s="3"/>
     </row>
-    <row r="702">
+    <row r="702" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -21388,7 +21414,7 @@
       <c r="Z702" s="3"/>
       <c r="AA702" s="3"/>
     </row>
-    <row r="703">
+    <row r="703" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -21417,7 +21443,7 @@
       <c r="Z703" s="3"/>
       <c r="AA703" s="3"/>
     </row>
-    <row r="704">
+    <row r="704" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -21446,7 +21472,7 @@
       <c r="Z704" s="3"/>
       <c r="AA704" s="3"/>
     </row>
-    <row r="705">
+    <row r="705" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -21475,7 +21501,7 @@
       <c r="Z705" s="3"/>
       <c r="AA705" s="3"/>
     </row>
-    <row r="706">
+    <row r="706" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -21504,7 +21530,7 @@
       <c r="Z706" s="3"/>
       <c r="AA706" s="3"/>
     </row>
-    <row r="707">
+    <row r="707" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -21533,7 +21559,7 @@
       <c r="Z707" s="3"/>
       <c r="AA707" s="3"/>
     </row>
-    <row r="708">
+    <row r="708" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -21562,7 +21588,7 @@
       <c r="Z708" s="3"/>
       <c r="AA708" s="3"/>
     </row>
-    <row r="709">
+    <row r="709" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -21591,7 +21617,7 @@
       <c r="Z709" s="3"/>
       <c r="AA709" s="3"/>
     </row>
-    <row r="710">
+    <row r="710" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -21620,7 +21646,7 @@
       <c r="Z710" s="3"/>
       <c r="AA710" s="3"/>
     </row>
-    <row r="711">
+    <row r="711" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -21649,7 +21675,7 @@
       <c r="Z711" s="3"/>
       <c r="AA711" s="3"/>
     </row>
-    <row r="712">
+    <row r="712" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -21678,7 +21704,7 @@
       <c r="Z712" s="3"/>
       <c r="AA712" s="3"/>
     </row>
-    <row r="713">
+    <row r="713" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -21707,7 +21733,7 @@
       <c r="Z713" s="3"/>
       <c r="AA713" s="3"/>
     </row>
-    <row r="714">
+    <row r="714" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -21736,7 +21762,7 @@
       <c r="Z714" s="3"/>
       <c r="AA714" s="3"/>
     </row>
-    <row r="715">
+    <row r="715" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -21765,7 +21791,7 @@
       <c r="Z715" s="3"/>
       <c r="AA715" s="3"/>
     </row>
-    <row r="716">
+    <row r="716" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -21794,7 +21820,7 @@
       <c r="Z716" s="3"/>
       <c r="AA716" s="3"/>
     </row>
-    <row r="717">
+    <row r="717" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -21823,7 +21849,7 @@
       <c r="Z717" s="3"/>
       <c r="AA717" s="3"/>
     </row>
-    <row r="718">
+    <row r="718" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -21852,7 +21878,7 @@
       <c r="Z718" s="3"/>
       <c r="AA718" s="3"/>
     </row>
-    <row r="719">
+    <row r="719" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -21881,7 +21907,7 @@
       <c r="Z719" s="3"/>
       <c r="AA719" s="3"/>
     </row>
-    <row r="720">
+    <row r="720" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -21910,7 +21936,7 @@
       <c r="Z720" s="3"/>
       <c r="AA720" s="3"/>
     </row>
-    <row r="721">
+    <row r="721" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -21939,7 +21965,7 @@
       <c r="Z721" s="3"/>
       <c r="AA721" s="3"/>
     </row>
-    <row r="722">
+    <row r="722" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -21968,7 +21994,7 @@
       <c r="Z722" s="3"/>
       <c r="AA722" s="3"/>
     </row>
-    <row r="723">
+    <row r="723" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -21997,7 +22023,7 @@
       <c r="Z723" s="3"/>
       <c r="AA723" s="3"/>
     </row>
-    <row r="724">
+    <row r="724" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -22026,7 +22052,7 @@
       <c r="Z724" s="3"/>
       <c r="AA724" s="3"/>
     </row>
-    <row r="725">
+    <row r="725" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -22055,7 +22081,7 @@
       <c r="Z725" s="3"/>
       <c r="AA725" s="3"/>
     </row>
-    <row r="726">
+    <row r="726" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -22084,7 +22110,7 @@
       <c r="Z726" s="3"/>
       <c r="AA726" s="3"/>
     </row>
-    <row r="727">
+    <row r="727" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -22113,7 +22139,7 @@
       <c r="Z727" s="3"/>
       <c r="AA727" s="3"/>
     </row>
-    <row r="728">
+    <row r="728" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -22142,7 +22168,7 @@
       <c r="Z728" s="3"/>
       <c r="AA728" s="3"/>
     </row>
-    <row r="729">
+    <row r="729" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -22171,7 +22197,7 @@
       <c r="Z729" s="3"/>
       <c r="AA729" s="3"/>
     </row>
-    <row r="730">
+    <row r="730" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -22200,7 +22226,7 @@
       <c r="Z730" s="3"/>
       <c r="AA730" s="3"/>
     </row>
-    <row r="731">
+    <row r="731" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -22229,7 +22255,7 @@
       <c r="Z731" s="3"/>
       <c r="AA731" s="3"/>
     </row>
-    <row r="732">
+    <row r="732" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -22258,7 +22284,7 @@
       <c r="Z732" s="3"/>
       <c r="AA732" s="3"/>
     </row>
-    <row r="733">
+    <row r="733" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -22287,7 +22313,7 @@
       <c r="Z733" s="3"/>
       <c r="AA733" s="3"/>
     </row>
-    <row r="734">
+    <row r="734" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -22316,7 +22342,7 @@
       <c r="Z734" s="3"/>
       <c r="AA734" s="3"/>
     </row>
-    <row r="735">
+    <row r="735" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -22345,7 +22371,7 @@
       <c r="Z735" s="3"/>
       <c r="AA735" s="3"/>
     </row>
-    <row r="736">
+    <row r="736" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -22374,7 +22400,7 @@
       <c r="Z736" s="3"/>
       <c r="AA736" s="3"/>
     </row>
-    <row r="737">
+    <row r="737" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -22403,7 +22429,7 @@
       <c r="Z737" s="3"/>
       <c r="AA737" s="3"/>
     </row>
-    <row r="738">
+    <row r="738" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -22432,7 +22458,7 @@
       <c r="Z738" s="3"/>
       <c r="AA738" s="3"/>
     </row>
-    <row r="739">
+    <row r="739" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -22461,7 +22487,7 @@
       <c r="Z739" s="3"/>
       <c r="AA739" s="3"/>
     </row>
-    <row r="740">
+    <row r="740" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -22490,7 +22516,7 @@
       <c r="Z740" s="3"/>
       <c r="AA740" s="3"/>
     </row>
-    <row r="741">
+    <row r="741" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -22519,7 +22545,7 @@
       <c r="Z741" s="3"/>
       <c r="AA741" s="3"/>
     </row>
-    <row r="742">
+    <row r="742" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -22548,7 +22574,7 @@
       <c r="Z742" s="3"/>
       <c r="AA742" s="3"/>
     </row>
-    <row r="743">
+    <row r="743" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -22577,7 +22603,7 @@
       <c r="Z743" s="3"/>
       <c r="AA743" s="3"/>
     </row>
-    <row r="744">
+    <row r="744" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -22606,7 +22632,7 @@
       <c r="Z744" s="3"/>
       <c r="AA744" s="3"/>
     </row>
-    <row r="745">
+    <row r="745" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -22635,7 +22661,7 @@
       <c r="Z745" s="3"/>
       <c r="AA745" s="3"/>
     </row>
-    <row r="746">
+    <row r="746" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -22664,7 +22690,7 @@
       <c r="Z746" s="3"/>
       <c r="AA746" s="3"/>
     </row>
-    <row r="747">
+    <row r="747" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -22693,7 +22719,7 @@
       <c r="Z747" s="3"/>
       <c r="AA747" s="3"/>
     </row>
-    <row r="748">
+    <row r="748" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -22722,7 +22748,7 @@
       <c r="Z748" s="3"/>
       <c r="AA748" s="3"/>
     </row>
-    <row r="749">
+    <row r="749" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -22751,7 +22777,7 @@
       <c r="Z749" s="3"/>
       <c r="AA749" s="3"/>
     </row>
-    <row r="750">
+    <row r="750" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -22780,7 +22806,7 @@
       <c r="Z750" s="3"/>
       <c r="AA750" s="3"/>
     </row>
-    <row r="751">
+    <row r="751" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -22809,7 +22835,7 @@
       <c r="Z751" s="3"/>
       <c r="AA751" s="3"/>
     </row>
-    <row r="752">
+    <row r="752" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -22838,7 +22864,7 @@
       <c r="Z752" s="3"/>
       <c r="AA752" s="3"/>
     </row>
-    <row r="753">
+    <row r="753" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -22867,7 +22893,7 @@
       <c r="Z753" s="3"/>
       <c r="AA753" s="3"/>
     </row>
-    <row r="754">
+    <row r="754" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -22896,7 +22922,7 @@
       <c r="Z754" s="3"/>
       <c r="AA754" s="3"/>
     </row>
-    <row r="755">
+    <row r="755" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -22925,7 +22951,7 @@
       <c r="Z755" s="3"/>
       <c r="AA755" s="3"/>
     </row>
-    <row r="756">
+    <row r="756" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -22954,7 +22980,7 @@
       <c r="Z756" s="3"/>
       <c r="AA756" s="3"/>
     </row>
-    <row r="757">
+    <row r="757" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -22983,7 +23009,7 @@
       <c r="Z757" s="3"/>
       <c r="AA757" s="3"/>
     </row>
-    <row r="758">
+    <row r="758" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -23012,7 +23038,7 @@
       <c r="Z758" s="3"/>
       <c r="AA758" s="3"/>
     </row>
-    <row r="759">
+    <row r="759" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -23041,7 +23067,7 @@
       <c r="Z759" s="3"/>
       <c r="AA759" s="3"/>
     </row>
-    <row r="760">
+    <row r="760" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -23070,7 +23096,7 @@
       <c r="Z760" s="3"/>
       <c r="AA760" s="3"/>
     </row>
-    <row r="761">
+    <row r="761" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -23099,7 +23125,7 @@
       <c r="Z761" s="3"/>
       <c r="AA761" s="3"/>
     </row>
-    <row r="762">
+    <row r="762" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -23128,7 +23154,7 @@
       <c r="Z762" s="3"/>
       <c r="AA762" s="3"/>
     </row>
-    <row r="763">
+    <row r="763" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -23157,7 +23183,7 @@
       <c r="Z763" s="3"/>
       <c r="AA763" s="3"/>
     </row>
-    <row r="764">
+    <row r="764" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -23186,7 +23212,7 @@
       <c r="Z764" s="3"/>
       <c r="AA764" s="3"/>
     </row>
-    <row r="765">
+    <row r="765" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -23215,7 +23241,7 @@
       <c r="Z765" s="3"/>
       <c r="AA765" s="3"/>
     </row>
-    <row r="766">
+    <row r="766" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -23244,7 +23270,7 @@
       <c r="Z766" s="3"/>
       <c r="AA766" s="3"/>
     </row>
-    <row r="767">
+    <row r="767" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -23273,7 +23299,7 @@
       <c r="Z767" s="3"/>
       <c r="AA767" s="3"/>
     </row>
-    <row r="768">
+    <row r="768" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -23302,7 +23328,7 @@
       <c r="Z768" s="3"/>
       <c r="AA768" s="3"/>
     </row>
-    <row r="769">
+    <row r="769" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -23331,7 +23357,7 @@
       <c r="Z769" s="3"/>
       <c r="AA769" s="3"/>
     </row>
-    <row r="770">
+    <row r="770" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -23360,7 +23386,7 @@
       <c r="Z770" s="3"/>
       <c r="AA770" s="3"/>
     </row>
-    <row r="771">
+    <row r="771" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -23389,7 +23415,7 @@
       <c r="Z771" s="3"/>
       <c r="AA771" s="3"/>
     </row>
-    <row r="772">
+    <row r="772" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -23418,7 +23444,7 @@
       <c r="Z772" s="3"/>
       <c r="AA772" s="3"/>
     </row>
-    <row r="773">
+    <row r="773" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -23447,7 +23473,7 @@
       <c r="Z773" s="3"/>
       <c r="AA773" s="3"/>
     </row>
-    <row r="774">
+    <row r="774" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -23476,7 +23502,7 @@
       <c r="Z774" s="3"/>
       <c r="AA774" s="3"/>
     </row>
-    <row r="775">
+    <row r="775" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -23505,7 +23531,7 @@
       <c r="Z775" s="3"/>
       <c r="AA775" s="3"/>
     </row>
-    <row r="776">
+    <row r="776" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -23534,7 +23560,7 @@
       <c r="Z776" s="3"/>
       <c r="AA776" s="3"/>
     </row>
-    <row r="777">
+    <row r="777" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -23563,7 +23589,7 @@
       <c r="Z777" s="3"/>
       <c r="AA777" s="3"/>
     </row>
-    <row r="778">
+    <row r="778" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -23592,7 +23618,7 @@
       <c r="Z778" s="3"/>
       <c r="AA778" s="3"/>
     </row>
-    <row r="779">
+    <row r="779" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -23621,7 +23647,7 @@
       <c r="Z779" s="3"/>
       <c r="AA779" s="3"/>
     </row>
-    <row r="780">
+    <row r="780" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -23650,7 +23676,7 @@
       <c r="Z780" s="3"/>
       <c r="AA780" s="3"/>
     </row>
-    <row r="781">
+    <row r="781" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -23679,7 +23705,7 @@
       <c r="Z781" s="3"/>
       <c r="AA781" s="3"/>
     </row>
-    <row r="782">
+    <row r="782" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -23708,7 +23734,7 @@
       <c r="Z782" s="3"/>
       <c r="AA782" s="3"/>
     </row>
-    <row r="783">
+    <row r="783" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -23737,7 +23763,7 @@
       <c r="Z783" s="3"/>
       <c r="AA783" s="3"/>
     </row>
-    <row r="784">
+    <row r="784" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -23766,7 +23792,7 @@
       <c r="Z784" s="3"/>
       <c r="AA784" s="3"/>
     </row>
-    <row r="785">
+    <row r="785" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -23795,7 +23821,7 @@
       <c r="Z785" s="3"/>
       <c r="AA785" s="3"/>
     </row>
-    <row r="786">
+    <row r="786" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -23824,7 +23850,7 @@
       <c r="Z786" s="3"/>
       <c r="AA786" s="3"/>
     </row>
-    <row r="787">
+    <row r="787" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -23853,7 +23879,7 @@
       <c r="Z787" s="3"/>
       <c r="AA787" s="3"/>
     </row>
-    <row r="788">
+    <row r="788" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -23882,7 +23908,7 @@
       <c r="Z788" s="3"/>
       <c r="AA788" s="3"/>
     </row>
-    <row r="789">
+    <row r="789" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -23911,7 +23937,7 @@
       <c r="Z789" s="3"/>
       <c r="AA789" s="3"/>
     </row>
-    <row r="790">
+    <row r="790" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -23940,7 +23966,7 @@
       <c r="Z790" s="3"/>
       <c r="AA790" s="3"/>
     </row>
-    <row r="791">
+    <row r="791" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -23969,7 +23995,7 @@
       <c r="Z791" s="3"/>
       <c r="AA791" s="3"/>
     </row>
-    <row r="792">
+    <row r="792" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -23998,7 +24024,7 @@
       <c r="Z792" s="3"/>
       <c r="AA792" s="3"/>
     </row>
-    <row r="793">
+    <row r="793" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -24027,7 +24053,7 @@
       <c r="Z793" s="3"/>
       <c r="AA793" s="3"/>
     </row>
-    <row r="794">
+    <row r="794" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -24056,7 +24082,7 @@
       <c r="Z794" s="3"/>
       <c r="AA794" s="3"/>
     </row>
-    <row r="795">
+    <row r="795" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -24085,7 +24111,7 @@
       <c r="Z795" s="3"/>
       <c r="AA795" s="3"/>
     </row>
-    <row r="796">
+    <row r="796" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -24114,7 +24140,7 @@
       <c r="Z796" s="3"/>
       <c r="AA796" s="3"/>
     </row>
-    <row r="797">
+    <row r="797" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -24143,7 +24169,7 @@
       <c r="Z797" s="3"/>
       <c r="AA797" s="3"/>
     </row>
-    <row r="798">
+    <row r="798" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -24172,7 +24198,7 @@
       <c r="Z798" s="3"/>
       <c r="AA798" s="3"/>
     </row>
-    <row r="799">
+    <row r="799" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -24201,7 +24227,7 @@
       <c r="Z799" s="3"/>
       <c r="AA799" s="3"/>
     </row>
-    <row r="800">
+    <row r="800" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -24230,7 +24256,7 @@
       <c r="Z800" s="3"/>
       <c r="AA800" s="3"/>
     </row>
-    <row r="801">
+    <row r="801" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -24259,7 +24285,7 @@
       <c r="Z801" s="3"/>
       <c r="AA801" s="3"/>
     </row>
-    <row r="802">
+    <row r="802" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -24288,7 +24314,7 @@
       <c r="Z802" s="3"/>
       <c r="AA802" s="3"/>
     </row>
-    <row r="803">
+    <row r="803" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -24317,7 +24343,7 @@
       <c r="Z803" s="3"/>
       <c r="AA803" s="3"/>
     </row>
-    <row r="804">
+    <row r="804" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -24346,7 +24372,7 @@
       <c r="Z804" s="3"/>
       <c r="AA804" s="3"/>
     </row>
-    <row r="805">
+    <row r="805" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -24375,7 +24401,7 @@
       <c r="Z805" s="3"/>
       <c r="AA805" s="3"/>
     </row>
-    <row r="806">
+    <row r="806" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -24404,7 +24430,7 @@
       <c r="Z806" s="3"/>
       <c r="AA806" s="3"/>
     </row>
-    <row r="807">
+    <row r="807" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -24433,7 +24459,7 @@
       <c r="Z807" s="3"/>
       <c r="AA807" s="3"/>
     </row>
-    <row r="808">
+    <row r="808" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -24462,7 +24488,7 @@
       <c r="Z808" s="3"/>
       <c r="AA808" s="3"/>
     </row>
-    <row r="809">
+    <row r="809" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -24491,7 +24517,7 @@
       <c r="Z809" s="3"/>
       <c r="AA809" s="3"/>
     </row>
-    <row r="810">
+    <row r="810" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -24520,7 +24546,7 @@
       <c r="Z810" s="3"/>
       <c r="AA810" s="3"/>
     </row>
-    <row r="811">
+    <row r="811" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -24549,7 +24575,7 @@
       <c r="Z811" s="3"/>
       <c r="AA811" s="3"/>
     </row>
-    <row r="812">
+    <row r="812" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -24578,7 +24604,7 @@
       <c r="Z812" s="3"/>
       <c r="AA812" s="3"/>
     </row>
-    <row r="813">
+    <row r="813" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -24607,7 +24633,7 @@
       <c r="Z813" s="3"/>
       <c r="AA813" s="3"/>
     </row>
-    <row r="814">
+    <row r="814" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -24636,7 +24662,7 @@
       <c r="Z814" s="3"/>
       <c r="AA814" s="3"/>
     </row>
-    <row r="815">
+    <row r="815" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -24665,7 +24691,7 @@
       <c r="Z815" s="3"/>
       <c r="AA815" s="3"/>
     </row>
-    <row r="816">
+    <row r="816" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -24694,7 +24720,7 @@
       <c r="Z816" s="3"/>
       <c r="AA816" s="3"/>
     </row>
-    <row r="817">
+    <row r="817" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -24723,7 +24749,7 @@
       <c r="Z817" s="3"/>
       <c r="AA817" s="3"/>
     </row>
-    <row r="818">
+    <row r="818" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -24752,7 +24778,7 @@
       <c r="Z818" s="3"/>
       <c r="AA818" s="3"/>
     </row>
-    <row r="819">
+    <row r="819" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -24781,7 +24807,7 @@
       <c r="Z819" s="3"/>
       <c r="AA819" s="3"/>
     </row>
-    <row r="820">
+    <row r="820" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -24810,7 +24836,7 @@
       <c r="Z820" s="3"/>
       <c r="AA820" s="3"/>
     </row>
-    <row r="821">
+    <row r="821" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -24839,7 +24865,7 @@
       <c r="Z821" s="3"/>
       <c r="AA821" s="3"/>
     </row>
-    <row r="822">
+    <row r="822" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -24868,7 +24894,7 @@
       <c r="Z822" s="3"/>
       <c r="AA822" s="3"/>
     </row>
-    <row r="823">
+    <row r="823" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -24897,7 +24923,7 @@
       <c r="Z823" s="3"/>
       <c r="AA823" s="3"/>
     </row>
-    <row r="824">
+    <row r="824" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -24926,7 +24952,7 @@
       <c r="Z824" s="3"/>
       <c r="AA824" s="3"/>
     </row>
-    <row r="825">
+    <row r="825" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -24955,7 +24981,7 @@
       <c r="Z825" s="3"/>
       <c r="AA825" s="3"/>
     </row>
-    <row r="826">
+    <row r="826" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -24984,7 +25010,7 @@
       <c r="Z826" s="3"/>
       <c r="AA826" s="3"/>
     </row>
-    <row r="827">
+    <row r="827" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -25013,7 +25039,7 @@
       <c r="Z827" s="3"/>
       <c r="AA827" s="3"/>
     </row>
-    <row r="828">
+    <row r="828" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -25042,7 +25068,7 @@
       <c r="Z828" s="3"/>
       <c r="AA828" s="3"/>
     </row>
-    <row r="829">
+    <row r="829" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -25071,7 +25097,7 @@
       <c r="Z829" s="3"/>
       <c r="AA829" s="3"/>
     </row>
-    <row r="830">
+    <row r="830" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -25100,7 +25126,7 @@
       <c r="Z830" s="3"/>
       <c r="AA830" s="3"/>
     </row>
-    <row r="831">
+    <row r="831" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -25129,7 +25155,7 @@
       <c r="Z831" s="3"/>
       <c r="AA831" s="3"/>
     </row>
-    <row r="832">
+    <row r="832" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -25158,7 +25184,7 @@
       <c r="Z832" s="3"/>
       <c r="AA832" s="3"/>
     </row>
-    <row r="833">
+    <row r="833" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -25187,7 +25213,7 @@
       <c r="Z833" s="3"/>
       <c r="AA833" s="3"/>
     </row>
-    <row r="834">
+    <row r="834" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -25216,7 +25242,7 @@
       <c r="Z834" s="3"/>
       <c r="AA834" s="3"/>
     </row>
-    <row r="835">
+    <row r="835" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -25245,7 +25271,7 @@
       <c r="Z835" s="3"/>
       <c r="AA835" s="3"/>
     </row>
-    <row r="836">
+    <row r="836" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -25274,7 +25300,7 @@
       <c r="Z836" s="3"/>
       <c r="AA836" s="3"/>
     </row>
-    <row r="837">
+    <row r="837" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -25303,7 +25329,7 @@
       <c r="Z837" s="3"/>
       <c r="AA837" s="3"/>
     </row>
-    <row r="838">
+    <row r="838" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -25332,7 +25358,7 @@
       <c r="Z838" s="3"/>
       <c r="AA838" s="3"/>
     </row>
-    <row r="839">
+    <row r="839" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -25361,7 +25387,7 @@
       <c r="Z839" s="3"/>
       <c r="AA839" s="3"/>
     </row>
-    <row r="840">
+    <row r="840" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -25390,7 +25416,7 @@
       <c r="Z840" s="3"/>
       <c r="AA840" s="3"/>
     </row>
-    <row r="841">
+    <row r="841" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -25419,7 +25445,7 @@
       <c r="Z841" s="3"/>
       <c r="AA841" s="3"/>
     </row>
-    <row r="842">
+    <row r="842" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -25448,7 +25474,7 @@
       <c r="Z842" s="3"/>
       <c r="AA842" s="3"/>
     </row>
-    <row r="843">
+    <row r="843" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -25477,7 +25503,7 @@
       <c r="Z843" s="3"/>
       <c r="AA843" s="3"/>
     </row>
-    <row r="844">
+    <row r="844" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -25506,7 +25532,7 @@
       <c r="Z844" s="3"/>
       <c r="AA844" s="3"/>
     </row>
-    <row r="845">
+    <row r="845" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -25535,7 +25561,7 @@
       <c r="Z845" s="3"/>
       <c r="AA845" s="3"/>
     </row>
-    <row r="846">
+    <row r="846" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -25564,7 +25590,7 @@
       <c r="Z846" s="3"/>
       <c r="AA846" s="3"/>
     </row>
-    <row r="847">
+    <row r="847" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -25593,7 +25619,7 @@
       <c r="Z847" s="3"/>
       <c r="AA847" s="3"/>
     </row>
-    <row r="848">
+    <row r="848" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -25622,7 +25648,7 @@
       <c r="Z848" s="3"/>
       <c r="AA848" s="3"/>
     </row>
-    <row r="849">
+    <row r="849" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -25651,7 +25677,7 @@
       <c r="Z849" s="3"/>
       <c r="AA849" s="3"/>
     </row>
-    <row r="850">
+    <row r="850" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -25680,7 +25706,7 @@
       <c r="Z850" s="3"/>
       <c r="AA850" s="3"/>
     </row>
-    <row r="851">
+    <row r="851" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -25709,7 +25735,7 @@
       <c r="Z851" s="3"/>
       <c r="AA851" s="3"/>
     </row>
-    <row r="852">
+    <row r="852" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -25738,7 +25764,7 @@
       <c r="Z852" s="3"/>
       <c r="AA852" s="3"/>
     </row>
-    <row r="853">
+    <row r="853" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -25767,7 +25793,7 @@
       <c r="Z853" s="3"/>
       <c r="AA853" s="3"/>
     </row>
-    <row r="854">
+    <row r="854" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -25796,7 +25822,7 @@
       <c r="Z854" s="3"/>
       <c r="AA854" s="3"/>
     </row>
-    <row r="855">
+    <row r="855" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -25825,7 +25851,7 @@
       <c r="Z855" s="3"/>
       <c r="AA855" s="3"/>
     </row>
-    <row r="856">
+    <row r="856" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -25854,7 +25880,7 @@
       <c r="Z856" s="3"/>
       <c r="AA856" s="3"/>
     </row>
-    <row r="857">
+    <row r="857" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -25883,7 +25909,7 @@
       <c r="Z857" s="3"/>
       <c r="AA857" s="3"/>
     </row>
-    <row r="858">
+    <row r="858" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -25912,7 +25938,7 @@
       <c r="Z858" s="3"/>
       <c r="AA858" s="3"/>
     </row>
-    <row r="859">
+    <row r="859" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -25941,7 +25967,7 @@
       <c r="Z859" s="3"/>
       <c r="AA859" s="3"/>
     </row>
-    <row r="860">
+    <row r="860" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -25970,7 +25996,7 @@
       <c r="Z860" s="3"/>
       <c r="AA860" s="3"/>
     </row>
-    <row r="861">
+    <row r="861" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -25999,7 +26025,7 @@
       <c r="Z861" s="3"/>
       <c r="AA861" s="3"/>
     </row>
-    <row r="862">
+    <row r="862" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -26028,7 +26054,7 @@
       <c r="Z862" s="3"/>
       <c r="AA862" s="3"/>
     </row>
-    <row r="863">
+    <row r="863" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -26057,7 +26083,7 @@
       <c r="Z863" s="3"/>
       <c r="AA863" s="3"/>
     </row>
-    <row r="864">
+    <row r="864" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -26086,7 +26112,7 @@
       <c r="Z864" s="3"/>
       <c r="AA864" s="3"/>
     </row>
-    <row r="865">
+    <row r="865" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -26115,7 +26141,7 @@
       <c r="Z865" s="3"/>
       <c r="AA865" s="3"/>
     </row>
-    <row r="866">
+    <row r="866" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -26144,7 +26170,7 @@
       <c r="Z866" s="3"/>
       <c r="AA866" s="3"/>
     </row>
-    <row r="867">
+    <row r="867" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -26173,7 +26199,7 @@
       <c r="Z867" s="3"/>
       <c r="AA867" s="3"/>
     </row>
-    <row r="868">
+    <row r="868" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -26202,7 +26228,7 @@
       <c r="Z868" s="3"/>
       <c r="AA868" s="3"/>
     </row>
-    <row r="869">
+    <row r="869" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -26231,7 +26257,7 @@
       <c r="Z869" s="3"/>
       <c r="AA869" s="3"/>
     </row>
-    <row r="870">
+    <row r="870" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -26260,7 +26286,7 @@
       <c r="Z870" s="3"/>
       <c r="AA870" s="3"/>
     </row>
-    <row r="871">
+    <row r="871" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -26289,7 +26315,7 @@
       <c r="Z871" s="3"/>
       <c r="AA871" s="3"/>
     </row>
-    <row r="872">
+    <row r="872" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -26318,7 +26344,7 @@
       <c r="Z872" s="3"/>
       <c r="AA872" s="3"/>
     </row>
-    <row r="873">
+    <row r="873" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -26347,7 +26373,7 @@
       <c r="Z873" s="3"/>
       <c r="AA873" s="3"/>
     </row>
-    <row r="874">
+    <row r="874" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -26376,7 +26402,7 @@
       <c r="Z874" s="3"/>
       <c r="AA874" s="3"/>
     </row>
-    <row r="875">
+    <row r="875" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -26405,7 +26431,7 @@
       <c r="Z875" s="3"/>
       <c r="AA875" s="3"/>
     </row>
-    <row r="876">
+    <row r="876" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -26434,7 +26460,7 @@
       <c r="Z876" s="3"/>
       <c r="AA876" s="3"/>
     </row>
-    <row r="877">
+    <row r="877" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -26463,7 +26489,7 @@
       <c r="Z877" s="3"/>
       <c r="AA877" s="3"/>
     </row>
-    <row r="878">
+    <row r="878" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -26492,7 +26518,7 @@
       <c r="Z878" s="3"/>
       <c r="AA878" s="3"/>
     </row>
-    <row r="879">
+    <row r="879" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -26521,7 +26547,7 @@
       <c r="Z879" s="3"/>
       <c r="AA879" s="3"/>
     </row>
-    <row r="880">
+    <row r="880" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -26550,7 +26576,7 @@
       <c r="Z880" s="3"/>
       <c r="AA880" s="3"/>
     </row>
-    <row r="881">
+    <row r="881" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -26579,7 +26605,7 @@
       <c r="Z881" s="3"/>
       <c r="AA881" s="3"/>
     </row>
-    <row r="882">
+    <row r="882" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -26608,7 +26634,7 @@
       <c r="Z882" s="3"/>
       <c r="AA882" s="3"/>
     </row>
-    <row r="883">
+    <row r="883" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -26637,7 +26663,7 @@
       <c r="Z883" s="3"/>
       <c r="AA883" s="3"/>
     </row>
-    <row r="884">
+    <row r="884" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -26666,7 +26692,7 @@
       <c r="Z884" s="3"/>
       <c r="AA884" s="3"/>
     </row>
-    <row r="885">
+    <row r="885" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -26695,7 +26721,7 @@
       <c r="Z885" s="3"/>
       <c r="AA885" s="3"/>
     </row>
-    <row r="886">
+    <row r="886" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -26724,7 +26750,7 @@
       <c r="Z886" s="3"/>
       <c r="AA886" s="3"/>
     </row>
-    <row r="887">
+    <row r="887" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -26753,7 +26779,7 @@
       <c r="Z887" s="3"/>
       <c r="AA887" s="3"/>
     </row>
-    <row r="888">
+    <row r="888" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -26782,7 +26808,7 @@
       <c r="Z888" s="3"/>
       <c r="AA888" s="3"/>
     </row>
-    <row r="889">
+    <row r="889" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -26811,7 +26837,7 @@
       <c r="Z889" s="3"/>
       <c r="AA889" s="3"/>
     </row>
-    <row r="890">
+    <row r="890" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -26840,7 +26866,7 @@
       <c r="Z890" s="3"/>
       <c r="AA890" s="3"/>
     </row>
-    <row r="891">
+    <row r="891" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -26869,7 +26895,7 @@
       <c r="Z891" s="3"/>
       <c r="AA891" s="3"/>
     </row>
-    <row r="892">
+    <row r="892" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -26898,7 +26924,7 @@
       <c r="Z892" s="3"/>
       <c r="AA892" s="3"/>
     </row>
-    <row r="893">
+    <row r="893" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -26927,7 +26953,7 @@
       <c r="Z893" s="3"/>
       <c r="AA893" s="3"/>
     </row>
-    <row r="894">
+    <row r="894" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -26956,7 +26982,7 @@
       <c r="Z894" s="3"/>
       <c r="AA894" s="3"/>
     </row>
-    <row r="895">
+    <row r="895" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -26985,7 +27011,7 @@
       <c r="Z895" s="3"/>
       <c r="AA895" s="3"/>
     </row>
-    <row r="896">
+    <row r="896" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -27014,7 +27040,7 @@
       <c r="Z896" s="3"/>
       <c r="AA896" s="3"/>
     </row>
-    <row r="897">
+    <row r="897" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -27043,7 +27069,7 @@
       <c r="Z897" s="3"/>
       <c r="AA897" s="3"/>
     </row>
-    <row r="898">
+    <row r="898" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -27072,7 +27098,7 @@
       <c r="Z898" s="3"/>
       <c r="AA898" s="3"/>
     </row>
-    <row r="899">
+    <row r="899" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -27101,7 +27127,7 @@
       <c r="Z899" s="3"/>
       <c r="AA899" s="3"/>
     </row>
-    <row r="900">
+    <row r="900" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -27130,7 +27156,7 @@
       <c r="Z900" s="3"/>
       <c r="AA900" s="3"/>
     </row>
-    <row r="901">
+    <row r="901" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -27159,7 +27185,7 @@
       <c r="Z901" s="3"/>
       <c r="AA901" s="3"/>
     </row>
-    <row r="902">
+    <row r="902" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -27188,7 +27214,7 @@
       <c r="Z902" s="3"/>
       <c r="AA902" s="3"/>
     </row>
-    <row r="903">
+    <row r="903" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -27217,7 +27243,7 @@
       <c r="Z903" s="3"/>
       <c r="AA903" s="3"/>
     </row>
-    <row r="904">
+    <row r="904" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -27246,7 +27272,7 @@
       <c r="Z904" s="3"/>
       <c r="AA904" s="3"/>
     </row>
-    <row r="905">
+    <row r="905" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -27275,7 +27301,7 @@
       <c r="Z905" s="3"/>
       <c r="AA905" s="3"/>
     </row>
-    <row r="906">
+    <row r="906" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -27304,7 +27330,7 @@
       <c r="Z906" s="3"/>
       <c r="AA906" s="3"/>
     </row>
-    <row r="907">
+    <row r="907" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -27333,7 +27359,7 @@
       <c r="Z907" s="3"/>
       <c r="AA907" s="3"/>
     </row>
-    <row r="908">
+    <row r="908" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -27362,7 +27388,7 @@
       <c r="Z908" s="3"/>
       <c r="AA908" s="3"/>
     </row>
-    <row r="909">
+    <row r="909" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -27391,7 +27417,7 @@
       <c r="Z909" s="3"/>
       <c r="AA909" s="3"/>
     </row>
-    <row r="910">
+    <row r="910" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -27420,7 +27446,7 @@
       <c r="Z910" s="3"/>
       <c r="AA910" s="3"/>
     </row>
-    <row r="911">
+    <row r="911" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -27449,7 +27475,7 @@
       <c r="Z911" s="3"/>
       <c r="AA911" s="3"/>
     </row>
-    <row r="912">
+    <row r="912" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -27478,7 +27504,7 @@
       <c r="Z912" s="3"/>
       <c r="AA912" s="3"/>
     </row>
-    <row r="913">
+    <row r="913" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -27507,7 +27533,7 @@
       <c r="Z913" s="3"/>
       <c r="AA913" s="3"/>
     </row>
-    <row r="914">
+    <row r="914" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -27536,7 +27562,7 @@
       <c r="Z914" s="3"/>
       <c r="AA914" s="3"/>
     </row>
-    <row r="915">
+    <row r="915" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -27565,7 +27591,7 @@
       <c r="Z915" s="3"/>
       <c r="AA915" s="3"/>
     </row>
-    <row r="916">
+    <row r="916" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -27594,7 +27620,7 @@
       <c r="Z916" s="3"/>
       <c r="AA916" s="3"/>
     </row>
-    <row r="917">
+    <row r="917" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -27623,7 +27649,7 @@
       <c r="Z917" s="3"/>
       <c r="AA917" s="3"/>
     </row>
-    <row r="918">
+    <row r="918" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -27652,7 +27678,7 @@
       <c r="Z918" s="3"/>
       <c r="AA918" s="3"/>
     </row>
-    <row r="919">
+    <row r="919" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -27681,7 +27707,7 @@
       <c r="Z919" s="3"/>
       <c r="AA919" s="3"/>
     </row>
-    <row r="920">
+    <row r="920" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -27710,7 +27736,7 @@
       <c r="Z920" s="3"/>
       <c r="AA920" s="3"/>
     </row>
-    <row r="921">
+    <row r="921" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -27739,7 +27765,7 @@
       <c r="Z921" s="3"/>
       <c r="AA921" s="3"/>
     </row>
-    <row r="922">
+    <row r="922" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -27768,7 +27794,7 @@
       <c r="Z922" s="3"/>
       <c r="AA922" s="3"/>
     </row>
-    <row r="923">
+    <row r="923" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -27797,7 +27823,7 @@
       <c r="Z923" s="3"/>
       <c r="AA923" s="3"/>
     </row>
-    <row r="924">
+    <row r="924" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -27826,7 +27852,7 @@
       <c r="Z924" s="3"/>
       <c r="AA924" s="3"/>
     </row>
-    <row r="925">
+    <row r="925" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -27855,7 +27881,7 @@
       <c r="Z925" s="3"/>
       <c r="AA925" s="3"/>
     </row>
-    <row r="926">
+    <row r="926" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -27884,7 +27910,7 @@
       <c r="Z926" s="3"/>
       <c r="AA926" s="3"/>
     </row>
-    <row r="927">
+    <row r="927" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -27913,7 +27939,7 @@
       <c r="Z927" s="3"/>
       <c r="AA927" s="3"/>
     </row>
-    <row r="928">
+    <row r="928" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -27942,7 +27968,7 @@
       <c r="Z928" s="3"/>
       <c r="AA928" s="3"/>
     </row>
-    <row r="929">
+    <row r="929" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -27971,7 +27997,7 @@
       <c r="Z929" s="3"/>
       <c r="AA929" s="3"/>
     </row>
-    <row r="930">
+    <row r="930" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -28000,7 +28026,7 @@
       <c r="Z930" s="3"/>
       <c r="AA930" s="3"/>
     </row>
-    <row r="931">
+    <row r="931" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -28029,7 +28055,7 @@
       <c r="Z931" s="3"/>
       <c r="AA931" s="3"/>
     </row>
-    <row r="932">
+    <row r="932" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -28058,7 +28084,7 @@
       <c r="Z932" s="3"/>
       <c r="AA932" s="3"/>
     </row>
-    <row r="933">
+    <row r="933" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -28087,7 +28113,7 @@
       <c r="Z933" s="3"/>
       <c r="AA933" s="3"/>
     </row>
-    <row r="934">
+    <row r="934" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -28116,7 +28142,7 @@
       <c r="Z934" s="3"/>
       <c r="AA934" s="3"/>
     </row>
-    <row r="935">
+    <row r="935" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -28145,7 +28171,7 @@
       <c r="Z935" s="3"/>
       <c r="AA935" s="3"/>
     </row>
-    <row r="936">
+    <row r="936" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -28174,7 +28200,7 @@
       <c r="Z936" s="3"/>
       <c r="AA936" s="3"/>
     </row>
-    <row r="937">
+    <row r="937" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -28203,7 +28229,7 @@
       <c r="Z937" s="3"/>
       <c r="AA937" s="3"/>
     </row>
-    <row r="938">
+    <row r="938" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -28232,7 +28258,7 @@
       <c r="Z938" s="3"/>
       <c r="AA938" s="3"/>
     </row>
-    <row r="939">
+    <row r="939" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -28261,7 +28287,7 @@
       <c r="Z939" s="3"/>
       <c r="AA939" s="3"/>
     </row>
-    <row r="940">
+    <row r="940" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -28290,7 +28316,7 @@
       <c r="Z940" s="3"/>
       <c r="AA940" s="3"/>
     </row>
-    <row r="941">
+    <row r="941" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -28319,7 +28345,7 @@
       <c r="Z941" s="3"/>
       <c r="AA941" s="3"/>
     </row>
-    <row r="942">
+    <row r="942" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -28348,7 +28374,7 @@
       <c r="Z942" s="3"/>
       <c r="AA942" s="3"/>
     </row>
-    <row r="943">
+    <row r="943" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -28377,7 +28403,7 @@
       <c r="Z943" s="3"/>
       <c r="AA943" s="3"/>
     </row>
-    <row r="944">
+    <row r="944" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -28406,7 +28432,7 @@
       <c r="Z944" s="3"/>
       <c r="AA944" s="3"/>
     </row>
-    <row r="945">
+    <row r="945" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -28435,7 +28461,7 @@
       <c r="Z945" s="3"/>
       <c r="AA945" s="3"/>
     </row>
-    <row r="946">
+    <row r="946" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -28464,7 +28490,7 @@
       <c r="Z946" s="3"/>
       <c r="AA946" s="3"/>
     </row>
-    <row r="947">
+    <row r="947" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -28493,7 +28519,7 @@
       <c r="Z947" s="3"/>
       <c r="AA947" s="3"/>
     </row>
-    <row r="948">
+    <row r="948" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -28522,7 +28548,7 @@
       <c r="Z948" s="3"/>
       <c r="AA948" s="3"/>
     </row>
-    <row r="949">
+    <row r="949" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -28551,7 +28577,7 @@
       <c r="Z949" s="3"/>
       <c r="AA949" s="3"/>
     </row>
-    <row r="950">
+    <row r="950" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -28580,7 +28606,94 @@
       <c r="Z950" s="3"/>
       <c r="AA950" s="3"/>
     </row>
+    <row r="951" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A951" s="3"/>
+      <c r="B951" s="3"/>
+      <c r="C951" s="3"/>
+      <c r="D951" s="3"/>
+      <c r="E951" s="3"/>
+      <c r="F951" s="3"/>
+      <c r="G951" s="3"/>
+      <c r="H951" s="3"/>
+      <c r="I951" s="3"/>
+      <c r="J951" s="3"/>
+      <c r="K951" s="3"/>
+      <c r="L951" s="3"/>
+      <c r="M951" s="3"/>
+      <c r="N951" s="3"/>
+      <c r="O951" s="3"/>
+      <c r="P951" s="3"/>
+      <c r="Q951" s="3"/>
+      <c r="R951" s="3"/>
+      <c r="S951" s="3"/>
+      <c r="T951" s="3"/>
+      <c r="U951" s="3"/>
+      <c r="V951" s="3"/>
+      <c r="W951" s="3"/>
+      <c r="X951" s="3"/>
+      <c r="Y951" s="3"/>
+      <c r="Z951" s="3"/>
+      <c r="AA951" s="3"/>
+    </row>
+    <row r="952" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A952" s="3"/>
+      <c r="B952" s="3"/>
+      <c r="C952" s="3"/>
+      <c r="D952" s="3"/>
+      <c r="E952" s="3"/>
+      <c r="F952" s="3"/>
+      <c r="G952" s="3"/>
+      <c r="H952" s="3"/>
+      <c r="I952" s="3"/>
+      <c r="J952" s="3"/>
+      <c r="K952" s="3"/>
+      <c r="L952" s="3"/>
+      <c r="M952" s="3"/>
+      <c r="N952" s="3"/>
+      <c r="O952" s="3"/>
+      <c r="P952" s="3"/>
+      <c r="Q952" s="3"/>
+      <c r="R952" s="3"/>
+      <c r="S952" s="3"/>
+      <c r="T952" s="3"/>
+      <c r="U952" s="3"/>
+      <c r="V952" s="3"/>
+      <c r="W952" s="3"/>
+      <c r="X952" s="3"/>
+      <c r="Y952" s="3"/>
+      <c r="Z952" s="3"/>
+      <c r="AA952" s="3"/>
+    </row>
+    <row r="953" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A953" s="3"/>
+      <c r="B953" s="3"/>
+      <c r="C953" s="3"/>
+      <c r="D953" s="3"/>
+      <c r="E953" s="3"/>
+      <c r="F953" s="3"/>
+      <c r="G953" s="3"/>
+      <c r="H953" s="3"/>
+      <c r="I953" s="3"/>
+      <c r="J953" s="3"/>
+      <c r="K953" s="3"/>
+      <c r="L953" s="3"/>
+      <c r="M953" s="3"/>
+      <c r="N953" s="3"/>
+      <c r="O953" s="3"/>
+      <c r="P953" s="3"/>
+      <c r="Q953" s="3"/>
+      <c r="R953" s="3"/>
+      <c r="S953" s="3"/>
+      <c r="T953" s="3"/>
+      <c r="U953" s="3"/>
+      <c r="V953" s="3"/>
+      <c r="W953" s="3"/>
+      <c r="X953" s="3"/>
+      <c r="Y953" s="3"/>
+      <c r="Z953" s="3"/>
+      <c r="AA953" s="3"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Week_6/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_6/Capstone Timesheet_Ripal Patel.xlsx
@@ -1,25 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Humber\Semester 3\Capstone Project\HealthCare Plus\Week_6\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8380"/>
-  </bookViews>
   <sheets>
-    <sheet name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
   <si>
     <t>Week_1</t>
   </si>
@@ -174,66 +166,72 @@
     <t>Week_6</t>
   </si>
   <si>
-    <t>Figma User Testing (2 Users)</t>
+    <t>Figma User Testing (for 2 Users)</t>
   </si>
   <si>
-    <t>Figma User Testing (3 Users)</t>
+    <t>Figma User Testing (for 3 Users)</t>
+  </si>
+  <si>
+    <t>Mentor Draft Email</t>
+  </si>
+  <si>
+    <t>Mentor Checklist</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd\-mmm"/>
-    <numFmt numFmtId="165" formatCode="d\-mmm"/>
+    <numFmt numFmtId="164" formatCode="dd-mmm"/>
+    <numFmt numFmtId="165" formatCode="d-mmm"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -243,7 +241,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -300,14 +298,8 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="3">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -321,189 +313,189 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="57">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+  <cellXfs count="56">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="2" fillId="6" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="2" fillId="7" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -511,7 +503,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -701,26 +693,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA953"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="62.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10.0"/>
+    <col customWidth="1" min="2" max="2" width="62.25"/>
+    <col customWidth="1" min="3" max="3" width="12.25"/>
+    <col customWidth="1" min="4" max="4" width="12.13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -757,13 +746,13 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D2" s="6">
         <v>1.3</v>
@@ -792,13 +781,13 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D3" s="6">
         <v>0.15</v>
@@ -827,16 +816,16 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -862,16 +851,16 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D5" s="4">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -897,13 +886,13 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="5">
-        <v>46038</v>
+        <v>46038.0</v>
       </c>
       <c r="D6" s="4">
         <v>4.75</v>
@@ -932,13 +921,13 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>46038</v>
+        <v>46038.0</v>
       </c>
       <c r="D7" s="4">
         <v>3.5</v>
@@ -967,13 +956,13 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="5">
-        <v>46038</v>
+        <v>46038.0</v>
       </c>
       <c r="D8" s="4">
         <v>5.75</v>
@@ -1002,16 +991,16 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>46039</v>
+        <v>46039.0</v>
       </c>
       <c r="D9" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1037,13 +1026,13 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="5">
-        <v>46039</v>
+        <v>46039.0</v>
       </c>
       <c r="D10" s="4">
         <v>5.5</v>
@@ -1072,13 +1061,13 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="5">
-        <v>46041</v>
+        <v>46041.0</v>
       </c>
       <c r="D11" s="4">
         <v>4.75</v>
@@ -1107,13 +1096,13 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="5">
-        <v>46043</v>
+        <v>46043.0</v>
       </c>
       <c r="D12" s="4">
         <v>4.75</v>
@@ -1142,7 +1131,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
@@ -1171,14 +1160,14 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="7">
-        <f>SUM(D2:D12)</f>
+        <f>sum(D2:D12)</f>
         <v>38.6</v>
       </c>
       <c r="E14" s="2"/>
@@ -1205,7 +1194,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1234,7 +1223,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1263,7 +1252,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17">
       <c r="A17" s="9" t="s">
         <v>16</v>
       </c>
@@ -1300,13 +1289,13 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="12">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="D18" s="13">
         <v>1.5</v>
@@ -1335,16 +1324,16 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" s="10"/>
       <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="12">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="D19" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1370,16 +1359,16 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="12">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="D20" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1405,16 +1394,16 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="12">
-        <v>46045</v>
+        <v>46045.0</v>
       </c>
       <c r="D21" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1440,16 +1429,16 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="12">
-        <v>46045</v>
+        <v>46045.0</v>
       </c>
       <c r="D22" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1475,13 +1464,13 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" s="10"/>
       <c r="B23" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="12">
-        <v>46046</v>
+        <v>46046.0</v>
       </c>
       <c r="D23" s="13">
         <v>1.5</v>
@@ -1510,13 +1499,13 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="12">
-        <v>46046</v>
+        <v>46046.0</v>
       </c>
       <c r="D24" s="13">
         <v>2.5</v>
@@ -1545,16 +1534,16 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" s="10"/>
       <c r="B25" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="12">
-        <v>46046</v>
+        <v>46046.0</v>
       </c>
       <c r="D25" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1580,13 +1569,13 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="10"/>
       <c r="B26" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="12">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="D26" s="13">
         <v>1.75</v>
@@ -1615,16 +1604,16 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
     </row>
-    <row r="27" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="10"/>
       <c r="B27" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="12">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="D27" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1650,13 +1639,13 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
     </row>
-    <row r="28" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="10"/>
       <c r="B28" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="12">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="D28" s="13">
         <v>2.75</v>
@@ -1685,16 +1674,16 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
     </row>
-    <row r="29" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="16">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="D29" s="17">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1720,16 +1709,16 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
     </row>
-    <row r="30" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="14"/>
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="16">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="D30" s="17">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -1755,16 +1744,16 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3"/>
     </row>
-    <row r="31" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="14"/>
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C31" s="16">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="D31" s="17">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1790,13 +1779,13 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3"/>
     </row>
-    <row r="32" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="14"/>
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="16">
-        <v>46049</v>
+        <v>46049.0</v>
       </c>
       <c r="D32" s="17">
         <v>2.5</v>
@@ -1825,13 +1814,13 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3"/>
     </row>
-    <row r="33" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="14"/>
       <c r="B33" s="18" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="19">
-        <v>46049</v>
+        <v>46049.0</v>
       </c>
       <c r="D33" s="20">
         <v>3.75</v>
@@ -1860,14 +1849,14 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
     </row>
-    <row r="34" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="21"/>
       <c r="B34" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="22"/>
       <c r="D34" s="21">
-        <f>SUM(D18:D33)</f>
+        <f>sum(D18:D33)</f>
         <v>33.4</v>
       </c>
       <c r="E34" s="2"/>
@@ -1894,7 +1883,7 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
     </row>
-    <row r="35" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1923,7 +1912,7 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
     </row>
-    <row r="36" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1952,7 +1941,7 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
     </row>
-    <row r="37" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37" s="23" t="s">
         <v>33</v>
       </c>
@@ -1989,13 +1978,13 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3"/>
     </row>
-    <row r="38" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="24"/>
       <c r="B38" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C38" s="26">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="D38" s="27">
         <v>1.5</v>
@@ -2024,13 +2013,13 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3"/>
     </row>
-    <row r="39" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39" s="24"/>
       <c r="B39" s="25" t="s">
         <v>35</v>
       </c>
       <c r="C39" s="26">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="D39" s="27">
         <v>1.75</v>
@@ -2059,13 +2048,13 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
     </row>
-    <row r="40" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40" s="24"/>
       <c r="B40" s="25" t="s">
         <v>36</v>
       </c>
       <c r="C40" s="26">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="D40" s="27">
         <v>2.15</v>
@@ -2094,13 +2083,13 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
     </row>
-    <row r="41" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="24"/>
       <c r="B41" s="25" t="s">
         <v>37</v>
       </c>
       <c r="C41" s="26">
-        <v>46054</v>
+        <v>46054.0</v>
       </c>
       <c r="D41" s="27">
         <v>2.75</v>
@@ -2129,13 +2118,13 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3"/>
     </row>
-    <row r="42" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42" s="24"/>
       <c r="B42" s="25" t="s">
         <v>38</v>
       </c>
       <c r="C42" s="26">
-        <v>46055</v>
+        <v>46055.0</v>
       </c>
       <c r="D42" s="27">
         <v>3.75</v>
@@ -2164,7 +2153,7 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3"/>
     </row>
-    <row r="43" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2193,14 +2182,14 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3"/>
     </row>
-    <row r="44" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44" s="28"/>
       <c r="B44" s="29" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="24">
-        <f>SUM(D38:D42)</f>
+        <f>sum(D38:D42)</f>
         <v>11.9</v>
       </c>
       <c r="E44" s="3"/>
@@ -2227,7 +2216,7 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3"/>
     </row>
-    <row r="45" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2256,7 +2245,7 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3"/>
     </row>
-    <row r="46" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2285,7 +2274,7 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3"/>
     </row>
-    <row r="47" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47" s="31" t="s">
         <v>39</v>
       </c>
@@ -2322,13 +2311,13 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3"/>
     </row>
-    <row r="48" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48" s="32"/>
       <c r="B48" s="33" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="34">
-        <v>46059</v>
+        <v>46059.0</v>
       </c>
       <c r="D48" s="35">
         <v>3.75</v>
@@ -2357,13 +2346,13 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3"/>
     </row>
-    <row r="49" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49" s="32"/>
       <c r="B49" s="33" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="34">
-        <v>46061</v>
+        <v>46061.0</v>
       </c>
       <c r="D49" s="35">
         <v>3.25</v>
@@ -2392,13 +2381,13 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3"/>
     </row>
-    <row r="50" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50" s="32"/>
       <c r="B50" s="33" t="s">
         <v>42</v>
       </c>
       <c r="C50" s="34">
-        <v>46061</v>
+        <v>46061.0</v>
       </c>
       <c r="D50" s="35">
         <v>4.5</v>
@@ -2427,13 +2416,13 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3"/>
     </row>
-    <row r="51" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="51">
       <c r="A51" s="32"/>
       <c r="B51" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="34">
-        <v>46062</v>
+        <v>46062.0</v>
       </c>
       <c r="D51" s="35">
         <v>3.75</v>
@@ -2462,13 +2451,13 @@
       <c r="Z51" s="3"/>
       <c r="AA51" s="3"/>
     </row>
-    <row r="52" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52" s="32"/>
       <c r="B52" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C52" s="34">
-        <v>46063</v>
+        <v>46063.0</v>
       </c>
       <c r="D52" s="35">
         <v>3.5</v>
@@ -2497,7 +2486,7 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3"/>
     </row>
-    <row r="53" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2526,14 +2515,14 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3"/>
     </row>
-    <row r="54" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54" s="36"/>
       <c r="B54" s="37" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="38"/>
       <c r="D54" s="39">
-        <f>SUM(D48:D52)</f>
+        <f>sum(D48:D52)</f>
         <v>18.75</v>
       </c>
       <c r="E54" s="3"/>
@@ -2560,7 +2549,7 @@
       <c r="Z54" s="3"/>
       <c r="AA54" s="3"/>
     </row>
-    <row r="55" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2589,7 +2578,7 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
     </row>
-    <row r="56" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="56">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2618,7 +2607,7 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
     </row>
-    <row r="57" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57" s="40" t="s">
         <v>45</v>
       </c>
@@ -2655,13 +2644,13 @@
       <c r="Z57" s="3"/>
       <c r="AA57" s="3"/>
     </row>
-    <row r="58" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58" s="41"/>
       <c r="B58" s="42" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="43">
-        <v>46066</v>
+        <v>46066.0</v>
       </c>
       <c r="D58" s="44">
         <v>2.15</v>
@@ -2690,13 +2679,13 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3"/>
     </row>
-    <row r="59" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59" s="41"/>
       <c r="B59" s="42" t="s">
         <v>47</v>
       </c>
       <c r="C59" s="43">
-        <v>46066</v>
+        <v>46066.0</v>
       </c>
       <c r="D59" s="44">
         <v>3.75</v>
@@ -2725,13 +2714,13 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3"/>
     </row>
-    <row r="60" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60" s="41"/>
       <c r="B60" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="43">
-        <v>46069</v>
+        <v>46069.0</v>
       </c>
       <c r="D60" s="44">
         <v>3.5</v>
@@ -2760,13 +2749,13 @@
       <c r="Z60" s="3"/>
       <c r="AA60" s="3"/>
     </row>
-    <row r="61" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61" s="41"/>
       <c r="B61" s="42" t="s">
         <v>49</v>
       </c>
       <c r="C61" s="43">
-        <v>46069</v>
+        <v>46069.0</v>
       </c>
       <c r="D61" s="44">
         <v>2.5</v>
@@ -2795,7 +2784,7 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3"/>
     </row>
-    <row r="62" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2824,14 +2813,14 @@
       <c r="Z62" s="3"/>
       <c r="AA62" s="3"/>
     </row>
-    <row r="63" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63" s="45"/>
       <c r="B63" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="47"/>
       <c r="D63" s="41">
-        <f>SUM(D58:D61)</f>
+        <f>sum(D58:D61)</f>
         <v>11.9</v>
       </c>
       <c r="E63" s="3"/>
@@ -2858,7 +2847,7 @@
       <c r="Z63" s="3"/>
       <c r="AA63" s="3"/>
     </row>
-    <row r="64" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2887,7 +2876,7 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3"/>
     </row>
-    <row r="65" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2916,17 +2905,17 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3"/>
     </row>
-    <row r="66" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="52" t="s">
+    <row r="66">
+      <c r="A66" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B66" s="52" t="s">
+      <c r="B66" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="52" t="s">
+      <c r="C66" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="52" t="s">
+      <c r="D66" s="48" t="s">
         <v>3</v>
       </c>
       <c r="E66" s="3"/>
@@ -2953,15 +2942,15 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3"/>
     </row>
-    <row r="67" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="53"/>
-      <c r="B67" s="54" t="s">
+    <row r="67">
+      <c r="A67" s="49"/>
+      <c r="B67" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="C67" s="55">
-        <v>46073</v>
+      <c r="C67" s="51">
+        <v>46073.0</v>
       </c>
-      <c r="D67" s="56">
+      <c r="D67" s="52">
         <v>1.75</v>
       </c>
       <c r="E67" s="3"/>
@@ -2988,16 +2977,16 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
     </row>
-    <row r="68" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="53"/>
-      <c r="B68" s="54" t="s">
+    <row r="68">
+      <c r="A68" s="49"/>
+      <c r="B68" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="C68" s="55">
-        <v>46074</v>
+      <c r="C68" s="51">
+        <v>46074.0</v>
       </c>
-      <c r="D68" s="56">
-        <v>2</v>
+      <c r="D68" s="52">
+        <v>2.0</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -3023,11 +3012,17 @@
       <c r="Z68" s="3"/>
       <c r="AA68" s="3"/>
     </row>
-    <row r="69" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="53"/>
-      <c r="B69" s="54"/>
-      <c r="C69" s="55"/>
-      <c r="D69" s="56"/>
+    <row r="69">
+      <c r="A69" s="49"/>
+      <c r="B69" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="51">
+        <v>46075.0</v>
+      </c>
+      <c r="D69" s="52">
+        <v>0.25</v>
+      </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -3052,11 +3047,17 @@
       <c r="Z69" s="3"/>
       <c r="AA69" s="3"/>
     </row>
-    <row r="70" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="53"/>
-      <c r="B70" s="54"/>
-      <c r="C70" s="55"/>
-      <c r="D70" s="56"/>
+    <row r="70">
+      <c r="A70" s="49"/>
+      <c r="B70" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" s="51">
+        <v>46076.0</v>
+      </c>
+      <c r="D70" s="52">
+        <v>1.75</v>
+      </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
@@ -3081,7 +3082,7 @@
       <c r="Z70" s="3"/>
       <c r="AA70" s="3"/>
     </row>
-    <row r="71" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -3110,15 +3111,15 @@
       <c r="Z71" s="3"/>
       <c r="AA71" s="3"/>
     </row>
-    <row r="72" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="49"/>
-      <c r="B72" s="50" t="s">
+    <row r="72">
+      <c r="A72" s="53"/>
+      <c r="B72" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="51"/>
-      <c r="D72" s="48">
-        <f>SUM(D67:D68)</f>
-        <v>3.75</v>
+      <c r="C72" s="55"/>
+      <c r="D72" s="49">
+        <f>sum(D67:D70)</f>
+        <v>5.75</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -3144,7 +3145,7 @@
       <c r="Z72" s="3"/>
       <c r="AA72" s="3"/>
     </row>
-    <row r="73" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -3173,7 +3174,7 @@
       <c r="Z73" s="3"/>
       <c r="AA73" s="3"/>
     </row>
-    <row r="74" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="74">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3202,7 +3203,7 @@
       <c r="Z74" s="3"/>
       <c r="AA74" s="3"/>
     </row>
-    <row r="75" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="75">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3231,7 +3232,7 @@
       <c r="Z75" s="3"/>
       <c r="AA75" s="3"/>
     </row>
-    <row r="76" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="76">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -3260,7 +3261,7 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3"/>
     </row>
-    <row r="77" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="77">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -3289,7 +3290,7 @@
       <c r="Z77" s="3"/>
       <c r="AA77" s="3"/>
     </row>
-    <row r="78" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="78">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -3318,7 +3319,7 @@
       <c r="Z78" s="3"/>
       <c r="AA78" s="3"/>
     </row>
-    <row r="79" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="79">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -3347,7 +3348,7 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3"/>
     </row>
-    <row r="80" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="80">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -3376,7 +3377,7 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3"/>
     </row>
-    <row r="81" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -3405,7 +3406,7 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3"/>
     </row>
-    <row r="82" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="82">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -3434,7 +3435,7 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
     </row>
-    <row r="83" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="83">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -3463,7 +3464,7 @@
       <c r="Z83" s="3"/>
       <c r="AA83" s="3"/>
     </row>
-    <row r="84" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="84">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -3492,7 +3493,7 @@
       <c r="Z84" s="3"/>
       <c r="AA84" s="3"/>
     </row>
-    <row r="85" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="85">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -3521,7 +3522,7 @@
       <c r="Z85" s="3"/>
       <c r="AA85" s="3"/>
     </row>
-    <row r="86" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="86">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -3550,7 +3551,7 @@
       <c r="Z86" s="3"/>
       <c r="AA86" s="3"/>
     </row>
-    <row r="87" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="87">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -3579,7 +3580,7 @@
       <c r="Z87" s="3"/>
       <c r="AA87" s="3"/>
     </row>
-    <row r="88" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="88">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -3608,7 +3609,7 @@
       <c r="Z88" s="3"/>
       <c r="AA88" s="3"/>
     </row>
-    <row r="89" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="89">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3637,7 +3638,7 @@
       <c r="Z89" s="3"/>
       <c r="AA89" s="3"/>
     </row>
-    <row r="90" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="90">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3666,7 +3667,7 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
     </row>
-    <row r="91" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="91">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -3695,7 +3696,7 @@
       <c r="Z91" s="3"/>
       <c r="AA91" s="3"/>
     </row>
-    <row r="92" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="92">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -3724,7 +3725,7 @@
       <c r="Z92" s="3"/>
       <c r="AA92" s="3"/>
     </row>
-    <row r="93" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="93">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -3753,7 +3754,7 @@
       <c r="Z93" s="3"/>
       <c r="AA93" s="3"/>
     </row>
-    <row r="94" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="94">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -3782,7 +3783,7 @@
       <c r="Z94" s="3"/>
       <c r="AA94" s="3"/>
     </row>
-    <row r="95" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="95">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -3811,7 +3812,7 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
     </row>
-    <row r="96" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="96">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -3840,7 +3841,7 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3"/>
     </row>
-    <row r="97" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="97">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -3869,7 +3870,7 @@
       <c r="Z97" s="3"/>
       <c r="AA97" s="3"/>
     </row>
-    <row r="98" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="98">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -3898,7 +3899,7 @@
       <c r="Z98" s="3"/>
       <c r="AA98" s="3"/>
     </row>
-    <row r="99" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="99">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -3927,7 +3928,7 @@
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
     </row>
-    <row r="100" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="100">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -3956,7 +3957,7 @@
       <c r="Z100" s="3"/>
       <c r="AA100" s="3"/>
     </row>
-    <row r="101" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="101">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -3985,7 +3986,7 @@
       <c r="Z101" s="3"/>
       <c r="AA101" s="3"/>
     </row>
-    <row r="102" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="102">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -4014,7 +4015,7 @@
       <c r="Z102" s="3"/>
       <c r="AA102" s="3"/>
     </row>
-    <row r="103" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="103">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4043,7 +4044,7 @@
       <c r="Z103" s="3"/>
       <c r="AA103" s="3"/>
     </row>
-    <row r="104" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="104">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4072,7 +4073,7 @@
       <c r="Z104" s="3"/>
       <c r="AA104" s="3"/>
     </row>
-    <row r="105" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="105">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4101,7 +4102,7 @@
       <c r="Z105" s="3"/>
       <c r="AA105" s="3"/>
     </row>
-    <row r="106" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="106">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4130,7 +4131,7 @@
       <c r="Z106" s="3"/>
       <c r="AA106" s="3"/>
     </row>
-    <row r="107" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="107">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4159,7 +4160,7 @@
       <c r="Z107" s="3"/>
       <c r="AA107" s="3"/>
     </row>
-    <row r="108" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="108">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4188,7 +4189,7 @@
       <c r="Z108" s="3"/>
       <c r="AA108" s="3"/>
     </row>
-    <row r="109" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="109">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4217,7 +4218,7 @@
       <c r="Z109" s="3"/>
       <c r="AA109" s="3"/>
     </row>
-    <row r="110" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="110">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4246,7 +4247,7 @@
       <c r="Z110" s="3"/>
       <c r="AA110" s="3"/>
     </row>
-    <row r="111" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="111">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4275,7 +4276,7 @@
       <c r="Z111" s="3"/>
       <c r="AA111" s="3"/>
     </row>
-    <row r="112" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="112">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4304,7 +4305,7 @@
       <c r="Z112" s="3"/>
       <c r="AA112" s="3"/>
     </row>
-    <row r="113" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="113">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4333,7 +4334,7 @@
       <c r="Z113" s="3"/>
       <c r="AA113" s="3"/>
     </row>
-    <row r="114" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="114">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4362,7 +4363,7 @@
       <c r="Z114" s="3"/>
       <c r="AA114" s="3"/>
     </row>
-    <row r="115" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="115">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4391,7 +4392,7 @@
       <c r="Z115" s="3"/>
       <c r="AA115" s="3"/>
     </row>
-    <row r="116" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="116">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4420,7 +4421,7 @@
       <c r="Z116" s="3"/>
       <c r="AA116" s="3"/>
     </row>
-    <row r="117" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="117">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4449,7 +4450,7 @@
       <c r="Z117" s="3"/>
       <c r="AA117" s="3"/>
     </row>
-    <row r="118" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="118">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4478,7 +4479,7 @@
       <c r="Z118" s="3"/>
       <c r="AA118" s="3"/>
     </row>
-    <row r="119" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="119">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4507,7 +4508,7 @@
       <c r="Z119" s="3"/>
       <c r="AA119" s="3"/>
     </row>
-    <row r="120" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="120">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -4536,7 +4537,7 @@
       <c r="Z120" s="3"/>
       <c r="AA120" s="3"/>
     </row>
-    <row r="121" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="121">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4565,7 +4566,7 @@
       <c r="Z121" s="3"/>
       <c r="AA121" s="3"/>
     </row>
-    <row r="122" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="122">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4594,7 +4595,7 @@
       <c r="Z122" s="3"/>
       <c r="AA122" s="3"/>
     </row>
-    <row r="123" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="123">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4623,7 +4624,7 @@
       <c r="Z123" s="3"/>
       <c r="AA123" s="3"/>
     </row>
-    <row r="124" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="124">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4652,7 +4653,7 @@
       <c r="Z124" s="3"/>
       <c r="AA124" s="3"/>
     </row>
-    <row r="125" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="125">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4681,7 +4682,7 @@
       <c r="Z125" s="3"/>
       <c r="AA125" s="3"/>
     </row>
-    <row r="126" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="126">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4710,7 +4711,7 @@
       <c r="Z126" s="3"/>
       <c r="AA126" s="3"/>
     </row>
-    <row r="127" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="127">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -4739,7 +4740,7 @@
       <c r="Z127" s="3"/>
       <c r="AA127" s="3"/>
     </row>
-    <row r="128" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="128">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -4768,7 +4769,7 @@
       <c r="Z128" s="3"/>
       <c r="AA128" s="3"/>
     </row>
-    <row r="129" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="129">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -4797,7 +4798,7 @@
       <c r="Z129" s="3"/>
       <c r="AA129" s="3"/>
     </row>
-    <row r="130" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="130">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -4826,7 +4827,7 @@
       <c r="Z130" s="3"/>
       <c r="AA130" s="3"/>
     </row>
-    <row r="131" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="131">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -4855,7 +4856,7 @@
       <c r="Z131" s="3"/>
       <c r="AA131" s="3"/>
     </row>
-    <row r="132" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="132">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -4884,7 +4885,7 @@
       <c r="Z132" s="3"/>
       <c r="AA132" s="3"/>
     </row>
-    <row r="133" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="133">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -4913,7 +4914,7 @@
       <c r="Z133" s="3"/>
       <c r="AA133" s="3"/>
     </row>
-    <row r="134" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="134">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -4942,7 +4943,7 @@
       <c r="Z134" s="3"/>
       <c r="AA134" s="3"/>
     </row>
-    <row r="135" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="135">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -4971,7 +4972,7 @@
       <c r="Z135" s="3"/>
       <c r="AA135" s="3"/>
     </row>
-    <row r="136" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="136">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -5000,7 +5001,7 @@
       <c r="Z136" s="3"/>
       <c r="AA136" s="3"/>
     </row>
-    <row r="137" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="137">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -5029,7 +5030,7 @@
       <c r="Z137" s="3"/>
       <c r="AA137" s="3"/>
     </row>
-    <row r="138" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="138">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -5058,7 +5059,7 @@
       <c r="Z138" s="3"/>
       <c r="AA138" s="3"/>
     </row>
-    <row r="139" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="139">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -5087,7 +5088,7 @@
       <c r="Z139" s="3"/>
       <c r="AA139" s="3"/>
     </row>
-    <row r="140" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="140">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -5116,7 +5117,7 @@
       <c r="Z140" s="3"/>
       <c r="AA140" s="3"/>
     </row>
-    <row r="141" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="141">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -5145,7 +5146,7 @@
       <c r="Z141" s="3"/>
       <c r="AA141" s="3"/>
     </row>
-    <row r="142" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="142">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -5174,7 +5175,7 @@
       <c r="Z142" s="3"/>
       <c r="AA142" s="3"/>
     </row>
-    <row r="143" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="143">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -5203,7 +5204,7 @@
       <c r="Z143" s="3"/>
       <c r="AA143" s="3"/>
     </row>
-    <row r="144" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="144">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -5232,7 +5233,7 @@
       <c r="Z144" s="3"/>
       <c r="AA144" s="3"/>
     </row>
-    <row r="145" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="145">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -5261,7 +5262,7 @@
       <c r="Z145" s="3"/>
       <c r="AA145" s="3"/>
     </row>
-    <row r="146" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="146">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -5290,7 +5291,7 @@
       <c r="Z146" s="3"/>
       <c r="AA146" s="3"/>
     </row>
-    <row r="147" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="147">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -5319,7 +5320,7 @@
       <c r="Z147" s="3"/>
       <c r="AA147" s="3"/>
     </row>
-    <row r="148" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="148">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -5348,7 +5349,7 @@
       <c r="Z148" s="3"/>
       <c r="AA148" s="3"/>
     </row>
-    <row r="149" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="149">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -5377,7 +5378,7 @@
       <c r="Z149" s="3"/>
       <c r="AA149" s="3"/>
     </row>
-    <row r="150" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="150">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -5406,7 +5407,7 @@
       <c r="Z150" s="3"/>
       <c r="AA150" s="3"/>
     </row>
-    <row r="151" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="151">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -5435,7 +5436,7 @@
       <c r="Z151" s="3"/>
       <c r="AA151" s="3"/>
     </row>
-    <row r="152" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="152">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -5464,7 +5465,7 @@
       <c r="Z152" s="3"/>
       <c r="AA152" s="3"/>
     </row>
-    <row r="153" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="153">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -5493,7 +5494,7 @@
       <c r="Z153" s="3"/>
       <c r="AA153" s="3"/>
     </row>
-    <row r="154" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="154">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -5522,7 +5523,7 @@
       <c r="Z154" s="3"/>
       <c r="AA154" s="3"/>
     </row>
-    <row r="155" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="155">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -5551,7 +5552,7 @@
       <c r="Z155" s="3"/>
       <c r="AA155" s="3"/>
     </row>
-    <row r="156" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="156">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -5580,7 +5581,7 @@
       <c r="Z156" s="3"/>
       <c r="AA156" s="3"/>
     </row>
-    <row r="157" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="157">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -5609,7 +5610,7 @@
       <c r="Z157" s="3"/>
       <c r="AA157" s="3"/>
     </row>
-    <row r="158" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="158">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -5638,7 +5639,7 @@
       <c r="Z158" s="3"/>
       <c r="AA158" s="3"/>
     </row>
-    <row r="159" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="159">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -5667,7 +5668,7 @@
       <c r="Z159" s="3"/>
       <c r="AA159" s="3"/>
     </row>
-    <row r="160" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="160">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -5696,7 +5697,7 @@
       <c r="Z160" s="3"/>
       <c r="AA160" s="3"/>
     </row>
-    <row r="161" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="161">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -5725,7 +5726,7 @@
       <c r="Z161" s="3"/>
       <c r="AA161" s="3"/>
     </row>
-    <row r="162" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="162">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -5754,7 +5755,7 @@
       <c r="Z162" s="3"/>
       <c r="AA162" s="3"/>
     </row>
-    <row r="163" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="163">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -5783,7 +5784,7 @@
       <c r="Z163" s="3"/>
       <c r="AA163" s="3"/>
     </row>
-    <row r="164" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="164">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -5812,7 +5813,7 @@
       <c r="Z164" s="3"/>
       <c r="AA164" s="3"/>
     </row>
-    <row r="165" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="165">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -5841,7 +5842,7 @@
       <c r="Z165" s="3"/>
       <c r="AA165" s="3"/>
     </row>
-    <row r="166" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="166">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -5870,7 +5871,7 @@
       <c r="Z166" s="3"/>
       <c r="AA166" s="3"/>
     </row>
-    <row r="167" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="167">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -5899,7 +5900,7 @@
       <c r="Z167" s="3"/>
       <c r="AA167" s="3"/>
     </row>
-    <row r="168" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="168">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -5928,7 +5929,7 @@
       <c r="Z168" s="3"/>
       <c r="AA168" s="3"/>
     </row>
-    <row r="169" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="169">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -5957,7 +5958,7 @@
       <c r="Z169" s="3"/>
       <c r="AA169" s="3"/>
     </row>
-    <row r="170" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="170">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -5986,7 +5987,7 @@
       <c r="Z170" s="3"/>
       <c r="AA170" s="3"/>
     </row>
-    <row r="171" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="171">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -6015,7 +6016,7 @@
       <c r="Z171" s="3"/>
       <c r="AA171" s="3"/>
     </row>
-    <row r="172" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="172">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -6044,7 +6045,7 @@
       <c r="Z172" s="3"/>
       <c r="AA172" s="3"/>
     </row>
-    <row r="173" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="173">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -6073,7 +6074,7 @@
       <c r="Z173" s="3"/>
       <c r="AA173" s="3"/>
     </row>
-    <row r="174" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="174">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -6102,7 +6103,7 @@
       <c r="Z174" s="3"/>
       <c r="AA174" s="3"/>
     </row>
-    <row r="175" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="175">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -6131,7 +6132,7 @@
       <c r="Z175" s="3"/>
       <c r="AA175" s="3"/>
     </row>
-    <row r="176" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="176">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -6160,7 +6161,7 @@
       <c r="Z176" s="3"/>
       <c r="AA176" s="3"/>
     </row>
-    <row r="177" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="177">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -6189,7 +6190,7 @@
       <c r="Z177" s="3"/>
       <c r="AA177" s="3"/>
     </row>
-    <row r="178" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="178">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -6218,7 +6219,7 @@
       <c r="Z178" s="3"/>
       <c r="AA178" s="3"/>
     </row>
-    <row r="179" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="179">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -6247,7 +6248,7 @@
       <c r="Z179" s="3"/>
       <c r="AA179" s="3"/>
     </row>
-    <row r="180" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="180">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -6276,7 +6277,7 @@
       <c r="Z180" s="3"/>
       <c r="AA180" s="3"/>
     </row>
-    <row r="181" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="181">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -6305,7 +6306,7 @@
       <c r="Z181" s="3"/>
       <c r="AA181" s="3"/>
     </row>
-    <row r="182" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="182">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -6334,7 +6335,7 @@
       <c r="Z182" s="3"/>
       <c r="AA182" s="3"/>
     </row>
-    <row r="183" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="183">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -6363,7 +6364,7 @@
       <c r="Z183" s="3"/>
       <c r="AA183" s="3"/>
     </row>
-    <row r="184" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="184">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -6392,7 +6393,7 @@
       <c r="Z184" s="3"/>
       <c r="AA184" s="3"/>
     </row>
-    <row r="185" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="185">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -6421,7 +6422,7 @@
       <c r="Z185" s="3"/>
       <c r="AA185" s="3"/>
     </row>
-    <row r="186" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="186">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -6450,7 +6451,7 @@
       <c r="Z186" s="3"/>
       <c r="AA186" s="3"/>
     </row>
-    <row r="187" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="187">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -6479,7 +6480,7 @@
       <c r="Z187" s="3"/>
       <c r="AA187" s="3"/>
     </row>
-    <row r="188" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="188">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -6508,7 +6509,7 @@
       <c r="Z188" s="3"/>
       <c r="AA188" s="3"/>
     </row>
-    <row r="189" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="189">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -6537,7 +6538,7 @@
       <c r="Z189" s="3"/>
       <c r="AA189" s="3"/>
     </row>
-    <row r="190" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="190">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -6566,7 +6567,7 @@
       <c r="Z190" s="3"/>
       <c r="AA190" s="3"/>
     </row>
-    <row r="191" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="191">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -6595,7 +6596,7 @@
       <c r="Z191" s="3"/>
       <c r="AA191" s="3"/>
     </row>
-    <row r="192" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="192">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -6624,7 +6625,7 @@
       <c r="Z192" s="3"/>
       <c r="AA192" s="3"/>
     </row>
-    <row r="193" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="193">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -6653,7 +6654,7 @@
       <c r="Z193" s="3"/>
       <c r="AA193" s="3"/>
     </row>
-    <row r="194" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="194">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -6682,7 +6683,7 @@
       <c r="Z194" s="3"/>
       <c r="AA194" s="3"/>
     </row>
-    <row r="195" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="195">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -6711,7 +6712,7 @@
       <c r="Z195" s="3"/>
       <c r="AA195" s="3"/>
     </row>
-    <row r="196" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="196">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -6740,7 +6741,7 @@
       <c r="Z196" s="3"/>
       <c r="AA196" s="3"/>
     </row>
-    <row r="197" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="197">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -6769,7 +6770,7 @@
       <c r="Z197" s="3"/>
       <c r="AA197" s="3"/>
     </row>
-    <row r="198" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="198">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -6798,7 +6799,7 @@
       <c r="Z198" s="3"/>
       <c r="AA198" s="3"/>
     </row>
-    <row r="199" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="199">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -6827,7 +6828,7 @@
       <c r="Z199" s="3"/>
       <c r="AA199" s="3"/>
     </row>
-    <row r="200" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="200">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -6856,7 +6857,7 @@
       <c r="Z200" s="3"/>
       <c r="AA200" s="3"/>
     </row>
-    <row r="201" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="201">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -6885,7 +6886,7 @@
       <c r="Z201" s="3"/>
       <c r="AA201" s="3"/>
     </row>
-    <row r="202" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="202">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -6914,7 +6915,7 @@
       <c r="Z202" s="3"/>
       <c r="AA202" s="3"/>
     </row>
-    <row r="203" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="203">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -6943,7 +6944,7 @@
       <c r="Z203" s="3"/>
       <c r="AA203" s="3"/>
     </row>
-    <row r="204" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="204">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -6972,7 +6973,7 @@
       <c r="Z204" s="3"/>
       <c r="AA204" s="3"/>
     </row>
-    <row r="205" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="205">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -7001,7 +7002,7 @@
       <c r="Z205" s="3"/>
       <c r="AA205" s="3"/>
     </row>
-    <row r="206" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="206">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -7030,7 +7031,7 @@
       <c r="Z206" s="3"/>
       <c r="AA206" s="3"/>
     </row>
-    <row r="207" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="207">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -7059,7 +7060,7 @@
       <c r="Z207" s="3"/>
       <c r="AA207" s="3"/>
     </row>
-    <row r="208" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="208">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -7088,7 +7089,7 @@
       <c r="Z208" s="3"/>
       <c r="AA208" s="3"/>
     </row>
-    <row r="209" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="209">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -7117,7 +7118,7 @@
       <c r="Z209" s="3"/>
       <c r="AA209" s="3"/>
     </row>
-    <row r="210" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="210">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -7146,7 +7147,7 @@
       <c r="Z210" s="3"/>
       <c r="AA210" s="3"/>
     </row>
-    <row r="211" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="211">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -7175,7 +7176,7 @@
       <c r="Z211" s="3"/>
       <c r="AA211" s="3"/>
     </row>
-    <row r="212" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="212">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -7204,7 +7205,7 @@
       <c r="Z212" s="3"/>
       <c r="AA212" s="3"/>
     </row>
-    <row r="213" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="213">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -7233,7 +7234,7 @@
       <c r="Z213" s="3"/>
       <c r="AA213" s="3"/>
     </row>
-    <row r="214" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="214">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -7262,7 +7263,7 @@
       <c r="Z214" s="3"/>
       <c r="AA214" s="3"/>
     </row>
-    <row r="215" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="215">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -7291,7 +7292,7 @@
       <c r="Z215" s="3"/>
       <c r="AA215" s="3"/>
     </row>
-    <row r="216" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="216">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -7320,7 +7321,7 @@
       <c r="Z216" s="3"/>
       <c r="AA216" s="3"/>
     </row>
-    <row r="217" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="217">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -7349,7 +7350,7 @@
       <c r="Z217" s="3"/>
       <c r="AA217" s="3"/>
     </row>
-    <row r="218" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="218">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -7378,7 +7379,7 @@
       <c r="Z218" s="3"/>
       <c r="AA218" s="3"/>
     </row>
-    <row r="219" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="219">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -7407,7 +7408,7 @@
       <c r="Z219" s="3"/>
       <c r="AA219" s="3"/>
     </row>
-    <row r="220" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="220">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -7436,7 +7437,7 @@
       <c r="Z220" s="3"/>
       <c r="AA220" s="3"/>
     </row>
-    <row r="221" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="221">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -7465,7 +7466,7 @@
       <c r="Z221" s="3"/>
       <c r="AA221" s="3"/>
     </row>
-    <row r="222" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="222">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -7494,7 +7495,7 @@
       <c r="Z222" s="3"/>
       <c r="AA222" s="3"/>
     </row>
-    <row r="223" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="223">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -7523,7 +7524,7 @@
       <c r="Z223" s="3"/>
       <c r="AA223" s="3"/>
     </row>
-    <row r="224" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="224">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -7552,7 +7553,7 @@
       <c r="Z224" s="3"/>
       <c r="AA224" s="3"/>
     </row>
-    <row r="225" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="225">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -7581,7 +7582,7 @@
       <c r="Z225" s="3"/>
       <c r="AA225" s="3"/>
     </row>
-    <row r="226" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="226">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -7610,7 +7611,7 @@
       <c r="Z226" s="3"/>
       <c r="AA226" s="3"/>
     </row>
-    <row r="227" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="227">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -7639,7 +7640,7 @@
       <c r="Z227" s="3"/>
       <c r="AA227" s="3"/>
     </row>
-    <row r="228" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="228">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -7668,7 +7669,7 @@
       <c r="Z228" s="3"/>
       <c r="AA228" s="3"/>
     </row>
-    <row r="229" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="229">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -7697,7 +7698,7 @@
       <c r="Z229" s="3"/>
       <c r="AA229" s="3"/>
     </row>
-    <row r="230" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="230">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -7726,7 +7727,7 @@
       <c r="Z230" s="3"/>
       <c r="AA230" s="3"/>
     </row>
-    <row r="231" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="231">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -7755,7 +7756,7 @@
       <c r="Z231" s="3"/>
       <c r="AA231" s="3"/>
     </row>
-    <row r="232" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="232">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -7784,7 +7785,7 @@
       <c r="Z232" s="3"/>
       <c r="AA232" s="3"/>
     </row>
-    <row r="233" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="233">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -7813,7 +7814,7 @@
       <c r="Z233" s="3"/>
       <c r="AA233" s="3"/>
     </row>
-    <row r="234" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="234">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -7842,7 +7843,7 @@
       <c r="Z234" s="3"/>
       <c r="AA234" s="3"/>
     </row>
-    <row r="235" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="235">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -7871,7 +7872,7 @@
       <c r="Z235" s="3"/>
       <c r="AA235" s="3"/>
     </row>
-    <row r="236" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="236">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -7900,7 +7901,7 @@
       <c r="Z236" s="3"/>
       <c r="AA236" s="3"/>
     </row>
-    <row r="237" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="237">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -7929,7 +7930,7 @@
       <c r="Z237" s="3"/>
       <c r="AA237" s="3"/>
     </row>
-    <row r="238" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="238">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -7958,7 +7959,7 @@
       <c r="Z238" s="3"/>
       <c r="AA238" s="3"/>
     </row>
-    <row r="239" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="239">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -7987,7 +7988,7 @@
       <c r="Z239" s="3"/>
       <c r="AA239" s="3"/>
     </row>
-    <row r="240" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="240">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -8016,7 +8017,7 @@
       <c r="Z240" s="3"/>
       <c r="AA240" s="3"/>
     </row>
-    <row r="241" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="241">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -8045,7 +8046,7 @@
       <c r="Z241" s="3"/>
       <c r="AA241" s="3"/>
     </row>
-    <row r="242" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="242">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -8074,7 +8075,7 @@
       <c r="Z242" s="3"/>
       <c r="AA242" s="3"/>
     </row>
-    <row r="243" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="243">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -8103,7 +8104,7 @@
       <c r="Z243" s="3"/>
       <c r="AA243" s="3"/>
     </row>
-    <row r="244" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="244">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -8132,7 +8133,7 @@
       <c r="Z244" s="3"/>
       <c r="AA244" s="3"/>
     </row>
-    <row r="245" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="245">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -8161,7 +8162,7 @@
       <c r="Z245" s="3"/>
       <c r="AA245" s="3"/>
     </row>
-    <row r="246" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="246">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -8190,7 +8191,7 @@
       <c r="Z246" s="3"/>
       <c r="AA246" s="3"/>
     </row>
-    <row r="247" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="247">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -8219,7 +8220,7 @@
       <c r="Z247" s="3"/>
       <c r="AA247" s="3"/>
     </row>
-    <row r="248" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="248">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -8248,7 +8249,7 @@
       <c r="Z248" s="3"/>
       <c r="AA248" s="3"/>
     </row>
-    <row r="249" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="249">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -8277,7 +8278,7 @@
       <c r="Z249" s="3"/>
       <c r="AA249" s="3"/>
     </row>
-    <row r="250" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="250">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -8306,7 +8307,7 @@
       <c r="Z250" s="3"/>
       <c r="AA250" s="3"/>
     </row>
-    <row r="251" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="251">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -8335,7 +8336,7 @@
       <c r="Z251" s="3"/>
       <c r="AA251" s="3"/>
     </row>
-    <row r="252" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="252">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -8364,7 +8365,7 @@
       <c r="Z252" s="3"/>
       <c r="AA252" s="3"/>
     </row>
-    <row r="253" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="253">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -8393,7 +8394,7 @@
       <c r="Z253" s="3"/>
       <c r="AA253" s="3"/>
     </row>
-    <row r="254" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="254">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -8422,7 +8423,7 @@
       <c r="Z254" s="3"/>
       <c r="AA254" s="3"/>
     </row>
-    <row r="255" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="255">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -8451,7 +8452,7 @@
       <c r="Z255" s="3"/>
       <c r="AA255" s="3"/>
     </row>
-    <row r="256" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="256">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -8480,7 +8481,7 @@
       <c r="Z256" s="3"/>
       <c r="AA256" s="3"/>
     </row>
-    <row r="257" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="257">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -8509,7 +8510,7 @@
       <c r="Z257" s="3"/>
       <c r="AA257" s="3"/>
     </row>
-    <row r="258" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="258">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -8538,7 +8539,7 @@
       <c r="Z258" s="3"/>
       <c r="AA258" s="3"/>
     </row>
-    <row r="259" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="259">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -8567,7 +8568,7 @@
       <c r="Z259" s="3"/>
       <c r="AA259" s="3"/>
     </row>
-    <row r="260" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="260">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -8596,7 +8597,7 @@
       <c r="Z260" s="3"/>
       <c r="AA260" s="3"/>
     </row>
-    <row r="261" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="261">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -8625,7 +8626,7 @@
       <c r="Z261" s="3"/>
       <c r="AA261" s="3"/>
     </row>
-    <row r="262" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="262">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -8654,7 +8655,7 @@
       <c r="Z262" s="3"/>
       <c r="AA262" s="3"/>
     </row>
-    <row r="263" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="263">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -8683,7 +8684,7 @@
       <c r="Z263" s="3"/>
       <c r="AA263" s="3"/>
     </row>
-    <row r="264" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="264">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -8712,7 +8713,7 @@
       <c r="Z264" s="3"/>
       <c r="AA264" s="3"/>
     </row>
-    <row r="265" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="265">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -8741,7 +8742,7 @@
       <c r="Z265" s="3"/>
       <c r="AA265" s="3"/>
     </row>
-    <row r="266" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="266">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -8770,7 +8771,7 @@
       <c r="Z266" s="3"/>
       <c r="AA266" s="3"/>
     </row>
-    <row r="267" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="267">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -8799,7 +8800,7 @@
       <c r="Z267" s="3"/>
       <c r="AA267" s="3"/>
     </row>
-    <row r="268" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="268">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -8828,7 +8829,7 @@
       <c r="Z268" s="3"/>
       <c r="AA268" s="3"/>
     </row>
-    <row r="269" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="269">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -8857,7 +8858,7 @@
       <c r="Z269" s="3"/>
       <c r="AA269" s="3"/>
     </row>
-    <row r="270" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="270">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -8886,7 +8887,7 @@
       <c r="Z270" s="3"/>
       <c r="AA270" s="3"/>
     </row>
-    <row r="271" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="271">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -8915,7 +8916,7 @@
       <c r="Z271" s="3"/>
       <c r="AA271" s="3"/>
     </row>
-    <row r="272" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="272">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -8944,7 +8945,7 @@
       <c r="Z272" s="3"/>
       <c r="AA272" s="3"/>
     </row>
-    <row r="273" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="273">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -8973,7 +8974,7 @@
       <c r="Z273" s="3"/>
       <c r="AA273" s="3"/>
     </row>
-    <row r="274" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="274">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -9002,7 +9003,7 @@
       <c r="Z274" s="3"/>
       <c r="AA274" s="3"/>
     </row>
-    <row r="275" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="275">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -9031,7 +9032,7 @@
       <c r="Z275" s="3"/>
       <c r="AA275" s="3"/>
     </row>
-    <row r="276" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="276">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -9060,7 +9061,7 @@
       <c r="Z276" s="3"/>
       <c r="AA276" s="3"/>
     </row>
-    <row r="277" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="277">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -9089,7 +9090,7 @@
       <c r="Z277" s="3"/>
       <c r="AA277" s="3"/>
     </row>
-    <row r="278" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="278">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -9118,7 +9119,7 @@
       <c r="Z278" s="3"/>
       <c r="AA278" s="3"/>
     </row>
-    <row r="279" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="279">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -9147,7 +9148,7 @@
       <c r="Z279" s="3"/>
       <c r="AA279" s="3"/>
     </row>
-    <row r="280" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="280">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -9176,7 +9177,7 @@
       <c r="Z280" s="3"/>
       <c r="AA280" s="3"/>
     </row>
-    <row r="281" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="281">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -9205,7 +9206,7 @@
       <c r="Z281" s="3"/>
       <c r="AA281" s="3"/>
     </row>
-    <row r="282" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="282">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -9234,7 +9235,7 @@
       <c r="Z282" s="3"/>
       <c r="AA282" s="3"/>
     </row>
-    <row r="283" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="283">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -9263,7 +9264,7 @@
       <c r="Z283" s="3"/>
       <c r="AA283" s="3"/>
     </row>
-    <row r="284" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="284">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -9292,7 +9293,7 @@
       <c r="Z284" s="3"/>
       <c r="AA284" s="3"/>
     </row>
-    <row r="285" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="285">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -9321,7 +9322,7 @@
       <c r="Z285" s="3"/>
       <c r="AA285" s="3"/>
     </row>
-    <row r="286" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="286">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -9350,7 +9351,7 @@
       <c r="Z286" s="3"/>
       <c r="AA286" s="3"/>
     </row>
-    <row r="287" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="287">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -9379,7 +9380,7 @@
       <c r="Z287" s="3"/>
       <c r="AA287" s="3"/>
     </row>
-    <row r="288" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="288">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -9408,7 +9409,7 @@
       <c r="Z288" s="3"/>
       <c r="AA288" s="3"/>
     </row>
-    <row r="289" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="289">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -9437,7 +9438,7 @@
       <c r="Z289" s="3"/>
       <c r="AA289" s="3"/>
     </row>
-    <row r="290" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="290">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -9466,7 +9467,7 @@
       <c r="Z290" s="3"/>
       <c r="AA290" s="3"/>
     </row>
-    <row r="291" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="291">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -9495,7 +9496,7 @@
       <c r="Z291" s="3"/>
       <c r="AA291" s="3"/>
     </row>
-    <row r="292" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="292">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -9524,7 +9525,7 @@
       <c r="Z292" s="3"/>
       <c r="AA292" s="3"/>
     </row>
-    <row r="293" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="293">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -9553,7 +9554,7 @@
       <c r="Z293" s="3"/>
       <c r="AA293" s="3"/>
     </row>
-    <row r="294" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="294">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -9582,7 +9583,7 @@
       <c r="Z294" s="3"/>
       <c r="AA294" s="3"/>
     </row>
-    <row r="295" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="295">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -9611,7 +9612,7 @@
       <c r="Z295" s="3"/>
       <c r="AA295" s="3"/>
     </row>
-    <row r="296" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="296">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -9640,7 +9641,7 @@
       <c r="Z296" s="3"/>
       <c r="AA296" s="3"/>
     </row>
-    <row r="297" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="297">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -9669,7 +9670,7 @@
       <c r="Z297" s="3"/>
       <c r="AA297" s="3"/>
     </row>
-    <row r="298" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="298">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -9698,7 +9699,7 @@
       <c r="Z298" s="3"/>
       <c r="AA298" s="3"/>
     </row>
-    <row r="299" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="299">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -9727,7 +9728,7 @@
       <c r="Z299" s="3"/>
       <c r="AA299" s="3"/>
     </row>
-    <row r="300" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="300">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -9756,7 +9757,7 @@
       <c r="Z300" s="3"/>
       <c r="AA300" s="3"/>
     </row>
-    <row r="301" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="301">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -9785,7 +9786,7 @@
       <c r="Z301" s="3"/>
       <c r="AA301" s="3"/>
     </row>
-    <row r="302" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="302">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -9814,7 +9815,7 @@
       <c r="Z302" s="3"/>
       <c r="AA302" s="3"/>
     </row>
-    <row r="303" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="303">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -9843,7 +9844,7 @@
       <c r="Z303" s="3"/>
       <c r="AA303" s="3"/>
     </row>
-    <row r="304" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="304">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -9872,7 +9873,7 @@
       <c r="Z304" s="3"/>
       <c r="AA304" s="3"/>
     </row>
-    <row r="305" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="305">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -9901,7 +9902,7 @@
       <c r="Z305" s="3"/>
       <c r="AA305" s="3"/>
     </row>
-    <row r="306" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="306">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -9930,7 +9931,7 @@
       <c r="Z306" s="3"/>
       <c r="AA306" s="3"/>
     </row>
-    <row r="307" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="307">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -9959,7 +9960,7 @@
       <c r="Z307" s="3"/>
       <c r="AA307" s="3"/>
     </row>
-    <row r="308" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="308">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -9988,7 +9989,7 @@
       <c r="Z308" s="3"/>
       <c r="AA308" s="3"/>
     </row>
-    <row r="309" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="309">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -10017,7 +10018,7 @@
       <c r="Z309" s="3"/>
       <c r="AA309" s="3"/>
     </row>
-    <row r="310" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="310">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -10046,7 +10047,7 @@
       <c r="Z310" s="3"/>
       <c r="AA310" s="3"/>
     </row>
-    <row r="311" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="311">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -10075,7 +10076,7 @@
       <c r="Z311" s="3"/>
       <c r="AA311" s="3"/>
     </row>
-    <row r="312" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="312">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -10104,7 +10105,7 @@
       <c r="Z312" s="3"/>
       <c r="AA312" s="3"/>
     </row>
-    <row r="313" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="313">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -10133,7 +10134,7 @@
       <c r="Z313" s="3"/>
       <c r="AA313" s="3"/>
     </row>
-    <row r="314" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="314">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -10162,7 +10163,7 @@
       <c r="Z314" s="3"/>
       <c r="AA314" s="3"/>
     </row>
-    <row r="315" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="315">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -10191,7 +10192,7 @@
       <c r="Z315" s="3"/>
       <c r="AA315" s="3"/>
     </row>
-    <row r="316" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="316">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -10220,7 +10221,7 @@
       <c r="Z316" s="3"/>
       <c r="AA316" s="3"/>
     </row>
-    <row r="317" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="317">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -10249,7 +10250,7 @@
       <c r="Z317" s="3"/>
       <c r="AA317" s="3"/>
     </row>
-    <row r="318" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="318">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -10278,7 +10279,7 @@
       <c r="Z318" s="3"/>
       <c r="AA318" s="3"/>
     </row>
-    <row r="319" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="319">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -10307,7 +10308,7 @@
       <c r="Z319" s="3"/>
       <c r="AA319" s="3"/>
     </row>
-    <row r="320" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="320">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -10336,7 +10337,7 @@
       <c r="Z320" s="3"/>
       <c r="AA320" s="3"/>
     </row>
-    <row r="321" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="321">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -10365,7 +10366,7 @@
       <c r="Z321" s="3"/>
       <c r="AA321" s="3"/>
     </row>
-    <row r="322" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="322">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -10394,7 +10395,7 @@
       <c r="Z322" s="3"/>
       <c r="AA322" s="3"/>
     </row>
-    <row r="323" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="323">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -10423,7 +10424,7 @@
       <c r="Z323" s="3"/>
       <c r="AA323" s="3"/>
     </row>
-    <row r="324" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="324">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -10452,7 +10453,7 @@
       <c r="Z324" s="3"/>
       <c r="AA324" s="3"/>
     </row>
-    <row r="325" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="325">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -10481,7 +10482,7 @@
       <c r="Z325" s="3"/>
       <c r="AA325" s="3"/>
     </row>
-    <row r="326" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="326">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -10510,7 +10511,7 @@
       <c r="Z326" s="3"/>
       <c r="AA326" s="3"/>
     </row>
-    <row r="327" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="327">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -10539,7 +10540,7 @@
       <c r="Z327" s="3"/>
       <c r="AA327" s="3"/>
     </row>
-    <row r="328" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="328">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -10568,7 +10569,7 @@
       <c r="Z328" s="3"/>
       <c r="AA328" s="3"/>
     </row>
-    <row r="329" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="329">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -10597,7 +10598,7 @@
       <c r="Z329" s="3"/>
       <c r="AA329" s="3"/>
     </row>
-    <row r="330" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="330">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -10626,7 +10627,7 @@
       <c r="Z330" s="3"/>
       <c r="AA330" s="3"/>
     </row>
-    <row r="331" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="331">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -10655,7 +10656,7 @@
       <c r="Z331" s="3"/>
       <c r="AA331" s="3"/>
     </row>
-    <row r="332" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="332">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -10684,7 +10685,7 @@
       <c r="Z332" s="3"/>
       <c r="AA332" s="3"/>
     </row>
-    <row r="333" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="333">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -10713,7 +10714,7 @@
       <c r="Z333" s="3"/>
       <c r="AA333" s="3"/>
     </row>
-    <row r="334" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="334">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -10742,7 +10743,7 @@
       <c r="Z334" s="3"/>
       <c r="AA334" s="3"/>
     </row>
-    <row r="335" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="335">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -10771,7 +10772,7 @@
       <c r="Z335" s="3"/>
       <c r="AA335" s="3"/>
     </row>
-    <row r="336" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="336">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -10800,7 +10801,7 @@
       <c r="Z336" s="3"/>
       <c r="AA336" s="3"/>
     </row>
-    <row r="337" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="337">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -10829,7 +10830,7 @@
       <c r="Z337" s="3"/>
       <c r="AA337" s="3"/>
     </row>
-    <row r="338" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="338">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -10858,7 +10859,7 @@
       <c r="Z338" s="3"/>
       <c r="AA338" s="3"/>
     </row>
-    <row r="339" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="339">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -10887,7 +10888,7 @@
       <c r="Z339" s="3"/>
       <c r="AA339" s="3"/>
     </row>
-    <row r="340" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="340">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -10916,7 +10917,7 @@
       <c r="Z340" s="3"/>
       <c r="AA340" s="3"/>
     </row>
-    <row r="341" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="341">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -10945,7 +10946,7 @@
       <c r="Z341" s="3"/>
       <c r="AA341" s="3"/>
     </row>
-    <row r="342" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="342">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -10974,7 +10975,7 @@
       <c r="Z342" s="3"/>
       <c r="AA342" s="3"/>
     </row>
-    <row r="343" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="343">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -11003,7 +11004,7 @@
       <c r="Z343" s="3"/>
       <c r="AA343" s="3"/>
     </row>
-    <row r="344" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="344">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -11032,7 +11033,7 @@
       <c r="Z344" s="3"/>
       <c r="AA344" s="3"/>
     </row>
-    <row r="345" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="345">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -11061,7 +11062,7 @@
       <c r="Z345" s="3"/>
       <c r="AA345" s="3"/>
     </row>
-    <row r="346" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="346">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -11090,7 +11091,7 @@
       <c r="Z346" s="3"/>
       <c r="AA346" s="3"/>
     </row>
-    <row r="347" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="347">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -11119,7 +11120,7 @@
       <c r="Z347" s="3"/>
       <c r="AA347" s="3"/>
     </row>
-    <row r="348" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="348">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -11148,7 +11149,7 @@
       <c r="Z348" s="3"/>
       <c r="AA348" s="3"/>
     </row>
-    <row r="349" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="349">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -11177,7 +11178,7 @@
       <c r="Z349" s="3"/>
       <c r="AA349" s="3"/>
     </row>
-    <row r="350" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="350">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -11206,7 +11207,7 @@
       <c r="Z350" s="3"/>
       <c r="AA350" s="3"/>
     </row>
-    <row r="351" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="351">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -11235,7 +11236,7 @@
       <c r="Z351" s="3"/>
       <c r="AA351" s="3"/>
     </row>
-    <row r="352" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="352">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -11264,7 +11265,7 @@
       <c r="Z352" s="3"/>
       <c r="AA352" s="3"/>
     </row>
-    <row r="353" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="353">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -11293,7 +11294,7 @@
       <c r="Z353" s="3"/>
       <c r="AA353" s="3"/>
     </row>
-    <row r="354" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="354">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -11322,7 +11323,7 @@
       <c r="Z354" s="3"/>
       <c r="AA354" s="3"/>
     </row>
-    <row r="355" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="355">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -11351,7 +11352,7 @@
       <c r="Z355" s="3"/>
       <c r="AA355" s="3"/>
     </row>
-    <row r="356" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="356">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -11380,7 +11381,7 @@
       <c r="Z356" s="3"/>
       <c r="AA356" s="3"/>
     </row>
-    <row r="357" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="357">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -11409,7 +11410,7 @@
       <c r="Z357" s="3"/>
       <c r="AA357" s="3"/>
     </row>
-    <row r="358" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="358">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -11438,7 +11439,7 @@
       <c r="Z358" s="3"/>
       <c r="AA358" s="3"/>
     </row>
-    <row r="359" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="359">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -11467,7 +11468,7 @@
       <c r="Z359" s="3"/>
       <c r="AA359" s="3"/>
     </row>
-    <row r="360" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="360">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -11496,7 +11497,7 @@
       <c r="Z360" s="3"/>
       <c r="AA360" s="3"/>
     </row>
-    <row r="361" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="361">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -11525,7 +11526,7 @@
       <c r="Z361" s="3"/>
       <c r="AA361" s="3"/>
     </row>
-    <row r="362" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="362">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -11554,7 +11555,7 @@
       <c r="Z362" s="3"/>
       <c r="AA362" s="3"/>
     </row>
-    <row r="363" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="363">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -11583,7 +11584,7 @@
       <c r="Z363" s="3"/>
       <c r="AA363" s="3"/>
     </row>
-    <row r="364" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="364">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -11612,7 +11613,7 @@
       <c r="Z364" s="3"/>
       <c r="AA364" s="3"/>
     </row>
-    <row r="365" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="365">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -11641,7 +11642,7 @@
       <c r="Z365" s="3"/>
       <c r="AA365" s="3"/>
     </row>
-    <row r="366" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="366">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -11670,7 +11671,7 @@
       <c r="Z366" s="3"/>
       <c r="AA366" s="3"/>
     </row>
-    <row r="367" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="367">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -11699,7 +11700,7 @@
       <c r="Z367" s="3"/>
       <c r="AA367" s="3"/>
     </row>
-    <row r="368" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="368">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -11728,7 +11729,7 @@
       <c r="Z368" s="3"/>
       <c r="AA368" s="3"/>
     </row>
-    <row r="369" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="369">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -11757,7 +11758,7 @@
       <c r="Z369" s="3"/>
       <c r="AA369" s="3"/>
     </row>
-    <row r="370" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="370">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -11786,7 +11787,7 @@
       <c r="Z370" s="3"/>
       <c r="AA370" s="3"/>
     </row>
-    <row r="371" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="371">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -11815,7 +11816,7 @@
       <c r="Z371" s="3"/>
       <c r="AA371" s="3"/>
     </row>
-    <row r="372" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="372">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -11844,7 +11845,7 @@
       <c r="Z372" s="3"/>
       <c r="AA372" s="3"/>
     </row>
-    <row r="373" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="373">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -11873,7 +11874,7 @@
       <c r="Z373" s="3"/>
       <c r="AA373" s="3"/>
     </row>
-    <row r="374" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="374">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -11902,7 +11903,7 @@
       <c r="Z374" s="3"/>
       <c r="AA374" s="3"/>
     </row>
-    <row r="375" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="375">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -11931,7 +11932,7 @@
       <c r="Z375" s="3"/>
       <c r="AA375" s="3"/>
     </row>
-    <row r="376" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="376">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -11960,7 +11961,7 @@
       <c r="Z376" s="3"/>
       <c r="AA376" s="3"/>
     </row>
-    <row r="377" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="377">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -11989,7 +11990,7 @@
       <c r="Z377" s="3"/>
       <c r="AA377" s="3"/>
     </row>
-    <row r="378" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="378">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -12018,7 +12019,7 @@
       <c r="Z378" s="3"/>
       <c r="AA378" s="3"/>
     </row>
-    <row r="379" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="379">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -12047,7 +12048,7 @@
       <c r="Z379" s="3"/>
       <c r="AA379" s="3"/>
     </row>
-    <row r="380" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="380">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -12076,7 +12077,7 @@
       <c r="Z380" s="3"/>
       <c r="AA380" s="3"/>
     </row>
-    <row r="381" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="381">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -12105,7 +12106,7 @@
       <c r="Z381" s="3"/>
       <c r="AA381" s="3"/>
     </row>
-    <row r="382" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="382">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -12134,7 +12135,7 @@
       <c r="Z382" s="3"/>
       <c r="AA382" s="3"/>
     </row>
-    <row r="383" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="383">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -12163,7 +12164,7 @@
       <c r="Z383" s="3"/>
       <c r="AA383" s="3"/>
     </row>
-    <row r="384" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="384">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -12192,7 +12193,7 @@
       <c r="Z384" s="3"/>
       <c r="AA384" s="3"/>
     </row>
-    <row r="385" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="385">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -12221,7 +12222,7 @@
       <c r="Z385" s="3"/>
       <c r="AA385" s="3"/>
     </row>
-    <row r="386" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="386">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -12250,7 +12251,7 @@
       <c r="Z386" s="3"/>
       <c r="AA386" s="3"/>
     </row>
-    <row r="387" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="387">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -12279,7 +12280,7 @@
       <c r="Z387" s="3"/>
       <c r="AA387" s="3"/>
     </row>
-    <row r="388" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="388">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -12308,7 +12309,7 @@
       <c r="Z388" s="3"/>
       <c r="AA388" s="3"/>
     </row>
-    <row r="389" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="389">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -12337,7 +12338,7 @@
       <c r="Z389" s="3"/>
       <c r="AA389" s="3"/>
     </row>
-    <row r="390" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="390">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -12366,7 +12367,7 @@
       <c r="Z390" s="3"/>
       <c r="AA390" s="3"/>
     </row>
-    <row r="391" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="391">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -12395,7 +12396,7 @@
       <c r="Z391" s="3"/>
       <c r="AA391" s="3"/>
     </row>
-    <row r="392" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="392">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -12424,7 +12425,7 @@
       <c r="Z392" s="3"/>
       <c r="AA392" s="3"/>
     </row>
-    <row r="393" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="393">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -12453,7 +12454,7 @@
       <c r="Z393" s="3"/>
       <c r="AA393" s="3"/>
     </row>
-    <row r="394" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="394">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -12482,7 +12483,7 @@
       <c r="Z394" s="3"/>
       <c r="AA394" s="3"/>
     </row>
-    <row r="395" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="395">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -12511,7 +12512,7 @@
       <c r="Z395" s="3"/>
       <c r="AA395" s="3"/>
     </row>
-    <row r="396" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="396">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -12540,7 +12541,7 @@
       <c r="Z396" s="3"/>
       <c r="AA396" s="3"/>
     </row>
-    <row r="397" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="397">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -12569,7 +12570,7 @@
       <c r="Z397" s="3"/>
       <c r="AA397" s="3"/>
     </row>
-    <row r="398" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="398">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -12598,7 +12599,7 @@
       <c r="Z398" s="3"/>
       <c r="AA398" s="3"/>
     </row>
-    <row r="399" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="399">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -12627,7 +12628,7 @@
       <c r="Z399" s="3"/>
       <c r="AA399" s="3"/>
     </row>
-    <row r="400" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="400">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -12656,7 +12657,7 @@
       <c r="Z400" s="3"/>
       <c r="AA400" s="3"/>
     </row>
-    <row r="401" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="401">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -12685,7 +12686,7 @@
       <c r="Z401" s="3"/>
       <c r="AA401" s="3"/>
     </row>
-    <row r="402" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="402">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -12714,7 +12715,7 @@
       <c r="Z402" s="3"/>
       <c r="AA402" s="3"/>
     </row>
-    <row r="403" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="403">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -12743,7 +12744,7 @@
       <c r="Z403" s="3"/>
       <c r="AA403" s="3"/>
     </row>
-    <row r="404" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="404">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -12772,7 +12773,7 @@
       <c r="Z404" s="3"/>
       <c r="AA404" s="3"/>
     </row>
-    <row r="405" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="405">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -12801,7 +12802,7 @@
       <c r="Z405" s="3"/>
       <c r="AA405" s="3"/>
     </row>
-    <row r="406" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="406">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -12830,7 +12831,7 @@
       <c r="Z406" s="3"/>
       <c r="AA406" s="3"/>
     </row>
-    <row r="407" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="407">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -12859,7 +12860,7 @@
       <c r="Z407" s="3"/>
       <c r="AA407" s="3"/>
     </row>
-    <row r="408" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="408">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -12888,7 +12889,7 @@
       <c r="Z408" s="3"/>
       <c r="AA408" s="3"/>
     </row>
-    <row r="409" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="409">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -12917,7 +12918,7 @@
       <c r="Z409" s="3"/>
       <c r="AA409" s="3"/>
     </row>
-    <row r="410" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="410">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -12946,7 +12947,7 @@
       <c r="Z410" s="3"/>
       <c r="AA410" s="3"/>
     </row>
-    <row r="411" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="411">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -12975,7 +12976,7 @@
       <c r="Z411" s="3"/>
       <c r="AA411" s="3"/>
     </row>
-    <row r="412" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="412">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -13004,7 +13005,7 @@
       <c r="Z412" s="3"/>
       <c r="AA412" s="3"/>
     </row>
-    <row r="413" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="413">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -13033,7 +13034,7 @@
       <c r="Z413" s="3"/>
       <c r="AA413" s="3"/>
     </row>
-    <row r="414" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="414">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -13062,7 +13063,7 @@
       <c r="Z414" s="3"/>
       <c r="AA414" s="3"/>
     </row>
-    <row r="415" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="415">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -13091,7 +13092,7 @@
       <c r="Z415" s="3"/>
       <c r="AA415" s="3"/>
     </row>
-    <row r="416" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="416">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -13120,7 +13121,7 @@
       <c r="Z416" s="3"/>
       <c r="AA416" s="3"/>
     </row>
-    <row r="417" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="417">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -13149,7 +13150,7 @@
       <c r="Z417" s="3"/>
       <c r="AA417" s="3"/>
     </row>
-    <row r="418" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="418">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -13178,7 +13179,7 @@
       <c r="Z418" s="3"/>
       <c r="AA418" s="3"/>
     </row>
-    <row r="419" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="419">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -13207,7 +13208,7 @@
       <c r="Z419" s="3"/>
       <c r="AA419" s="3"/>
     </row>
-    <row r="420" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="420">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -13236,7 +13237,7 @@
       <c r="Z420" s="3"/>
       <c r="AA420" s="3"/>
     </row>
-    <row r="421" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="421">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -13265,7 +13266,7 @@
       <c r="Z421" s="3"/>
       <c r="AA421" s="3"/>
     </row>
-    <row r="422" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="422">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -13294,7 +13295,7 @@
       <c r="Z422" s="3"/>
       <c r="AA422" s="3"/>
     </row>
-    <row r="423" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="423">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -13323,7 +13324,7 @@
       <c r="Z423" s="3"/>
       <c r="AA423" s="3"/>
     </row>
-    <row r="424" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="424">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -13352,7 +13353,7 @@
       <c r="Z424" s="3"/>
       <c r="AA424" s="3"/>
     </row>
-    <row r="425" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="425">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -13381,7 +13382,7 @@
       <c r="Z425" s="3"/>
       <c r="AA425" s="3"/>
     </row>
-    <row r="426" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="426">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -13410,7 +13411,7 @@
       <c r="Z426" s="3"/>
       <c r="AA426" s="3"/>
     </row>
-    <row r="427" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="427">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -13439,7 +13440,7 @@
       <c r="Z427" s="3"/>
       <c r="AA427" s="3"/>
     </row>
-    <row r="428" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="428">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -13468,7 +13469,7 @@
       <c r="Z428" s="3"/>
       <c r="AA428" s="3"/>
     </row>
-    <row r="429" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="429">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -13497,7 +13498,7 @@
       <c r="Z429" s="3"/>
       <c r="AA429" s="3"/>
     </row>
-    <row r="430" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="430">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -13526,7 +13527,7 @@
       <c r="Z430" s="3"/>
       <c r="AA430" s="3"/>
     </row>
-    <row r="431" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="431">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -13555,7 +13556,7 @@
       <c r="Z431" s="3"/>
       <c r="AA431" s="3"/>
     </row>
-    <row r="432" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="432">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -13584,7 +13585,7 @@
       <c r="Z432" s="3"/>
       <c r="AA432" s="3"/>
     </row>
-    <row r="433" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="433">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -13613,7 +13614,7 @@
       <c r="Z433" s="3"/>
       <c r="AA433" s="3"/>
     </row>
-    <row r="434" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="434">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -13642,7 +13643,7 @@
       <c r="Z434" s="3"/>
       <c r="AA434" s="3"/>
     </row>
-    <row r="435" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="435">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -13671,7 +13672,7 @@
       <c r="Z435" s="3"/>
       <c r="AA435" s="3"/>
     </row>
-    <row r="436" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="436">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -13700,7 +13701,7 @@
       <c r="Z436" s="3"/>
       <c r="AA436" s="3"/>
     </row>
-    <row r="437" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="437">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -13729,7 +13730,7 @@
       <c r="Z437" s="3"/>
       <c r="AA437" s="3"/>
     </row>
-    <row r="438" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="438">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -13758,7 +13759,7 @@
       <c r="Z438" s="3"/>
       <c r="AA438" s="3"/>
     </row>
-    <row r="439" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="439">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -13787,7 +13788,7 @@
       <c r="Z439" s="3"/>
       <c r="AA439" s="3"/>
     </row>
-    <row r="440" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="440">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -13816,7 +13817,7 @@
       <c r="Z440" s="3"/>
       <c r="AA440" s="3"/>
     </row>
-    <row r="441" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="441">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -13845,7 +13846,7 @@
       <c r="Z441" s="3"/>
       <c r="AA441" s="3"/>
     </row>
-    <row r="442" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="442">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -13874,7 +13875,7 @@
       <c r="Z442" s="3"/>
       <c r="AA442" s="3"/>
     </row>
-    <row r="443" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="443">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -13903,7 +13904,7 @@
       <c r="Z443" s="3"/>
       <c r="AA443" s="3"/>
     </row>
-    <row r="444" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="444">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -13932,7 +13933,7 @@
       <c r="Z444" s="3"/>
       <c r="AA444" s="3"/>
     </row>
-    <row r="445" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="445">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -13961,7 +13962,7 @@
       <c r="Z445" s="3"/>
       <c r="AA445" s="3"/>
     </row>
-    <row r="446" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="446">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -13990,7 +13991,7 @@
       <c r="Z446" s="3"/>
       <c r="AA446" s="3"/>
     </row>
-    <row r="447" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="447">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -14019,7 +14020,7 @@
       <c r="Z447" s="3"/>
       <c r="AA447" s="3"/>
     </row>
-    <row r="448" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="448">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -14048,7 +14049,7 @@
       <c r="Z448" s="3"/>
       <c r="AA448" s="3"/>
     </row>
-    <row r="449" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="449">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -14077,7 +14078,7 @@
       <c r="Z449" s="3"/>
       <c r="AA449" s="3"/>
     </row>
-    <row r="450" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="450">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -14106,7 +14107,7 @@
       <c r="Z450" s="3"/>
       <c r="AA450" s="3"/>
     </row>
-    <row r="451" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="451">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -14135,7 +14136,7 @@
       <c r="Z451" s="3"/>
       <c r="AA451" s="3"/>
     </row>
-    <row r="452" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="452">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -14164,7 +14165,7 @@
       <c r="Z452" s="3"/>
       <c r="AA452" s="3"/>
     </row>
-    <row r="453" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="453">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -14193,7 +14194,7 @@
       <c r="Z453" s="3"/>
       <c r="AA453" s="3"/>
     </row>
-    <row r="454" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="454">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -14222,7 +14223,7 @@
       <c r="Z454" s="3"/>
       <c r="AA454" s="3"/>
     </row>
-    <row r="455" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="455">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -14251,7 +14252,7 @@
       <c r="Z455" s="3"/>
       <c r="AA455" s="3"/>
     </row>
-    <row r="456" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="456">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -14280,7 +14281,7 @@
       <c r="Z456" s="3"/>
       <c r="AA456" s="3"/>
     </row>
-    <row r="457" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="457">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -14309,7 +14310,7 @@
       <c r="Z457" s="3"/>
       <c r="AA457" s="3"/>
     </row>
-    <row r="458" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="458">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -14338,7 +14339,7 @@
       <c r="Z458" s="3"/>
       <c r="AA458" s="3"/>
     </row>
-    <row r="459" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="459">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -14367,7 +14368,7 @@
       <c r="Z459" s="3"/>
       <c r="AA459" s="3"/>
     </row>
-    <row r="460" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="460">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -14396,7 +14397,7 @@
       <c r="Z460" s="3"/>
       <c r="AA460" s="3"/>
     </row>
-    <row r="461" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="461">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -14425,7 +14426,7 @@
       <c r="Z461" s="3"/>
       <c r="AA461" s="3"/>
     </row>
-    <row r="462" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="462">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -14454,7 +14455,7 @@
       <c r="Z462" s="3"/>
       <c r="AA462" s="3"/>
     </row>
-    <row r="463" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="463">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -14483,7 +14484,7 @@
       <c r="Z463" s="3"/>
       <c r="AA463" s="3"/>
     </row>
-    <row r="464" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="464">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -14512,7 +14513,7 @@
       <c r="Z464" s="3"/>
       <c r="AA464" s="3"/>
     </row>
-    <row r="465" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="465">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -14541,7 +14542,7 @@
       <c r="Z465" s="3"/>
       <c r="AA465" s="3"/>
     </row>
-    <row r="466" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="466">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -14570,7 +14571,7 @@
       <c r="Z466" s="3"/>
       <c r="AA466" s="3"/>
     </row>
-    <row r="467" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="467">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -14599,7 +14600,7 @@
       <c r="Z467" s="3"/>
       <c r="AA467" s="3"/>
     </row>
-    <row r="468" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="468">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -14628,7 +14629,7 @@
       <c r="Z468" s="3"/>
       <c r="AA468" s="3"/>
     </row>
-    <row r="469" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="469">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -14657,7 +14658,7 @@
       <c r="Z469" s="3"/>
       <c r="AA469" s="3"/>
     </row>
-    <row r="470" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="470">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -14686,7 +14687,7 @@
       <c r="Z470" s="3"/>
       <c r="AA470" s="3"/>
     </row>
-    <row r="471" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="471">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -14715,7 +14716,7 @@
       <c r="Z471" s="3"/>
       <c r="AA471" s="3"/>
     </row>
-    <row r="472" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="472">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -14744,7 +14745,7 @@
       <c r="Z472" s="3"/>
       <c r="AA472" s="3"/>
     </row>
-    <row r="473" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="473">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -14773,7 +14774,7 @@
       <c r="Z473" s="3"/>
       <c r="AA473" s="3"/>
     </row>
-    <row r="474" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="474">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -14802,7 +14803,7 @@
       <c r="Z474" s="3"/>
       <c r="AA474" s="3"/>
     </row>
-    <row r="475" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="475">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -14831,7 +14832,7 @@
       <c r="Z475" s="3"/>
       <c r="AA475" s="3"/>
     </row>
-    <row r="476" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="476">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -14860,7 +14861,7 @@
       <c r="Z476" s="3"/>
       <c r="AA476" s="3"/>
     </row>
-    <row r="477" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="477">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -14889,7 +14890,7 @@
       <c r="Z477" s="3"/>
       <c r="AA477" s="3"/>
     </row>
-    <row r="478" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="478">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -14918,7 +14919,7 @@
       <c r="Z478" s="3"/>
       <c r="AA478" s="3"/>
     </row>
-    <row r="479" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="479">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -14947,7 +14948,7 @@
       <c r="Z479" s="3"/>
       <c r="AA479" s="3"/>
     </row>
-    <row r="480" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="480">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -14976,7 +14977,7 @@
       <c r="Z480" s="3"/>
       <c r="AA480" s="3"/>
     </row>
-    <row r="481" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="481">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -15005,7 +15006,7 @@
       <c r="Z481" s="3"/>
       <c r="AA481" s="3"/>
     </row>
-    <row r="482" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="482">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -15034,7 +15035,7 @@
       <c r="Z482" s="3"/>
       <c r="AA482" s="3"/>
     </row>
-    <row r="483" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="483">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -15063,7 +15064,7 @@
       <c r="Z483" s="3"/>
       <c r="AA483" s="3"/>
     </row>
-    <row r="484" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="484">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -15092,7 +15093,7 @@
       <c r="Z484" s="3"/>
       <c r="AA484" s="3"/>
     </row>
-    <row r="485" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="485">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -15121,7 +15122,7 @@
       <c r="Z485" s="3"/>
       <c r="AA485" s="3"/>
     </row>
-    <row r="486" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="486">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -15150,7 +15151,7 @@
       <c r="Z486" s="3"/>
       <c r="AA486" s="3"/>
     </row>
-    <row r="487" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="487">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -15179,7 +15180,7 @@
       <c r="Z487" s="3"/>
       <c r="AA487" s="3"/>
     </row>
-    <row r="488" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="488">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -15208,7 +15209,7 @@
       <c r="Z488" s="3"/>
       <c r="AA488" s="3"/>
     </row>
-    <row r="489" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="489">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -15237,7 +15238,7 @@
       <c r="Z489" s="3"/>
       <c r="AA489" s="3"/>
     </row>
-    <row r="490" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="490">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -15266,7 +15267,7 @@
       <c r="Z490" s="3"/>
       <c r="AA490" s="3"/>
     </row>
-    <row r="491" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="491">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -15295,7 +15296,7 @@
       <c r="Z491" s="3"/>
       <c r="AA491" s="3"/>
     </row>
-    <row r="492" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="492">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -15324,7 +15325,7 @@
       <c r="Z492" s="3"/>
       <c r="AA492" s="3"/>
     </row>
-    <row r="493" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="493">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -15353,7 +15354,7 @@
       <c r="Z493" s="3"/>
       <c r="AA493" s="3"/>
     </row>
-    <row r="494" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="494">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -15382,7 +15383,7 @@
       <c r="Z494" s="3"/>
       <c r="AA494" s="3"/>
     </row>
-    <row r="495" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="495">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -15411,7 +15412,7 @@
       <c r="Z495" s="3"/>
       <c r="AA495" s="3"/>
     </row>
-    <row r="496" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="496">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -15440,7 +15441,7 @@
       <c r="Z496" s="3"/>
       <c r="AA496" s="3"/>
     </row>
-    <row r="497" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="497">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -15469,7 +15470,7 @@
       <c r="Z497" s="3"/>
       <c r="AA497" s="3"/>
     </row>
-    <row r="498" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="498">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -15498,7 +15499,7 @@
       <c r="Z498" s="3"/>
       <c r="AA498" s="3"/>
     </row>
-    <row r="499" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="499">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -15527,7 +15528,7 @@
       <c r="Z499" s="3"/>
       <c r="AA499" s="3"/>
     </row>
-    <row r="500" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="500">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -15556,7 +15557,7 @@
       <c r="Z500" s="3"/>
       <c r="AA500" s="3"/>
     </row>
-    <row r="501" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="501">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -15585,7 +15586,7 @@
       <c r="Z501" s="3"/>
       <c r="AA501" s="3"/>
     </row>
-    <row r="502" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="502">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -15614,7 +15615,7 @@
       <c r="Z502" s="3"/>
       <c r="AA502" s="3"/>
     </row>
-    <row r="503" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="503">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -15643,7 +15644,7 @@
       <c r="Z503" s="3"/>
       <c r="AA503" s="3"/>
     </row>
-    <row r="504" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="504">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -15672,7 +15673,7 @@
       <c r="Z504" s="3"/>
       <c r="AA504" s="3"/>
     </row>
-    <row r="505" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="505">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -15701,7 +15702,7 @@
       <c r="Z505" s="3"/>
       <c r="AA505" s="3"/>
     </row>
-    <row r="506" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="506">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -15730,7 +15731,7 @@
       <c r="Z506" s="3"/>
       <c r="AA506" s="3"/>
     </row>
-    <row r="507" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="507">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -15759,7 +15760,7 @@
       <c r="Z507" s="3"/>
       <c r="AA507" s="3"/>
     </row>
-    <row r="508" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="508">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -15788,7 +15789,7 @@
       <c r="Z508" s="3"/>
       <c r="AA508" s="3"/>
     </row>
-    <row r="509" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="509">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -15817,7 +15818,7 @@
       <c r="Z509" s="3"/>
       <c r="AA509" s="3"/>
     </row>
-    <row r="510" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="510">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -15846,7 +15847,7 @@
       <c r="Z510" s="3"/>
       <c r="AA510" s="3"/>
     </row>
-    <row r="511" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="511">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -15875,7 +15876,7 @@
       <c r="Z511" s="3"/>
       <c r="AA511" s="3"/>
     </row>
-    <row r="512" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="512">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -15904,7 +15905,7 @@
       <c r="Z512" s="3"/>
       <c r="AA512" s="3"/>
     </row>
-    <row r="513" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="513">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -15933,7 +15934,7 @@
       <c r="Z513" s="3"/>
       <c r="AA513" s="3"/>
     </row>
-    <row r="514" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="514">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -15962,7 +15963,7 @@
       <c r="Z514" s="3"/>
       <c r="AA514" s="3"/>
     </row>
-    <row r="515" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="515">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -15991,7 +15992,7 @@
       <c r="Z515" s="3"/>
       <c r="AA515" s="3"/>
     </row>
-    <row r="516" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="516">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -16020,7 +16021,7 @@
       <c r="Z516" s="3"/>
       <c r="AA516" s="3"/>
     </row>
-    <row r="517" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="517">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -16049,7 +16050,7 @@
       <c r="Z517" s="3"/>
       <c r="AA517" s="3"/>
     </row>
-    <row r="518" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="518">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -16078,7 +16079,7 @@
       <c r="Z518" s="3"/>
       <c r="AA518" s="3"/>
     </row>
-    <row r="519" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="519">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -16107,7 +16108,7 @@
       <c r="Z519" s="3"/>
       <c r="AA519" s="3"/>
     </row>
-    <row r="520" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="520">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -16136,7 +16137,7 @@
       <c r="Z520" s="3"/>
       <c r="AA520" s="3"/>
     </row>
-    <row r="521" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="521">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -16165,7 +16166,7 @@
       <c r="Z521" s="3"/>
       <c r="AA521" s="3"/>
     </row>
-    <row r="522" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="522">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -16194,7 +16195,7 @@
       <c r="Z522" s="3"/>
       <c r="AA522" s="3"/>
     </row>
-    <row r="523" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="523">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -16223,7 +16224,7 @@
       <c r="Z523" s="3"/>
       <c r="AA523" s="3"/>
     </row>
-    <row r="524" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="524">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -16252,7 +16253,7 @@
       <c r="Z524" s="3"/>
       <c r="AA524" s="3"/>
     </row>
-    <row r="525" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="525">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -16281,7 +16282,7 @@
       <c r="Z525" s="3"/>
       <c r="AA525" s="3"/>
     </row>
-    <row r="526" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="526">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -16310,7 +16311,7 @@
       <c r="Z526" s="3"/>
       <c r="AA526" s="3"/>
     </row>
-    <row r="527" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="527">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -16339,7 +16340,7 @@
       <c r="Z527" s="3"/>
       <c r="AA527" s="3"/>
     </row>
-    <row r="528" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="528">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -16368,7 +16369,7 @@
       <c r="Z528" s="3"/>
       <c r="AA528" s="3"/>
     </row>
-    <row r="529" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="529">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -16397,7 +16398,7 @@
       <c r="Z529" s="3"/>
       <c r="AA529" s="3"/>
     </row>
-    <row r="530" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="530">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -16426,7 +16427,7 @@
       <c r="Z530" s="3"/>
       <c r="AA530" s="3"/>
     </row>
-    <row r="531" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="531">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -16455,7 +16456,7 @@
       <c r="Z531" s="3"/>
       <c r="AA531" s="3"/>
     </row>
-    <row r="532" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="532">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -16484,7 +16485,7 @@
       <c r="Z532" s="3"/>
       <c r="AA532" s="3"/>
     </row>
-    <row r="533" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="533">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -16513,7 +16514,7 @@
       <c r="Z533" s="3"/>
       <c r="AA533" s="3"/>
     </row>
-    <row r="534" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="534">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -16542,7 +16543,7 @@
       <c r="Z534" s="3"/>
       <c r="AA534" s="3"/>
     </row>
-    <row r="535" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="535">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -16571,7 +16572,7 @@
       <c r="Z535" s="3"/>
       <c r="AA535" s="3"/>
     </row>
-    <row r="536" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="536">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -16600,7 +16601,7 @@
       <c r="Z536" s="3"/>
       <c r="AA536" s="3"/>
     </row>
-    <row r="537" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="537">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -16629,7 +16630,7 @@
       <c r="Z537" s="3"/>
       <c r="AA537" s="3"/>
     </row>
-    <row r="538" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="538">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -16658,7 +16659,7 @@
       <c r="Z538" s="3"/>
       <c r="AA538" s="3"/>
     </row>
-    <row r="539" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="539">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -16687,7 +16688,7 @@
       <c r="Z539" s="3"/>
       <c r="AA539" s="3"/>
     </row>
-    <row r="540" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="540">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -16716,7 +16717,7 @@
       <c r="Z540" s="3"/>
       <c r="AA540" s="3"/>
     </row>
-    <row r="541" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="541">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -16745,7 +16746,7 @@
       <c r="Z541" s="3"/>
       <c r="AA541" s="3"/>
     </row>
-    <row r="542" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="542">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -16774,7 +16775,7 @@
       <c r="Z542" s="3"/>
       <c r="AA542" s="3"/>
     </row>
-    <row r="543" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="543">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -16803,7 +16804,7 @@
       <c r="Z543" s="3"/>
       <c r="AA543" s="3"/>
     </row>
-    <row r="544" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="544">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -16832,7 +16833,7 @@
       <c r="Z544" s="3"/>
       <c r="AA544" s="3"/>
     </row>
-    <row r="545" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="545">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -16861,7 +16862,7 @@
       <c r="Z545" s="3"/>
       <c r="AA545" s="3"/>
     </row>
-    <row r="546" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="546">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -16890,7 +16891,7 @@
       <c r="Z546" s="3"/>
       <c r="AA546" s="3"/>
     </row>
-    <row r="547" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="547">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -16919,7 +16920,7 @@
       <c r="Z547" s="3"/>
       <c r="AA547" s="3"/>
     </row>
-    <row r="548" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="548">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -16948,7 +16949,7 @@
       <c r="Z548" s="3"/>
       <c r="AA548" s="3"/>
     </row>
-    <row r="549" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="549">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -16977,7 +16978,7 @@
       <c r="Z549" s="3"/>
       <c r="AA549" s="3"/>
     </row>
-    <row r="550" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="550">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -17006,7 +17007,7 @@
       <c r="Z550" s="3"/>
       <c r="AA550" s="3"/>
     </row>
-    <row r="551" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="551">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -17035,7 +17036,7 @@
       <c r="Z551" s="3"/>
       <c r="AA551" s="3"/>
     </row>
-    <row r="552" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="552">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -17064,7 +17065,7 @@
       <c r="Z552" s="3"/>
       <c r="AA552" s="3"/>
     </row>
-    <row r="553" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="553">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -17093,7 +17094,7 @@
       <c r="Z553" s="3"/>
       <c r="AA553" s="3"/>
     </row>
-    <row r="554" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="554">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -17122,7 +17123,7 @@
       <c r="Z554" s="3"/>
       <c r="AA554" s="3"/>
     </row>
-    <row r="555" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="555">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -17151,7 +17152,7 @@
       <c r="Z555" s="3"/>
       <c r="AA555" s="3"/>
     </row>
-    <row r="556" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="556">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -17180,7 +17181,7 @@
       <c r="Z556" s="3"/>
       <c r="AA556" s="3"/>
     </row>
-    <row r="557" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="557">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -17209,7 +17210,7 @@
       <c r="Z557" s="3"/>
       <c r="AA557" s="3"/>
     </row>
-    <row r="558" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="558">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -17238,7 +17239,7 @@
       <c r="Z558" s="3"/>
       <c r="AA558" s="3"/>
     </row>
-    <row r="559" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="559">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -17267,7 +17268,7 @@
       <c r="Z559" s="3"/>
       <c r="AA559" s="3"/>
     </row>
-    <row r="560" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="560">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -17296,7 +17297,7 @@
       <c r="Z560" s="3"/>
       <c r="AA560" s="3"/>
     </row>
-    <row r="561" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="561">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -17325,7 +17326,7 @@
       <c r="Z561" s="3"/>
       <c r="AA561" s="3"/>
     </row>
-    <row r="562" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="562">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -17354,7 +17355,7 @@
       <c r="Z562" s="3"/>
       <c r="AA562" s="3"/>
     </row>
-    <row r="563" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="563">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -17383,7 +17384,7 @@
       <c r="Z563" s="3"/>
       <c r="AA563" s="3"/>
     </row>
-    <row r="564" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="564">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -17412,7 +17413,7 @@
       <c r="Z564" s="3"/>
       <c r="AA564" s="3"/>
     </row>
-    <row r="565" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="565">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -17441,7 +17442,7 @@
       <c r="Z565" s="3"/>
       <c r="AA565" s="3"/>
     </row>
-    <row r="566" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="566">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -17470,7 +17471,7 @@
       <c r="Z566" s="3"/>
       <c r="AA566" s="3"/>
     </row>
-    <row r="567" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="567">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -17499,7 +17500,7 @@
       <c r="Z567" s="3"/>
       <c r="AA567" s="3"/>
     </row>
-    <row r="568" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="568">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -17528,7 +17529,7 @@
       <c r="Z568" s="3"/>
       <c r="AA568" s="3"/>
     </row>
-    <row r="569" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="569">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -17557,7 +17558,7 @@
       <c r="Z569" s="3"/>
       <c r="AA569" s="3"/>
     </row>
-    <row r="570" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="570">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -17586,7 +17587,7 @@
       <c r="Z570" s="3"/>
       <c r="AA570" s="3"/>
     </row>
-    <row r="571" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="571">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -17615,7 +17616,7 @@
       <c r="Z571" s="3"/>
       <c r="AA571" s="3"/>
     </row>
-    <row r="572" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="572">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -17644,7 +17645,7 @@
       <c r="Z572" s="3"/>
       <c r="AA572" s="3"/>
     </row>
-    <row r="573" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="573">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -17673,7 +17674,7 @@
       <c r="Z573" s="3"/>
       <c r="AA573" s="3"/>
     </row>
-    <row r="574" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="574">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -17702,7 +17703,7 @@
       <c r="Z574" s="3"/>
       <c r="AA574" s="3"/>
     </row>
-    <row r="575" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="575">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -17731,7 +17732,7 @@
       <c r="Z575" s="3"/>
       <c r="AA575" s="3"/>
     </row>
-    <row r="576" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="576">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -17760,7 +17761,7 @@
       <c r="Z576" s="3"/>
       <c r="AA576" s="3"/>
     </row>
-    <row r="577" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="577">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -17789,7 +17790,7 @@
       <c r="Z577" s="3"/>
       <c r="AA577" s="3"/>
     </row>
-    <row r="578" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="578">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -17818,7 +17819,7 @@
       <c r="Z578" s="3"/>
       <c r="AA578" s="3"/>
     </row>
-    <row r="579" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="579">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -17847,7 +17848,7 @@
       <c r="Z579" s="3"/>
       <c r="AA579" s="3"/>
     </row>
-    <row r="580" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="580">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -17876,7 +17877,7 @@
       <c r="Z580" s="3"/>
       <c r="AA580" s="3"/>
     </row>
-    <row r="581" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="581">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -17905,7 +17906,7 @@
       <c r="Z581" s="3"/>
       <c r="AA581" s="3"/>
     </row>
-    <row r="582" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="582">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -17934,7 +17935,7 @@
       <c r="Z582" s="3"/>
       <c r="AA582" s="3"/>
     </row>
-    <row r="583" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="583">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -17963,7 +17964,7 @@
       <c r="Z583" s="3"/>
       <c r="AA583" s="3"/>
     </row>
-    <row r="584" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="584">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -17992,7 +17993,7 @@
       <c r="Z584" s="3"/>
       <c r="AA584" s="3"/>
     </row>
-    <row r="585" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="585">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -18021,7 +18022,7 @@
       <c r="Z585" s="3"/>
       <c r="AA585" s="3"/>
     </row>
-    <row r="586" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="586">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -18050,7 +18051,7 @@
       <c r="Z586" s="3"/>
       <c r="AA586" s="3"/>
     </row>
-    <row r="587" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="587">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -18079,7 +18080,7 @@
       <c r="Z587" s="3"/>
       <c r="AA587" s="3"/>
     </row>
-    <row r="588" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="588">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -18108,7 +18109,7 @@
       <c r="Z588" s="3"/>
       <c r="AA588" s="3"/>
     </row>
-    <row r="589" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="589">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -18137,7 +18138,7 @@
       <c r="Z589" s="3"/>
       <c r="AA589" s="3"/>
     </row>
-    <row r="590" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="590">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -18166,7 +18167,7 @@
       <c r="Z590" s="3"/>
       <c r="AA590" s="3"/>
     </row>
-    <row r="591" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="591">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -18195,7 +18196,7 @@
       <c r="Z591" s="3"/>
       <c r="AA591" s="3"/>
     </row>
-    <row r="592" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="592">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -18224,7 +18225,7 @@
       <c r="Z592" s="3"/>
       <c r="AA592" s="3"/>
     </row>
-    <row r="593" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="593">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -18253,7 +18254,7 @@
       <c r="Z593" s="3"/>
       <c r="AA593" s="3"/>
     </row>
-    <row r="594" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="594">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -18282,7 +18283,7 @@
       <c r="Z594" s="3"/>
       <c r="AA594" s="3"/>
     </row>
-    <row r="595" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="595">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -18311,7 +18312,7 @@
       <c r="Z595" s="3"/>
       <c r="AA595" s="3"/>
     </row>
-    <row r="596" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="596">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -18340,7 +18341,7 @@
       <c r="Z596" s="3"/>
       <c r="AA596" s="3"/>
     </row>
-    <row r="597" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="597">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -18369,7 +18370,7 @@
       <c r="Z597" s="3"/>
       <c r="AA597" s="3"/>
     </row>
-    <row r="598" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="598">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -18398,7 +18399,7 @@
       <c r="Z598" s="3"/>
       <c r="AA598" s="3"/>
     </row>
-    <row r="599" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="599">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -18427,7 +18428,7 @@
       <c r="Z599" s="3"/>
       <c r="AA599" s="3"/>
     </row>
-    <row r="600" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="600">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -18456,7 +18457,7 @@
       <c r="Z600" s="3"/>
       <c r="AA600" s="3"/>
     </row>
-    <row r="601" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="601">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -18485,7 +18486,7 @@
       <c r="Z601" s="3"/>
       <c r="AA601" s="3"/>
     </row>
-    <row r="602" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="602">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -18514,7 +18515,7 @@
       <c r="Z602" s="3"/>
       <c r="AA602" s="3"/>
     </row>
-    <row r="603" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="603">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -18543,7 +18544,7 @@
       <c r="Z603" s="3"/>
       <c r="AA603" s="3"/>
     </row>
-    <row r="604" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="604">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -18572,7 +18573,7 @@
       <c r="Z604" s="3"/>
       <c r="AA604" s="3"/>
     </row>
-    <row r="605" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="605">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -18601,7 +18602,7 @@
       <c r="Z605" s="3"/>
       <c r="AA605" s="3"/>
     </row>
-    <row r="606" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="606">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -18630,7 +18631,7 @@
       <c r="Z606" s="3"/>
       <c r="AA606" s="3"/>
     </row>
-    <row r="607" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="607">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -18659,7 +18660,7 @@
       <c r="Z607" s="3"/>
       <c r="AA607" s="3"/>
     </row>
-    <row r="608" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="608">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -18688,7 +18689,7 @@
       <c r="Z608" s="3"/>
       <c r="AA608" s="3"/>
     </row>
-    <row r="609" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="609">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -18717,7 +18718,7 @@
       <c r="Z609" s="3"/>
       <c r="AA609" s="3"/>
     </row>
-    <row r="610" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="610">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -18746,7 +18747,7 @@
       <c r="Z610" s="3"/>
       <c r="AA610" s="3"/>
     </row>
-    <row r="611" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="611">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -18775,7 +18776,7 @@
       <c r="Z611" s="3"/>
       <c r="AA611" s="3"/>
     </row>
-    <row r="612" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="612">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -18804,7 +18805,7 @@
       <c r="Z612" s="3"/>
       <c r="AA612" s="3"/>
     </row>
-    <row r="613" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="613">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -18833,7 +18834,7 @@
       <c r="Z613" s="3"/>
       <c r="AA613" s="3"/>
     </row>
-    <row r="614" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="614">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -18862,7 +18863,7 @@
       <c r="Z614" s="3"/>
       <c r="AA614" s="3"/>
     </row>
-    <row r="615" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="615">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -18891,7 +18892,7 @@
       <c r="Z615" s="3"/>
       <c r="AA615" s="3"/>
     </row>
-    <row r="616" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="616">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -18920,7 +18921,7 @@
       <c r="Z616" s="3"/>
       <c r="AA616" s="3"/>
     </row>
-    <row r="617" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="617">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -18949,7 +18950,7 @@
       <c r="Z617" s="3"/>
       <c r="AA617" s="3"/>
     </row>
-    <row r="618" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="618">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -18978,7 +18979,7 @@
       <c r="Z618" s="3"/>
       <c r="AA618" s="3"/>
     </row>
-    <row r="619" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="619">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -19007,7 +19008,7 @@
       <c r="Z619" s="3"/>
       <c r="AA619" s="3"/>
     </row>
-    <row r="620" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="620">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -19036,7 +19037,7 @@
       <c r="Z620" s="3"/>
       <c r="AA620" s="3"/>
     </row>
-    <row r="621" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="621">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -19065,7 +19066,7 @@
       <c r="Z621" s="3"/>
       <c r="AA621" s="3"/>
     </row>
-    <row r="622" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="622">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -19094,7 +19095,7 @@
       <c r="Z622" s="3"/>
       <c r="AA622" s="3"/>
     </row>
-    <row r="623" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="623">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -19123,7 +19124,7 @@
       <c r="Z623" s="3"/>
       <c r="AA623" s="3"/>
     </row>
-    <row r="624" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="624">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -19152,7 +19153,7 @@
       <c r="Z624" s="3"/>
       <c r="AA624" s="3"/>
     </row>
-    <row r="625" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="625">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -19181,7 +19182,7 @@
       <c r="Z625" s="3"/>
       <c r="AA625" s="3"/>
     </row>
-    <row r="626" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="626">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -19210,7 +19211,7 @@
       <c r="Z626" s="3"/>
       <c r="AA626" s="3"/>
     </row>
-    <row r="627" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="627">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -19239,7 +19240,7 @@
       <c r="Z627" s="3"/>
       <c r="AA627" s="3"/>
     </row>
-    <row r="628" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="628">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -19268,7 +19269,7 @@
       <c r="Z628" s="3"/>
       <c r="AA628" s="3"/>
     </row>
-    <row r="629" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="629">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -19297,7 +19298,7 @@
       <c r="Z629" s="3"/>
       <c r="AA629" s="3"/>
     </row>
-    <row r="630" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="630">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -19326,7 +19327,7 @@
       <c r="Z630" s="3"/>
       <c r="AA630" s="3"/>
     </row>
-    <row r="631" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="631">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -19355,7 +19356,7 @@
       <c r="Z631" s="3"/>
       <c r="AA631" s="3"/>
     </row>
-    <row r="632" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="632">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -19384,7 +19385,7 @@
       <c r="Z632" s="3"/>
       <c r="AA632" s="3"/>
     </row>
-    <row r="633" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="633">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -19413,7 +19414,7 @@
       <c r="Z633" s="3"/>
       <c r="AA633" s="3"/>
     </row>
-    <row r="634" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="634">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -19442,7 +19443,7 @@
       <c r="Z634" s="3"/>
       <c r="AA634" s="3"/>
     </row>
-    <row r="635" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="635">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -19471,7 +19472,7 @@
       <c r="Z635" s="3"/>
       <c r="AA635" s="3"/>
     </row>
-    <row r="636" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="636">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -19500,7 +19501,7 @@
       <c r="Z636" s="3"/>
       <c r="AA636" s="3"/>
     </row>
-    <row r="637" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="637">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -19529,7 +19530,7 @@
       <c r="Z637" s="3"/>
       <c r="AA637" s="3"/>
     </row>
-    <row r="638" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="638">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -19558,7 +19559,7 @@
       <c r="Z638" s="3"/>
       <c r="AA638" s="3"/>
     </row>
-    <row r="639" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="639">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -19587,7 +19588,7 @@
       <c r="Z639" s="3"/>
       <c r="AA639" s="3"/>
     </row>
-    <row r="640" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="640">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -19616,7 +19617,7 @@
       <c r="Z640" s="3"/>
       <c r="AA640" s="3"/>
     </row>
-    <row r="641" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="641">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -19645,7 +19646,7 @@
       <c r="Z641" s="3"/>
       <c r="AA641" s="3"/>
     </row>
-    <row r="642" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="642">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -19674,7 +19675,7 @@
       <c r="Z642" s="3"/>
       <c r="AA642" s="3"/>
     </row>
-    <row r="643" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="643">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -19703,7 +19704,7 @@
       <c r="Z643" s="3"/>
       <c r="AA643" s="3"/>
     </row>
-    <row r="644" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="644">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -19732,7 +19733,7 @@
       <c r="Z644" s="3"/>
       <c r="AA644" s="3"/>
     </row>
-    <row r="645" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="645">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -19761,7 +19762,7 @@
       <c r="Z645" s="3"/>
       <c r="AA645" s="3"/>
     </row>
-    <row r="646" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="646">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -19790,7 +19791,7 @@
       <c r="Z646" s="3"/>
       <c r="AA646" s="3"/>
     </row>
-    <row r="647" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="647">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -19819,7 +19820,7 @@
       <c r="Z647" s="3"/>
       <c r="AA647" s="3"/>
     </row>
-    <row r="648" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="648">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -19848,7 +19849,7 @@
       <c r="Z648" s="3"/>
       <c r="AA648" s="3"/>
     </row>
-    <row r="649" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="649">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -19877,7 +19878,7 @@
       <c r="Z649" s="3"/>
       <c r="AA649" s="3"/>
     </row>
-    <row r="650" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="650">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -19906,7 +19907,7 @@
       <c r="Z650" s="3"/>
       <c r="AA650" s="3"/>
     </row>
-    <row r="651" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="651">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -19935,7 +19936,7 @@
       <c r="Z651" s="3"/>
       <c r="AA651" s="3"/>
     </row>
-    <row r="652" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="652">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -19964,7 +19965,7 @@
       <c r="Z652" s="3"/>
       <c r="AA652" s="3"/>
     </row>
-    <row r="653" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="653">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -19993,7 +19994,7 @@
       <c r="Z653" s="3"/>
       <c r="AA653" s="3"/>
     </row>
-    <row r="654" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="654">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -20022,7 +20023,7 @@
       <c r="Z654" s="3"/>
       <c r="AA654" s="3"/>
     </row>
-    <row r="655" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="655">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -20051,7 +20052,7 @@
       <c r="Z655" s="3"/>
       <c r="AA655" s="3"/>
     </row>
-    <row r="656" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="656">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -20080,7 +20081,7 @@
       <c r="Z656" s="3"/>
       <c r="AA656" s="3"/>
     </row>
-    <row r="657" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="657">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -20109,7 +20110,7 @@
       <c r="Z657" s="3"/>
       <c r="AA657" s="3"/>
     </row>
-    <row r="658" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="658">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -20138,7 +20139,7 @@
       <c r="Z658" s="3"/>
       <c r="AA658" s="3"/>
     </row>
-    <row r="659" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="659">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -20167,7 +20168,7 @@
       <c r="Z659" s="3"/>
       <c r="AA659" s="3"/>
     </row>
-    <row r="660" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="660">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -20196,7 +20197,7 @@
       <c r="Z660" s="3"/>
       <c r="AA660" s="3"/>
     </row>
-    <row r="661" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="661">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -20225,7 +20226,7 @@
       <c r="Z661" s="3"/>
       <c r="AA661" s="3"/>
     </row>
-    <row r="662" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="662">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -20254,7 +20255,7 @@
       <c r="Z662" s="3"/>
       <c r="AA662" s="3"/>
     </row>
-    <row r="663" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="663">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -20283,7 +20284,7 @@
       <c r="Z663" s="3"/>
       <c r="AA663" s="3"/>
     </row>
-    <row r="664" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="664">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -20312,7 +20313,7 @@
       <c r="Z664" s="3"/>
       <c r="AA664" s="3"/>
     </row>
-    <row r="665" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="665">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -20341,7 +20342,7 @@
       <c r="Z665" s="3"/>
       <c r="AA665" s="3"/>
     </row>
-    <row r="666" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="666">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -20370,7 +20371,7 @@
       <c r="Z666" s="3"/>
       <c r="AA666" s="3"/>
     </row>
-    <row r="667" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="667">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -20399,7 +20400,7 @@
       <c r="Z667" s="3"/>
       <c r="AA667" s="3"/>
     </row>
-    <row r="668" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="668">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -20428,7 +20429,7 @@
       <c r="Z668" s="3"/>
       <c r="AA668" s="3"/>
     </row>
-    <row r="669" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="669">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -20457,7 +20458,7 @@
       <c r="Z669" s="3"/>
       <c r="AA669" s="3"/>
     </row>
-    <row r="670" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="670">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -20486,7 +20487,7 @@
       <c r="Z670" s="3"/>
       <c r="AA670" s="3"/>
     </row>
-    <row r="671" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="671">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -20515,7 +20516,7 @@
       <c r="Z671" s="3"/>
       <c r="AA671" s="3"/>
     </row>
-    <row r="672" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="672">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -20544,7 +20545,7 @@
       <c r="Z672" s="3"/>
       <c r="AA672" s="3"/>
     </row>
-    <row r="673" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="673">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -20573,7 +20574,7 @@
       <c r="Z673" s="3"/>
       <c r="AA673" s="3"/>
     </row>
-    <row r="674" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="674">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -20602,7 +20603,7 @@
       <c r="Z674" s="3"/>
       <c r="AA674" s="3"/>
     </row>
-    <row r="675" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="675">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -20631,7 +20632,7 @@
       <c r="Z675" s="3"/>
       <c r="AA675" s="3"/>
     </row>
-    <row r="676" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="676">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -20660,7 +20661,7 @@
       <c r="Z676" s="3"/>
       <c r="AA676" s="3"/>
     </row>
-    <row r="677" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="677">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -20689,7 +20690,7 @@
       <c r="Z677" s="3"/>
       <c r="AA677" s="3"/>
     </row>
-    <row r="678" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="678">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -20718,7 +20719,7 @@
       <c r="Z678" s="3"/>
       <c r="AA678" s="3"/>
     </row>
-    <row r="679" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="679">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -20747,7 +20748,7 @@
       <c r="Z679" s="3"/>
       <c r="AA679" s="3"/>
     </row>
-    <row r="680" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="680">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -20776,7 +20777,7 @@
       <c r="Z680" s="3"/>
       <c r="AA680" s="3"/>
     </row>
-    <row r="681" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="681">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -20805,7 +20806,7 @@
       <c r="Z681" s="3"/>
       <c r="AA681" s="3"/>
     </row>
-    <row r="682" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="682">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -20834,7 +20835,7 @@
       <c r="Z682" s="3"/>
       <c r="AA682" s="3"/>
     </row>
-    <row r="683" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="683">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -20863,7 +20864,7 @@
       <c r="Z683" s="3"/>
       <c r="AA683" s="3"/>
     </row>
-    <row r="684" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="684">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -20892,7 +20893,7 @@
       <c r="Z684" s="3"/>
       <c r="AA684" s="3"/>
     </row>
-    <row r="685" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="685">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -20921,7 +20922,7 @@
       <c r="Z685" s="3"/>
       <c r="AA685" s="3"/>
     </row>
-    <row r="686" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="686">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -20950,7 +20951,7 @@
       <c r="Z686" s="3"/>
       <c r="AA686" s="3"/>
     </row>
-    <row r="687" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="687">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -20979,7 +20980,7 @@
       <c r="Z687" s="3"/>
       <c r="AA687" s="3"/>
     </row>
-    <row r="688" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="688">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -21008,7 +21009,7 @@
       <c r="Z688" s="3"/>
       <c r="AA688" s="3"/>
     </row>
-    <row r="689" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="689">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -21037,7 +21038,7 @@
       <c r="Z689" s="3"/>
       <c r="AA689" s="3"/>
     </row>
-    <row r="690" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="690">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -21066,7 +21067,7 @@
       <c r="Z690" s="3"/>
       <c r="AA690" s="3"/>
     </row>
-    <row r="691" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="691">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -21095,7 +21096,7 @@
       <c r="Z691" s="3"/>
       <c r="AA691" s="3"/>
     </row>
-    <row r="692" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="692">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -21124,7 +21125,7 @@
       <c r="Z692" s="3"/>
       <c r="AA692" s="3"/>
     </row>
-    <row r="693" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="693">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -21153,7 +21154,7 @@
       <c r="Z693" s="3"/>
       <c r="AA693" s="3"/>
     </row>
-    <row r="694" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="694">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -21182,7 +21183,7 @@
       <c r="Z694" s="3"/>
       <c r="AA694" s="3"/>
     </row>
-    <row r="695" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="695">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -21211,7 +21212,7 @@
       <c r="Z695" s="3"/>
       <c r="AA695" s="3"/>
     </row>
-    <row r="696" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="696">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -21240,7 +21241,7 @@
       <c r="Z696" s="3"/>
       <c r="AA696" s="3"/>
     </row>
-    <row r="697" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="697">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -21269,7 +21270,7 @@
       <c r="Z697" s="3"/>
       <c r="AA697" s="3"/>
     </row>
-    <row r="698" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="698">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -21298,7 +21299,7 @@
       <c r="Z698" s="3"/>
       <c r="AA698" s="3"/>
     </row>
-    <row r="699" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="699">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -21327,7 +21328,7 @@
       <c r="Z699" s="3"/>
       <c r="AA699" s="3"/>
     </row>
-    <row r="700" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="700">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -21356,7 +21357,7 @@
       <c r="Z700" s="3"/>
       <c r="AA700" s="3"/>
     </row>
-    <row r="701" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="701">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -21385,7 +21386,7 @@
       <c r="Z701" s="3"/>
       <c r="AA701" s="3"/>
     </row>
-    <row r="702" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="702">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -21414,7 +21415,7 @@
       <c r="Z702" s="3"/>
       <c r="AA702" s="3"/>
     </row>
-    <row r="703" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="703">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -21443,7 +21444,7 @@
       <c r="Z703" s="3"/>
       <c r="AA703" s="3"/>
     </row>
-    <row r="704" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="704">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -21472,7 +21473,7 @@
       <c r="Z704" s="3"/>
       <c r="AA704" s="3"/>
     </row>
-    <row r="705" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="705">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -21501,7 +21502,7 @@
       <c r="Z705" s="3"/>
       <c r="AA705" s="3"/>
     </row>
-    <row r="706" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="706">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -21530,7 +21531,7 @@
       <c r="Z706" s="3"/>
       <c r="AA706" s="3"/>
     </row>
-    <row r="707" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="707">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -21559,7 +21560,7 @@
       <c r="Z707" s="3"/>
       <c r="AA707" s="3"/>
     </row>
-    <row r="708" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="708">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -21588,7 +21589,7 @@
       <c r="Z708" s="3"/>
       <c r="AA708" s="3"/>
     </row>
-    <row r="709" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="709">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -21617,7 +21618,7 @@
       <c r="Z709" s="3"/>
       <c r="AA709" s="3"/>
     </row>
-    <row r="710" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="710">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -21646,7 +21647,7 @@
       <c r="Z710" s="3"/>
       <c r="AA710" s="3"/>
     </row>
-    <row r="711" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="711">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -21675,7 +21676,7 @@
       <c r="Z711" s="3"/>
       <c r="AA711" s="3"/>
     </row>
-    <row r="712" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="712">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -21704,7 +21705,7 @@
       <c r="Z712" s="3"/>
       <c r="AA712" s="3"/>
     </row>
-    <row r="713" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="713">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -21733,7 +21734,7 @@
       <c r="Z713" s="3"/>
       <c r="AA713" s="3"/>
     </row>
-    <row r="714" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="714">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -21762,7 +21763,7 @@
       <c r="Z714" s="3"/>
       <c r="AA714" s="3"/>
     </row>
-    <row r="715" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="715">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -21791,7 +21792,7 @@
       <c r="Z715" s="3"/>
       <c r="AA715" s="3"/>
     </row>
-    <row r="716" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="716">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -21820,7 +21821,7 @@
       <c r="Z716" s="3"/>
       <c r="AA716" s="3"/>
     </row>
-    <row r="717" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="717">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -21849,7 +21850,7 @@
       <c r="Z717" s="3"/>
       <c r="AA717" s="3"/>
     </row>
-    <row r="718" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="718">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -21878,7 +21879,7 @@
       <c r="Z718" s="3"/>
       <c r="AA718" s="3"/>
     </row>
-    <row r="719" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="719">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -21907,7 +21908,7 @@
       <c r="Z719" s="3"/>
       <c r="AA719" s="3"/>
     </row>
-    <row r="720" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="720">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -21936,7 +21937,7 @@
       <c r="Z720" s="3"/>
       <c r="AA720" s="3"/>
     </row>
-    <row r="721" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="721">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -21965,7 +21966,7 @@
       <c r="Z721" s="3"/>
       <c r="AA721" s="3"/>
     </row>
-    <row r="722" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="722">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -21994,7 +21995,7 @@
       <c r="Z722" s="3"/>
       <c r="AA722" s="3"/>
     </row>
-    <row r="723" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="723">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -22023,7 +22024,7 @@
       <c r="Z723" s="3"/>
       <c r="AA723" s="3"/>
     </row>
-    <row r="724" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="724">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -22052,7 +22053,7 @@
       <c r="Z724" s="3"/>
       <c r="AA724" s="3"/>
     </row>
-    <row r="725" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="725">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -22081,7 +22082,7 @@
       <c r="Z725" s="3"/>
       <c r="AA725" s="3"/>
     </row>
-    <row r="726" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="726">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -22110,7 +22111,7 @@
       <c r="Z726" s="3"/>
       <c r="AA726" s="3"/>
     </row>
-    <row r="727" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="727">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -22139,7 +22140,7 @@
       <c r="Z727" s="3"/>
       <c r="AA727" s="3"/>
     </row>
-    <row r="728" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="728">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -22168,7 +22169,7 @@
       <c r="Z728" s="3"/>
       <c r="AA728" s="3"/>
     </row>
-    <row r="729" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="729">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -22197,7 +22198,7 @@
       <c r="Z729" s="3"/>
       <c r="AA729" s="3"/>
     </row>
-    <row r="730" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="730">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -22226,7 +22227,7 @@
       <c r="Z730" s="3"/>
       <c r="AA730" s="3"/>
     </row>
-    <row r="731" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="731">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -22255,7 +22256,7 @@
       <c r="Z731" s="3"/>
       <c r="AA731" s="3"/>
     </row>
-    <row r="732" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="732">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -22284,7 +22285,7 @@
       <c r="Z732" s="3"/>
       <c r="AA732" s="3"/>
     </row>
-    <row r="733" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="733">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -22313,7 +22314,7 @@
       <c r="Z733" s="3"/>
       <c r="AA733" s="3"/>
     </row>
-    <row r="734" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="734">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -22342,7 +22343,7 @@
       <c r="Z734" s="3"/>
       <c r="AA734" s="3"/>
     </row>
-    <row r="735" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="735">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -22371,7 +22372,7 @@
       <c r="Z735" s="3"/>
       <c r="AA735" s="3"/>
     </row>
-    <row r="736" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="736">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -22400,7 +22401,7 @@
       <c r="Z736" s="3"/>
       <c r="AA736" s="3"/>
     </row>
-    <row r="737" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="737">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -22429,7 +22430,7 @@
       <c r="Z737" s="3"/>
       <c r="AA737" s="3"/>
     </row>
-    <row r="738" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="738">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -22458,7 +22459,7 @@
       <c r="Z738" s="3"/>
       <c r="AA738" s="3"/>
     </row>
-    <row r="739" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="739">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -22487,7 +22488,7 @@
       <c r="Z739" s="3"/>
       <c r="AA739" s="3"/>
     </row>
-    <row r="740" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="740">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -22516,7 +22517,7 @@
       <c r="Z740" s="3"/>
       <c r="AA740" s="3"/>
     </row>
-    <row r="741" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="741">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -22545,7 +22546,7 @@
       <c r="Z741" s="3"/>
       <c r="AA741" s="3"/>
     </row>
-    <row r="742" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="742">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -22574,7 +22575,7 @@
       <c r="Z742" s="3"/>
       <c r="AA742" s="3"/>
     </row>
-    <row r="743" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="743">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -22603,7 +22604,7 @@
       <c r="Z743" s="3"/>
       <c r="AA743" s="3"/>
     </row>
-    <row r="744" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="744">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -22632,7 +22633,7 @@
       <c r="Z744" s="3"/>
       <c r="AA744" s="3"/>
     </row>
-    <row r="745" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="745">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -22661,7 +22662,7 @@
       <c r="Z745" s="3"/>
       <c r="AA745" s="3"/>
     </row>
-    <row r="746" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="746">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -22690,7 +22691,7 @@
       <c r="Z746" s="3"/>
       <c r="AA746" s="3"/>
     </row>
-    <row r="747" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="747">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -22719,7 +22720,7 @@
       <c r="Z747" s="3"/>
       <c r="AA747" s="3"/>
     </row>
-    <row r="748" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="748">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -22748,7 +22749,7 @@
       <c r="Z748" s="3"/>
       <c r="AA748" s="3"/>
     </row>
-    <row r="749" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="749">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -22777,7 +22778,7 @@
       <c r="Z749" s="3"/>
       <c r="AA749" s="3"/>
     </row>
-    <row r="750" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="750">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -22806,7 +22807,7 @@
       <c r="Z750" s="3"/>
       <c r="AA750" s="3"/>
     </row>
-    <row r="751" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="751">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -22835,7 +22836,7 @@
       <c r="Z751" s="3"/>
       <c r="AA751" s="3"/>
     </row>
-    <row r="752" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="752">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -22864,7 +22865,7 @@
       <c r="Z752" s="3"/>
       <c r="AA752" s="3"/>
     </row>
-    <row r="753" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="753">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -22893,7 +22894,7 @@
       <c r="Z753" s="3"/>
       <c r="AA753" s="3"/>
     </row>
-    <row r="754" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="754">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -22922,7 +22923,7 @@
       <c r="Z754" s="3"/>
       <c r="AA754" s="3"/>
     </row>
-    <row r="755" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="755">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -22951,7 +22952,7 @@
       <c r="Z755" s="3"/>
       <c r="AA755" s="3"/>
     </row>
-    <row r="756" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="756">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -22980,7 +22981,7 @@
       <c r="Z756" s="3"/>
       <c r="AA756" s="3"/>
     </row>
-    <row r="757" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="757">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -23009,7 +23010,7 @@
       <c r="Z757" s="3"/>
       <c r="AA757" s="3"/>
     </row>
-    <row r="758" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="758">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -23038,7 +23039,7 @@
       <c r="Z758" s="3"/>
       <c r="AA758" s="3"/>
     </row>
-    <row r="759" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="759">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -23067,7 +23068,7 @@
       <c r="Z759" s="3"/>
       <c r="AA759" s="3"/>
     </row>
-    <row r="760" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="760">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -23096,7 +23097,7 @@
       <c r="Z760" s="3"/>
       <c r="AA760" s="3"/>
     </row>
-    <row r="761" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="761">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -23125,7 +23126,7 @@
       <c r="Z761" s="3"/>
       <c r="AA761" s="3"/>
     </row>
-    <row r="762" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="762">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -23154,7 +23155,7 @@
       <c r="Z762" s="3"/>
       <c r="AA762" s="3"/>
     </row>
-    <row r="763" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="763">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -23183,7 +23184,7 @@
       <c r="Z763" s="3"/>
       <c r="AA763" s="3"/>
     </row>
-    <row r="764" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="764">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -23212,7 +23213,7 @@
       <c r="Z764" s="3"/>
       <c r="AA764" s="3"/>
     </row>
-    <row r="765" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="765">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -23241,7 +23242,7 @@
       <c r="Z765" s="3"/>
       <c r="AA765" s="3"/>
     </row>
-    <row r="766" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="766">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -23270,7 +23271,7 @@
       <c r="Z766" s="3"/>
       <c r="AA766" s="3"/>
     </row>
-    <row r="767" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="767">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -23299,7 +23300,7 @@
       <c r="Z767" s="3"/>
       <c r="AA767" s="3"/>
     </row>
-    <row r="768" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="768">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -23328,7 +23329,7 @@
       <c r="Z768" s="3"/>
       <c r="AA768" s="3"/>
     </row>
-    <row r="769" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="769">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -23357,7 +23358,7 @@
       <c r="Z769" s="3"/>
       <c r="AA769" s="3"/>
     </row>
-    <row r="770" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="770">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -23386,7 +23387,7 @@
       <c r="Z770" s="3"/>
       <c r="AA770" s="3"/>
     </row>
-    <row r="771" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="771">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -23415,7 +23416,7 @@
       <c r="Z771" s="3"/>
       <c r="AA771" s="3"/>
     </row>
-    <row r="772" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="772">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -23444,7 +23445,7 @@
       <c r="Z772" s="3"/>
       <c r="AA772" s="3"/>
     </row>
-    <row r="773" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="773">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -23473,7 +23474,7 @@
       <c r="Z773" s="3"/>
       <c r="AA773" s="3"/>
     </row>
-    <row r="774" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="774">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -23502,7 +23503,7 @@
       <c r="Z774" s="3"/>
       <c r="AA774" s="3"/>
     </row>
-    <row r="775" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="775">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -23531,7 +23532,7 @@
       <c r="Z775" s="3"/>
       <c r="AA775" s="3"/>
     </row>
-    <row r="776" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="776">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -23560,7 +23561,7 @@
       <c r="Z776" s="3"/>
       <c r="AA776" s="3"/>
     </row>
-    <row r="777" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="777">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -23589,7 +23590,7 @@
       <c r="Z777" s="3"/>
       <c r="AA777" s="3"/>
     </row>
-    <row r="778" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="778">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -23618,7 +23619,7 @@
       <c r="Z778" s="3"/>
       <c r="AA778" s="3"/>
     </row>
-    <row r="779" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="779">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -23647,7 +23648,7 @@
       <c r="Z779" s="3"/>
       <c r="AA779" s="3"/>
     </row>
-    <row r="780" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="780">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -23676,7 +23677,7 @@
       <c r="Z780" s="3"/>
       <c r="AA780" s="3"/>
     </row>
-    <row r="781" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="781">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -23705,7 +23706,7 @@
       <c r="Z781" s="3"/>
       <c r="AA781" s="3"/>
     </row>
-    <row r="782" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="782">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -23734,7 +23735,7 @@
       <c r="Z782" s="3"/>
       <c r="AA782" s="3"/>
     </row>
-    <row r="783" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="783">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -23763,7 +23764,7 @@
       <c r="Z783" s="3"/>
       <c r="AA783" s="3"/>
     </row>
-    <row r="784" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="784">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -23792,7 +23793,7 @@
       <c r="Z784" s="3"/>
       <c r="AA784" s="3"/>
     </row>
-    <row r="785" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="785">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -23821,7 +23822,7 @@
       <c r="Z785" s="3"/>
       <c r="AA785" s="3"/>
     </row>
-    <row r="786" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="786">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -23850,7 +23851,7 @@
       <c r="Z786" s="3"/>
       <c r="AA786" s="3"/>
     </row>
-    <row r="787" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="787">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -23879,7 +23880,7 @@
       <c r="Z787" s="3"/>
       <c r="AA787" s="3"/>
     </row>
-    <row r="788" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="788">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -23908,7 +23909,7 @@
       <c r="Z788" s="3"/>
       <c r="AA788" s="3"/>
     </row>
-    <row r="789" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="789">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -23937,7 +23938,7 @@
       <c r="Z789" s="3"/>
       <c r="AA789" s="3"/>
     </row>
-    <row r="790" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="790">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -23966,7 +23967,7 @@
       <c r="Z790" s="3"/>
       <c r="AA790" s="3"/>
     </row>
-    <row r="791" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="791">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -23995,7 +23996,7 @@
       <c r="Z791" s="3"/>
       <c r="AA791" s="3"/>
     </row>
-    <row r="792" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="792">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -24024,7 +24025,7 @@
       <c r="Z792" s="3"/>
       <c r="AA792" s="3"/>
     </row>
-    <row r="793" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="793">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -24053,7 +24054,7 @@
       <c r="Z793" s="3"/>
       <c r="AA793" s="3"/>
     </row>
-    <row r="794" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="794">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -24082,7 +24083,7 @@
       <c r="Z794" s="3"/>
       <c r="AA794" s="3"/>
     </row>
-    <row r="795" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="795">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -24111,7 +24112,7 @@
       <c r="Z795" s="3"/>
       <c r="AA795" s="3"/>
     </row>
-    <row r="796" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="796">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -24140,7 +24141,7 @@
       <c r="Z796" s="3"/>
       <c r="AA796" s="3"/>
     </row>
-    <row r="797" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="797">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -24169,7 +24170,7 @@
       <c r="Z797" s="3"/>
       <c r="AA797" s="3"/>
     </row>
-    <row r="798" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="798">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -24198,7 +24199,7 @@
       <c r="Z798" s="3"/>
       <c r="AA798" s="3"/>
     </row>
-    <row r="799" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="799">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -24227,7 +24228,7 @@
       <c r="Z799" s="3"/>
       <c r="AA799" s="3"/>
     </row>
-    <row r="800" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="800">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -24256,7 +24257,7 @@
       <c r="Z800" s="3"/>
       <c r="AA800" s="3"/>
     </row>
-    <row r="801" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="801">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -24285,7 +24286,7 @@
       <c r="Z801" s="3"/>
       <c r="AA801" s="3"/>
     </row>
-    <row r="802" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="802">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -24314,7 +24315,7 @@
       <c r="Z802" s="3"/>
       <c r="AA802" s="3"/>
     </row>
-    <row r="803" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="803">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -24343,7 +24344,7 @@
       <c r="Z803" s="3"/>
       <c r="AA803" s="3"/>
     </row>
-    <row r="804" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="804">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -24372,7 +24373,7 @@
       <c r="Z804" s="3"/>
       <c r="AA804" s="3"/>
     </row>
-    <row r="805" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="805">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -24401,7 +24402,7 @@
       <c r="Z805" s="3"/>
       <c r="AA805" s="3"/>
     </row>
-    <row r="806" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="806">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -24430,7 +24431,7 @@
       <c r="Z806" s="3"/>
       <c r="AA806" s="3"/>
     </row>
-    <row r="807" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="807">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -24459,7 +24460,7 @@
       <c r="Z807" s="3"/>
       <c r="AA807" s="3"/>
     </row>
-    <row r="808" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="808">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -24488,7 +24489,7 @@
       <c r="Z808" s="3"/>
       <c r="AA808" s="3"/>
     </row>
-    <row r="809" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="809">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -24517,7 +24518,7 @@
       <c r="Z809" s="3"/>
       <c r="AA809" s="3"/>
     </row>
-    <row r="810" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="810">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -24546,7 +24547,7 @@
       <c r="Z810" s="3"/>
       <c r="AA810" s="3"/>
     </row>
-    <row r="811" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="811">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -24575,7 +24576,7 @@
       <c r="Z811" s="3"/>
       <c r="AA811" s="3"/>
     </row>
-    <row r="812" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="812">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -24604,7 +24605,7 @@
       <c r="Z812" s="3"/>
       <c r="AA812" s="3"/>
     </row>
-    <row r="813" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="813">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -24633,7 +24634,7 @@
       <c r="Z813" s="3"/>
       <c r="AA813" s="3"/>
     </row>
-    <row r="814" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="814">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -24662,7 +24663,7 @@
       <c r="Z814" s="3"/>
       <c r="AA814" s="3"/>
     </row>
-    <row r="815" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="815">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -24691,7 +24692,7 @@
       <c r="Z815" s="3"/>
       <c r="AA815" s="3"/>
     </row>
-    <row r="816" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="816">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -24720,7 +24721,7 @@
       <c r="Z816" s="3"/>
       <c r="AA816" s="3"/>
     </row>
-    <row r="817" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="817">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -24749,7 +24750,7 @@
       <c r="Z817" s="3"/>
       <c r="AA817" s="3"/>
     </row>
-    <row r="818" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="818">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -24778,7 +24779,7 @@
       <c r="Z818" s="3"/>
       <c r="AA818" s="3"/>
     </row>
-    <row r="819" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="819">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -24807,7 +24808,7 @@
       <c r="Z819" s="3"/>
       <c r="AA819" s="3"/>
     </row>
-    <row r="820" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="820">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -24836,7 +24837,7 @@
       <c r="Z820" s="3"/>
       <c r="AA820" s="3"/>
     </row>
-    <row r="821" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="821">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -24865,7 +24866,7 @@
       <c r="Z821" s="3"/>
       <c r="AA821" s="3"/>
     </row>
-    <row r="822" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="822">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -24894,7 +24895,7 @@
       <c r="Z822" s="3"/>
       <c r="AA822" s="3"/>
     </row>
-    <row r="823" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="823">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -24923,7 +24924,7 @@
       <c r="Z823" s="3"/>
       <c r="AA823" s="3"/>
     </row>
-    <row r="824" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="824">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -24952,7 +24953,7 @@
       <c r="Z824" s="3"/>
       <c r="AA824" s="3"/>
     </row>
-    <row r="825" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="825">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -24981,7 +24982,7 @@
       <c r="Z825" s="3"/>
       <c r="AA825" s="3"/>
     </row>
-    <row r="826" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="826">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -25010,7 +25011,7 @@
       <c r="Z826" s="3"/>
       <c r="AA826" s="3"/>
     </row>
-    <row r="827" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="827">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -25039,7 +25040,7 @@
       <c r="Z827" s="3"/>
       <c r="AA827" s="3"/>
     </row>
-    <row r="828" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="828">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -25068,7 +25069,7 @@
       <c r="Z828" s="3"/>
       <c r="AA828" s="3"/>
     </row>
-    <row r="829" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="829">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -25097,7 +25098,7 @@
       <c r="Z829" s="3"/>
       <c r="AA829" s="3"/>
     </row>
-    <row r="830" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="830">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -25126,7 +25127,7 @@
       <c r="Z830" s="3"/>
       <c r="AA830" s="3"/>
     </row>
-    <row r="831" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="831">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -25155,7 +25156,7 @@
       <c r="Z831" s="3"/>
       <c r="AA831" s="3"/>
     </row>
-    <row r="832" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="832">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -25184,7 +25185,7 @@
       <c r="Z832" s="3"/>
       <c r="AA832" s="3"/>
     </row>
-    <row r="833" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="833">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -25213,7 +25214,7 @@
       <c r="Z833" s="3"/>
       <c r="AA833" s="3"/>
     </row>
-    <row r="834" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="834">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -25242,7 +25243,7 @@
       <c r="Z834" s="3"/>
       <c r="AA834" s="3"/>
     </row>
-    <row r="835" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="835">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -25271,7 +25272,7 @@
       <c r="Z835" s="3"/>
       <c r="AA835" s="3"/>
     </row>
-    <row r="836" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="836">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -25300,7 +25301,7 @@
       <c r="Z836" s="3"/>
       <c r="AA836" s="3"/>
     </row>
-    <row r="837" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="837">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -25329,7 +25330,7 @@
       <c r="Z837" s="3"/>
       <c r="AA837" s="3"/>
     </row>
-    <row r="838" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="838">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -25358,7 +25359,7 @@
       <c r="Z838" s="3"/>
       <c r="AA838" s="3"/>
     </row>
-    <row r="839" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="839">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -25387,7 +25388,7 @@
       <c r="Z839" s="3"/>
       <c r="AA839" s="3"/>
     </row>
-    <row r="840" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="840">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -25416,7 +25417,7 @@
       <c r="Z840" s="3"/>
       <c r="AA840" s="3"/>
     </row>
-    <row r="841" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="841">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -25445,7 +25446,7 @@
       <c r="Z841" s="3"/>
       <c r="AA841" s="3"/>
     </row>
-    <row r="842" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="842">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -25474,7 +25475,7 @@
       <c r="Z842" s="3"/>
       <c r="AA842" s="3"/>
     </row>
-    <row r="843" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="843">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -25503,7 +25504,7 @@
       <c r="Z843" s="3"/>
       <c r="AA843" s="3"/>
     </row>
-    <row r="844" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="844">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -25532,7 +25533,7 @@
       <c r="Z844" s="3"/>
       <c r="AA844" s="3"/>
     </row>
-    <row r="845" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="845">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -25561,7 +25562,7 @@
       <c r="Z845" s="3"/>
       <c r="AA845" s="3"/>
     </row>
-    <row r="846" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="846">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -25590,7 +25591,7 @@
       <c r="Z846" s="3"/>
       <c r="AA846" s="3"/>
     </row>
-    <row r="847" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="847">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -25619,7 +25620,7 @@
       <c r="Z847" s="3"/>
       <c r="AA847" s="3"/>
     </row>
-    <row r="848" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="848">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -25648,7 +25649,7 @@
       <c r="Z848" s="3"/>
       <c r="AA848" s="3"/>
     </row>
-    <row r="849" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="849">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -25677,7 +25678,7 @@
       <c r="Z849" s="3"/>
       <c r="AA849" s="3"/>
     </row>
-    <row r="850" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="850">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -25706,7 +25707,7 @@
       <c r="Z850" s="3"/>
       <c r="AA850" s="3"/>
     </row>
-    <row r="851" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="851">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -25735,7 +25736,7 @@
       <c r="Z851" s="3"/>
       <c r="AA851" s="3"/>
     </row>
-    <row r="852" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="852">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -25764,7 +25765,7 @@
       <c r="Z852" s="3"/>
       <c r="AA852" s="3"/>
     </row>
-    <row r="853" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="853">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -25793,7 +25794,7 @@
       <c r="Z853" s="3"/>
       <c r="AA853" s="3"/>
     </row>
-    <row r="854" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="854">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -25822,7 +25823,7 @@
       <c r="Z854" s="3"/>
       <c r="AA854" s="3"/>
     </row>
-    <row r="855" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="855">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -25851,7 +25852,7 @@
       <c r="Z855" s="3"/>
       <c r="AA855" s="3"/>
     </row>
-    <row r="856" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="856">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -25880,7 +25881,7 @@
       <c r="Z856" s="3"/>
       <c r="AA856" s="3"/>
     </row>
-    <row r="857" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="857">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -25909,7 +25910,7 @@
       <c r="Z857" s="3"/>
       <c r="AA857" s="3"/>
     </row>
-    <row r="858" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="858">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -25938,7 +25939,7 @@
       <c r="Z858" s="3"/>
       <c r="AA858" s="3"/>
     </row>
-    <row r="859" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="859">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -25967,7 +25968,7 @@
       <c r="Z859" s="3"/>
       <c r="AA859" s="3"/>
     </row>
-    <row r="860" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="860">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -25996,7 +25997,7 @@
       <c r="Z860" s="3"/>
       <c r="AA860" s="3"/>
     </row>
-    <row r="861" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="861">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -26025,7 +26026,7 @@
       <c r="Z861" s="3"/>
       <c r="AA861" s="3"/>
     </row>
-    <row r="862" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="862">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -26054,7 +26055,7 @@
       <c r="Z862" s="3"/>
       <c r="AA862" s="3"/>
     </row>
-    <row r="863" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="863">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -26083,7 +26084,7 @@
       <c r="Z863" s="3"/>
       <c r="AA863" s="3"/>
     </row>
-    <row r="864" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="864">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -26112,7 +26113,7 @@
       <c r="Z864" s="3"/>
       <c r="AA864" s="3"/>
     </row>
-    <row r="865" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="865">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -26141,7 +26142,7 @@
       <c r="Z865" s="3"/>
       <c r="AA865" s="3"/>
     </row>
-    <row r="866" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="866">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -26170,7 +26171,7 @@
       <c r="Z866" s="3"/>
       <c r="AA866" s="3"/>
     </row>
-    <row r="867" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="867">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -26199,7 +26200,7 @@
       <c r="Z867" s="3"/>
       <c r="AA867" s="3"/>
     </row>
-    <row r="868" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="868">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -26228,7 +26229,7 @@
       <c r="Z868" s="3"/>
       <c r="AA868" s="3"/>
     </row>
-    <row r="869" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="869">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -26257,7 +26258,7 @@
       <c r="Z869" s="3"/>
       <c r="AA869" s="3"/>
     </row>
-    <row r="870" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="870">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -26286,7 +26287,7 @@
       <c r="Z870" s="3"/>
       <c r="AA870" s="3"/>
     </row>
-    <row r="871" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="871">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -26315,7 +26316,7 @@
       <c r="Z871" s="3"/>
       <c r="AA871" s="3"/>
     </row>
-    <row r="872" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="872">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -26344,7 +26345,7 @@
       <c r="Z872" s="3"/>
       <c r="AA872" s="3"/>
     </row>
-    <row r="873" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="873">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -26373,7 +26374,7 @@
       <c r="Z873" s="3"/>
       <c r="AA873" s="3"/>
     </row>
-    <row r="874" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="874">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -26402,7 +26403,7 @@
       <c r="Z874" s="3"/>
       <c r="AA874" s="3"/>
     </row>
-    <row r="875" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="875">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -26431,7 +26432,7 @@
       <c r="Z875" s="3"/>
       <c r="AA875" s="3"/>
     </row>
-    <row r="876" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="876">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -26460,7 +26461,7 @@
       <c r="Z876" s="3"/>
       <c r="AA876" s="3"/>
     </row>
-    <row r="877" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="877">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -26489,7 +26490,7 @@
       <c r="Z877" s="3"/>
       <c r="AA877" s="3"/>
     </row>
-    <row r="878" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="878">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -26518,7 +26519,7 @@
       <c r="Z878" s="3"/>
       <c r="AA878" s="3"/>
     </row>
-    <row r="879" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="879">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -26547,7 +26548,7 @@
       <c r="Z879" s="3"/>
       <c r="AA879" s="3"/>
     </row>
-    <row r="880" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="880">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -26576,7 +26577,7 @@
       <c r="Z880" s="3"/>
       <c r="AA880" s="3"/>
     </row>
-    <row r="881" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="881">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -26605,7 +26606,7 @@
       <c r="Z881" s="3"/>
       <c r="AA881" s="3"/>
     </row>
-    <row r="882" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="882">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -26634,7 +26635,7 @@
       <c r="Z882" s="3"/>
       <c r="AA882" s="3"/>
     </row>
-    <row r="883" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="883">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -26663,7 +26664,7 @@
       <c r="Z883" s="3"/>
       <c r="AA883" s="3"/>
     </row>
-    <row r="884" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="884">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -26692,7 +26693,7 @@
       <c r="Z884" s="3"/>
       <c r="AA884" s="3"/>
     </row>
-    <row r="885" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="885">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -26721,7 +26722,7 @@
       <c r="Z885" s="3"/>
       <c r="AA885" s="3"/>
     </row>
-    <row r="886" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="886">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -26750,7 +26751,7 @@
       <c r="Z886" s="3"/>
       <c r="AA886" s="3"/>
     </row>
-    <row r="887" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="887">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -26779,7 +26780,7 @@
       <c r="Z887" s="3"/>
       <c r="AA887" s="3"/>
     </row>
-    <row r="888" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="888">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -26808,7 +26809,7 @@
       <c r="Z888" s="3"/>
       <c r="AA888" s="3"/>
     </row>
-    <row r="889" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="889">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -26837,7 +26838,7 @@
       <c r="Z889" s="3"/>
       <c r="AA889" s="3"/>
     </row>
-    <row r="890" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="890">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -26866,7 +26867,7 @@
       <c r="Z890" s="3"/>
       <c r="AA890" s="3"/>
     </row>
-    <row r="891" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="891">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -26895,7 +26896,7 @@
       <c r="Z891" s="3"/>
       <c r="AA891" s="3"/>
     </row>
-    <row r="892" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="892">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -26924,7 +26925,7 @@
       <c r="Z892" s="3"/>
       <c r="AA892" s="3"/>
     </row>
-    <row r="893" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="893">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -26953,7 +26954,7 @@
       <c r="Z893" s="3"/>
       <c r="AA893" s="3"/>
     </row>
-    <row r="894" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="894">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -26982,7 +26983,7 @@
       <c r="Z894" s="3"/>
       <c r="AA894" s="3"/>
     </row>
-    <row r="895" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="895">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -27011,7 +27012,7 @@
       <c r="Z895" s="3"/>
       <c r="AA895" s="3"/>
     </row>
-    <row r="896" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="896">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -27040,7 +27041,7 @@
       <c r="Z896" s="3"/>
       <c r="AA896" s="3"/>
     </row>
-    <row r="897" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="897">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -27069,7 +27070,7 @@
       <c r="Z897" s="3"/>
       <c r="AA897" s="3"/>
     </row>
-    <row r="898" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="898">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -27098,7 +27099,7 @@
       <c r="Z898" s="3"/>
       <c r="AA898" s="3"/>
     </row>
-    <row r="899" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="899">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -27127,7 +27128,7 @@
       <c r="Z899" s="3"/>
       <c r="AA899" s="3"/>
     </row>
-    <row r="900" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="900">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -27156,7 +27157,7 @@
       <c r="Z900" s="3"/>
       <c r="AA900" s="3"/>
     </row>
-    <row r="901" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="901">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -27185,7 +27186,7 @@
       <c r="Z901" s="3"/>
       <c r="AA901" s="3"/>
     </row>
-    <row r="902" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="902">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -27214,7 +27215,7 @@
       <c r="Z902" s="3"/>
       <c r="AA902" s="3"/>
     </row>
-    <row r="903" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="903">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -27243,7 +27244,7 @@
       <c r="Z903" s="3"/>
       <c r="AA903" s="3"/>
     </row>
-    <row r="904" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="904">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -27272,7 +27273,7 @@
       <c r="Z904" s="3"/>
       <c r="AA904" s="3"/>
     </row>
-    <row r="905" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="905">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -27301,7 +27302,7 @@
       <c r="Z905" s="3"/>
       <c r="AA905" s="3"/>
     </row>
-    <row r="906" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="906">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -27330,7 +27331,7 @@
       <c r="Z906" s="3"/>
       <c r="AA906" s="3"/>
     </row>
-    <row r="907" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="907">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -27359,7 +27360,7 @@
       <c r="Z907" s="3"/>
       <c r="AA907" s="3"/>
     </row>
-    <row r="908" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="908">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -27388,7 +27389,7 @@
       <c r="Z908" s="3"/>
       <c r="AA908" s="3"/>
     </row>
-    <row r="909" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="909">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -27417,7 +27418,7 @@
       <c r="Z909" s="3"/>
       <c r="AA909" s="3"/>
     </row>
-    <row r="910" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="910">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -27446,7 +27447,7 @@
       <c r="Z910" s="3"/>
       <c r="AA910" s="3"/>
     </row>
-    <row r="911" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="911">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -27475,7 +27476,7 @@
       <c r="Z911" s="3"/>
       <c r="AA911" s="3"/>
     </row>
-    <row r="912" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="912">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -27504,7 +27505,7 @@
       <c r="Z912" s="3"/>
       <c r="AA912" s="3"/>
     </row>
-    <row r="913" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="913">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -27533,7 +27534,7 @@
       <c r="Z913" s="3"/>
       <c r="AA913" s="3"/>
     </row>
-    <row r="914" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="914">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -27562,7 +27563,7 @@
       <c r="Z914" s="3"/>
       <c r="AA914" s="3"/>
     </row>
-    <row r="915" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="915">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -27591,7 +27592,7 @@
       <c r="Z915" s="3"/>
       <c r="AA915" s="3"/>
     </row>
-    <row r="916" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="916">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -27620,7 +27621,7 @@
       <c r="Z916" s="3"/>
       <c r="AA916" s="3"/>
     </row>
-    <row r="917" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="917">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -27649,7 +27650,7 @@
       <c r="Z917" s="3"/>
       <c r="AA917" s="3"/>
     </row>
-    <row r="918" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="918">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -27678,7 +27679,7 @@
       <c r="Z918" s="3"/>
       <c r="AA918" s="3"/>
     </row>
-    <row r="919" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="919">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -27707,7 +27708,7 @@
       <c r="Z919" s="3"/>
       <c r="AA919" s="3"/>
     </row>
-    <row r="920" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="920">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -27736,7 +27737,7 @@
       <c r="Z920" s="3"/>
       <c r="AA920" s="3"/>
     </row>
-    <row r="921" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="921">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -27765,7 +27766,7 @@
       <c r="Z921" s="3"/>
       <c r="AA921" s="3"/>
     </row>
-    <row r="922" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="922">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -27794,7 +27795,7 @@
       <c r="Z922" s="3"/>
       <c r="AA922" s="3"/>
     </row>
-    <row r="923" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="923">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -27823,7 +27824,7 @@
       <c r="Z923" s="3"/>
       <c r="AA923" s="3"/>
     </row>
-    <row r="924" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="924">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -27852,7 +27853,7 @@
       <c r="Z924" s="3"/>
       <c r="AA924" s="3"/>
     </row>
-    <row r="925" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="925">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -27881,7 +27882,7 @@
       <c r="Z925" s="3"/>
       <c r="AA925" s="3"/>
     </row>
-    <row r="926" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="926">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -27910,7 +27911,7 @@
       <c r="Z926" s="3"/>
       <c r="AA926" s="3"/>
     </row>
-    <row r="927" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="927">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -27939,7 +27940,7 @@
       <c r="Z927" s="3"/>
       <c r="AA927" s="3"/>
     </row>
-    <row r="928" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="928">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -27968,7 +27969,7 @@
       <c r="Z928" s="3"/>
       <c r="AA928" s="3"/>
     </row>
-    <row r="929" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="929">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -27997,7 +27998,7 @@
       <c r="Z929" s="3"/>
       <c r="AA929" s="3"/>
     </row>
-    <row r="930" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="930">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -28026,7 +28027,7 @@
       <c r="Z930" s="3"/>
       <c r="AA930" s="3"/>
     </row>
-    <row r="931" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="931">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -28055,7 +28056,7 @@
       <c r="Z931" s="3"/>
       <c r="AA931" s="3"/>
     </row>
-    <row r="932" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="932">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -28084,7 +28085,7 @@
       <c r="Z932" s="3"/>
       <c r="AA932" s="3"/>
     </row>
-    <row r="933" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="933">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -28113,7 +28114,7 @@
       <c r="Z933" s="3"/>
       <c r="AA933" s="3"/>
     </row>
-    <row r="934" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="934">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -28142,7 +28143,7 @@
       <c r="Z934" s="3"/>
       <c r="AA934" s="3"/>
     </row>
-    <row r="935" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="935">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -28171,7 +28172,7 @@
       <c r="Z935" s="3"/>
       <c r="AA935" s="3"/>
     </row>
-    <row r="936" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="936">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -28200,7 +28201,7 @@
       <c r="Z936" s="3"/>
       <c r="AA936" s="3"/>
     </row>
-    <row r="937" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="937">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -28229,7 +28230,7 @@
       <c r="Z937" s="3"/>
       <c r="AA937" s="3"/>
     </row>
-    <row r="938" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="938">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -28258,7 +28259,7 @@
       <c r="Z938" s="3"/>
       <c r="AA938" s="3"/>
     </row>
-    <row r="939" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="939">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -28287,7 +28288,7 @@
       <c r="Z939" s="3"/>
       <c r="AA939" s="3"/>
     </row>
-    <row r="940" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="940">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -28316,7 +28317,7 @@
       <c r="Z940" s="3"/>
       <c r="AA940" s="3"/>
     </row>
-    <row r="941" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="941">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -28345,7 +28346,7 @@
       <c r="Z941" s="3"/>
       <c r="AA941" s="3"/>
     </row>
-    <row r="942" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="942">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -28374,7 +28375,7 @@
       <c r="Z942" s="3"/>
       <c r="AA942" s="3"/>
     </row>
-    <row r="943" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="943">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -28403,7 +28404,7 @@
       <c r="Z943" s="3"/>
       <c r="AA943" s="3"/>
     </row>
-    <row r="944" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="944">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -28432,7 +28433,7 @@
       <c r="Z944" s="3"/>
       <c r="AA944" s="3"/>
     </row>
-    <row r="945" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="945">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -28461,7 +28462,7 @@
       <c r="Z945" s="3"/>
       <c r="AA945" s="3"/>
     </row>
-    <row r="946" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="946">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -28490,7 +28491,7 @@
       <c r="Z946" s="3"/>
       <c r="AA946" s="3"/>
     </row>
-    <row r="947" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="947">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -28519,7 +28520,7 @@
       <c r="Z947" s="3"/>
       <c r="AA947" s="3"/>
     </row>
-    <row r="948" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="948">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -28548,7 +28549,7 @@
       <c r="Z948" s="3"/>
       <c r="AA948" s="3"/>
     </row>
-    <row r="949" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="949">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -28577,7 +28578,7 @@
       <c r="Z949" s="3"/>
       <c r="AA949" s="3"/>
     </row>
-    <row r="950" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="950">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -28606,7 +28607,7 @@
       <c r="Z950" s="3"/>
       <c r="AA950" s="3"/>
     </row>
-    <row r="951" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="951">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -28635,7 +28636,7 @@
       <c r="Z951" s="3"/>
       <c r="AA951" s="3"/>
     </row>
-    <row r="952" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="952">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -28664,7 +28665,7 @@
       <c r="Z952" s="3"/>
       <c r="AA952" s="3"/>
     </row>
-    <row r="953" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="953">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -28694,6 +28695,6 @@
       <c r="AA953" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Week_6/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_6/Capstone Timesheet_Ripal Patel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t>Week_1</t>
   </si>
@@ -177,6 +177,9 @@
   <si>
     <t>Mentor Checklist</t>
   </si>
+  <si>
+    <t>set up the Laravel project, connected the database, installed the login/register system, added user roles (patient, doctor, admin), created role-based dashboard routes, and worked on debugging the login/session issue.</t>
+  </si>
 </sst>
 </file>
 
@@ -323,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -476,6 +479,9 @@
     </xf>
     <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -3083,10 +3089,16 @@
       <c r="AA70" s="3"/>
     </row>
     <row r="71">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
+      <c r="A71" s="49"/>
+      <c r="B71" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C71" s="51">
+        <v>46076.0</v>
+      </c>
+      <c r="D71" s="52">
+        <v>3.75</v>
+      </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
@@ -3112,15 +3124,10 @@
       <c r="AA71" s="3"/>
     </row>
     <row r="72">
-      <c r="A72" s="53"/>
-      <c r="B72" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="55"/>
-      <c r="D72" s="49">
-        <f>sum(D67:D70)</f>
-        <v>5.75</v>
-      </c>
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -3146,10 +3153,15 @@
       <c r="AA72" s="3"/>
     </row>
     <row r="73">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
+      <c r="A73" s="54"/>
+      <c r="B73" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="56"/>
+      <c r="D73" s="49">
+        <f>sum(D67:D71)</f>
+        <v>9.5</v>
+      </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
@@ -28694,6 +28706,35 @@
       <c r="Z953" s="3"/>
       <c r="AA953" s="3"/>
     </row>
+    <row r="954">
+      <c r="A954" s="3"/>
+      <c r="B954" s="3"/>
+      <c r="C954" s="3"/>
+      <c r="D954" s="3"/>
+      <c r="E954" s="3"/>
+      <c r="F954" s="3"/>
+      <c r="G954" s="3"/>
+      <c r="H954" s="3"/>
+      <c r="I954" s="3"/>
+      <c r="J954" s="3"/>
+      <c r="K954" s="3"/>
+      <c r="L954" s="3"/>
+      <c r="M954" s="3"/>
+      <c r="N954" s="3"/>
+      <c r="O954" s="3"/>
+      <c r="P954" s="3"/>
+      <c r="Q954" s="3"/>
+      <c r="R954" s="3"/>
+      <c r="S954" s="3"/>
+      <c r="T954" s="3"/>
+      <c r="U954" s="3"/>
+      <c r="V954" s="3"/>
+      <c r="W954" s="3"/>
+      <c r="X954" s="3"/>
+      <c r="Y954" s="3"/>
+      <c r="Z954" s="3"/>
+      <c r="AA954" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
